--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>44461</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>44517</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45526</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>46125</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44651</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46051</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46125</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45278</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44480</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>44470</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45002</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44913</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45188</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44523</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45119</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44880</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45530</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>45147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>46037</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44549</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44790</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44608</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>44616</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44880</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>44523</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44771</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>44868</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>44753</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44735</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44517</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>44785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44865</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44606</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44523</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44544</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45166</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>44970</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>44747</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45453</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>45197</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45091</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>45148</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>45593</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45012</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>44944</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>45439</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>45530</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>45701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>45716</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45337</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45127</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45127</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45279</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45755</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45359</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>44517</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45415</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>45551</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>45476</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>45371</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>45148</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>45124</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45124</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45527</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45891</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45527</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45831</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45821</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45632</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45894</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>45897</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45999</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45761</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>45477</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44881</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>45931</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45483</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44662</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>45905</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>45905</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>44847</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>45241</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45723</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45287</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>44489</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44524</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>45932</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>45623</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>46146</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>46146</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>46146</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45497</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>45932</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45932</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45148</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>45447</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45999</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>46146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44970</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45404</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45947</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>46149</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45667</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>46153</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>46153</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45439</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>46153</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44697</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>44902</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44987</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45274</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>44756</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45988</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45784</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45988</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>44894</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45993</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45993</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45993</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>46163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>46163</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45237</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>44550</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44550</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>44970</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45478</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>46003</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45399</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>45593</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45272</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44876</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45442</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45446</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45148</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44578</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45121</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>44916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>46030</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44823</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44638</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45765</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>44535</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>44915</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>44581</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45127</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45127</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44662</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>45533</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45905</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>46052</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45593</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45378</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45614</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>44542</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>45078</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>46182</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>46181</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>46181</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>46079</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45124</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>46186</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>46086</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>46186</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46186</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45105</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>46188</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45085</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44812</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45526</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44719</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45127</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>46106</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>46108</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>46201</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>46245</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>46122</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>46121</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>46126</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45709</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>46202</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>46245</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>46129</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>46245</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>46245</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>46132</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45237</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>46135</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>45099</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45632</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45960</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>44902</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45723</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>46251</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44581</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>46251</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>46209</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45062</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>46209</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>45124</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>46255</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45532</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45075</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45614</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>44796</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>44936</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>44916</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45127</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45049</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>45439</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>46222</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45530</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45789</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45355</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45802</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45055</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45727</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45470</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>45834</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45835</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>45755</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>44834</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45266</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45266</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44901</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>44901</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45266</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>44606</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44606</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45834</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE260"/>
+  <dimension ref="A1:AE261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>44517</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 34758-2024</t>
+          <t>A 18094-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45526</v>
+        <v>46125</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -894,21 +894,134 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blackticka
+Fjällig taggsvamp s.str.
+Brandticka
+Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18094-2026 artfynd.xlsx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18094-2026 karta.png", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18094-2026 georefererad karta.tif", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18094-2026 FSC-klagomål.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18094-2026 FSC-klagomål mail.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18094-2026 tillsynsbegäran.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18094-2026 tillsynsbegäran mail.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 34758-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45526</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp
 Fjällig taggsvamp s.str.
@@ -916,148 +1029,35 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 34758-2024 artfynd.xlsx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 34758-2024 karta.png", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 34758-2024 georefererad karta.tif", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 34758-2024 FSC-klagomål.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 34758-2024 FSC-klagomål mail.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 34758-2024 tillsynsbegäran.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 34758-2024 tillsynsbegäran mail.docx", "A 34758-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 18094-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46125</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blackticka
-Fjällig taggsvamp s.str.
-Brandticka
-Mörk husmossa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18094-2026 artfynd.xlsx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18094-2026 karta.png", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18094-2026 georefererad karta.tif", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18094-2026 FSC-klagomål.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18094-2026 FSC-klagomål mail.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18094-2026 tillsynsbegäran.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18094-2026 tillsynsbegäran mail.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>44549</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 5766-2026</t>
+          <t>A 63799-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46051</v>
+        <v>45278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,20 +1201,25 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1226,10 +1231,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1241,493 +1246,488 @@
         <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blåtryffel
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 63799-2023 artfynd.xlsx", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 63799-2023 karta.png", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 63799-2023 georefererad karta.tif", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 63799-2023 FSC-klagomål.docx", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 63799-2023 FSC-klagomål mail.docx", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 63799-2023 tillsynsbegäran.docx", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 63799-2023 tillsynsbegäran mail.docx", "A 63799-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 14114-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44651</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril
+Göktyta
+Sotnätfjäril</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 14114-2022 artfynd.xlsx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 14114-2022 karta.png", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 14114-2022 georefererad karta.tif", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 14114-2022 FSC-klagomål.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 14114-2022 FSC-klagomål mail.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 14114-2022 tillsynsbegäran.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 14114-2022 tillsynsbegäran mail.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 14114-2022 prioriterade fågelarter.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 5766-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Nästrot
 Svart trolldruva
 Blåsippa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 5766-2026 artfynd.xlsx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 5766-2026 karta.png", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 5766-2026 georefererad karta.tif", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 5766-2026 FSC-klagomål.docx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 5766-2026 FSC-klagomål mail.docx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 5766-2026 tillsynsbegäran.docx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 5766-2026 tillsynsbegäran mail.docx", "A 5766-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 12854-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>46092</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I10" t="n">
         <v>12.1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ävjepilört
 Springkorn
 Strutbräken</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12854-2026 artfynd.xlsx", "A 12854-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12854-2026 karta.png", "A 12854-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12854-2026 georefererad karta.tif", "A 12854-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12854-2026 FSC-klagomål.docx", "A 12854-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12854-2026 FSC-klagomål mail.docx", "A 12854-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12854-2026 tillsynsbegäran.docx", "A 12854-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12854-2026 tillsynsbegäran mail.docx", "A 12854-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 14114-2022</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44651</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 18103-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="I11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril
-Göktyta
-Sotnätfjäril</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 14114-2022 artfynd.xlsx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 14114-2022 karta.png", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 14114-2022 georefererad karta.tif", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 14114-2022 FSC-klagomål.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 14114-2022 FSC-klagomål mail.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 14114-2022 tillsynsbegäran.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 14114-2022 tillsynsbegäran mail.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 14114-2022 prioriterade fågelarter.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 18103-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46125</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Gransotdyna
 Mörk husmossa
 Blåsippa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18103-2026 artfynd.xlsx", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18103-2026 karta.png", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18103-2026 georefererad karta.tif", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18103-2026 FSC-klagomål.docx", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18103-2026 FSC-klagomål mail.docx", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18103-2026 tillsynsbegäran.docx", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18103-2026 tillsynsbegäran mail.docx", "A 18103-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 63799-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45278</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Blåtryffel
-Svart trolldruva
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 63799-2023 artfynd.xlsx", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 63799-2023 karta.png", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 63799-2023 georefererad karta.tif", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 63799-2023 FSC-klagomål.docx", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 63799-2023 FSC-klagomål mail.docx", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 63799-2023 tillsynsbegäran.docx", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 63799-2023 tillsynsbegäran mail.docx", "A 63799-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45764</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35334-2024</t>
+          <t>A 54189-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45530</v>
+        <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2188,17 +2188,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>24.8</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2228,46 +2228,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 54189-2021 artfynd.xlsx", "A 54189-2021")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 54189-2021 karta.png", "A 54189-2021")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 54189-2021 georefererad karta.tif", "A 54189-2021")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 54189-2021 FSC-klagomål.docx", "A 54189-2021")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 54189-2021 FSC-klagomål mail.docx", "A 54189-2021")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 54189-2021 tillsynsbegäran.docx", "A 54189-2021")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 54189-2021 tillsynsbegäran mail.docx", "A 54189-2021")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54189-2021</t>
+          <t>A 13208-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44470</v>
+        <v>45002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2296,19 +2296,14 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>24.8</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2338,46 +2333,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 54189-2021 artfynd.xlsx", "A 54189-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 13208-2023 artfynd.xlsx", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 54189-2021 karta.png", "A 54189-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 13208-2023 karta.png", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 54189-2021 georefererad karta.tif", "A 54189-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 13208-2023 georefererad karta.tif", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 54189-2021 FSC-klagomål.docx", "A 54189-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 13208-2023 FSC-klagomål.docx", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 54189-2021 FSC-klagomål mail.docx", "A 54189-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 13208-2023 FSC-klagomål mail.docx", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 54189-2021 tillsynsbegäran.docx", "A 54189-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 13208-2023 tillsynsbegäran.docx", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 54189-2021 tillsynsbegäran mail.docx", "A 54189-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 13208-2023 tillsynsbegäran mail.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 13208-2023 prioriterade fågelarter.docx", "A 13208-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13208-2023</t>
+          <t>A 60736-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2390,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45002</v>
+        <v>44913</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2407,7 +2406,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2416,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2431,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2443,50 +2442,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 13208-2023 artfynd.xlsx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 13208-2023 karta.png", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 13208-2023 georefererad karta.tif", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 13208-2023 FSC-klagomål.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 13208-2023 FSC-klagomål mail.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 13208-2023 tillsynsbegäran.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 13208-2023 tillsynsbegäran mail.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 13208-2023 prioriterade fågelarter.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 35573-2023</t>
+          <t>A 45484-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2500,10 +2499,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45147</v>
+        <v>45188</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2515,19 +2514,14 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2557,39 +2551,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35573-2023 artfynd.xlsx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 45484-2023 artfynd.xlsx", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35573-2023 karta.png", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 45484-2023 karta.png", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35573-2023 georefererad karta.tif", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 45484-2023 georefererad karta.tif", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35573-2023 FSC-klagomål.docx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 45484-2023 FSC-klagomål.docx", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35573-2023 FSC-klagomål mail.docx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 45484-2023 FSC-klagomål mail.docx", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35573-2023 tillsynsbegäran.docx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 45484-2023 tillsynsbegäran.docx", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35573-2023 tillsynsbegäran mail.docx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 45484-2023 tillsynsbegäran mail.docx", "A 45484-2023")</f>
         <v/>
       </c>
     </row>
@@ -2613,7 +2607,7 @@
         <v>44523</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2701,7 +2695,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53706-2022</t>
+          <t>A 31980-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2711,14 +2705,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44880</v>
+        <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,16 +2730,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>17.7</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2760,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2776,147 +2770,152 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 31980-2023 artfynd.xlsx", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 31980-2023 karta.png", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 31980-2023 georefererad karta.tif", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 31980-2023 FSC-klagomål.docx", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 31980-2023 FSC-klagomål mail.docx", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 31980-2023 tillsynsbegäran.docx", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 31980-2023 tillsynsbegäran mail.docx", "A 31980-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53706-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44880</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>Gullpudra</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 53706-2022 artfynd.xlsx", "A 53706-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 53706-2022 karta.png", "A 53706-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 53706-2022 georefererad karta.tif", "A 53706-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 53706-2022 FSC-klagomål.docx", "A 53706-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 53706-2022 FSC-klagomål mail.docx", "A 53706-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 53706-2022 tillsynsbegäran.docx", "A 53706-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 53706-2022 tillsynsbegäran mail.docx", "A 53706-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 45484-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45188</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 45484-2023 artfynd.xlsx", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 45484-2023 karta.png", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 45484-2023 georefererad karta.tif", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 45484-2023 FSC-klagomål.docx", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 45484-2023 FSC-klagomål mail.docx", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 45484-2023 tillsynsbegäran.docx", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 45484-2023 tillsynsbegäran mail.docx", "A 45484-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31980-2023</t>
+          <t>A 35334-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2926,14 +2925,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45119</v>
+        <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2947,17 +2946,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2991,42 +2990,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 31980-2023 artfynd.xlsx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 31980-2023 karta.png", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 31980-2023 georefererad karta.tif", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 31980-2023 FSC-klagomål.docx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 31980-2023 FSC-klagomål mail.docx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 31980-2023 tillsynsbegäran.docx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 31980-2023 tillsynsbegäran mail.docx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60736-2022</t>
+          <t>A 46620-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3040,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44913</v>
+        <v>45583</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3056,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3065,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3080,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3089,53 +3088,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46620-2024</t>
+          <t>A 35573-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3149,10 +3144,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45583</v>
+        <v>45147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,8 +3159,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3198,42 +3198,42 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35573-2023 artfynd.xlsx", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35573-2023 karta.png", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35573-2023 georefererad karta.tif", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35573-2023 FSC-klagomål.docx", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35573-2023 FSC-klagomål mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35573-2023 tillsynsbegäran.docx", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35573-2023 tillsynsbegäran mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>44785</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35831-2023</t>
+          <t>A 7289-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45148</v>
+        <v>44606</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5014,13 +5014,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5063,7 +5058,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35863-2023</t>
+          <t>A 67198-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5077,10 +5072,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45148</v>
+        <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5092,13 +5087,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5158,7 +5148,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5214,7 +5204,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7289-2022</t>
+          <t>A 23451-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5228,10 +5218,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44606</v>
+        <v>45453</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5244,7 +5234,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5287,7 +5277,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 46530-2023</t>
+          <t>A 6947-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5297,14 +5287,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45197</v>
+        <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5322,7 +5312,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5365,7 +5355,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 67198-2021</t>
+          <t>A 34427-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5375,14 +5365,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44523</v>
+        <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5394,8 +5384,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5438,7 +5433,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22619-2025</t>
+          <t>A 39213-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5452,10 +5447,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45789</v>
+        <v>45166</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5469,11 +5464,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5516,7 +5511,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10996-2025</t>
+          <t>A 50635-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5530,10 +5525,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45723</v>
+        <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5546,7 +5541,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5589,7 +5584,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35940-2024</t>
+          <t>A 7273-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5603,10 +5598,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45533</v>
+        <v>44970</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5619,7 +5614,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5662,7 +5657,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16885-2025</t>
+          <t>A 28327-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5676,10 +5671,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45755</v>
+        <v>44747</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5692,7 +5687,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5735,7 +5730,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26037-2023</t>
+          <t>A 53573-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5749,10 +5744,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45091</v>
+        <v>45614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5765,7 +5760,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5808,7 +5803,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 71625-2021</t>
+          <t>A 18439-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5822,10 +5817,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44542</v>
+        <v>45762</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5837,8 +5832,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8952-2024</t>
+          <t>A 46530-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45355</v>
+        <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5910,8 +5910,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5954,7 +5959,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33218-2023</t>
+          <t>A 73267-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5968,10 +5973,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45127</v>
+        <v>44550</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5983,13 +5988,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6032,7 +6032,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61457-2022</t>
+          <t>A 26037-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44916</v>
+        <v>45091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6105,7 +6105,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53074-2022</t>
+          <t>A 35335-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6119,10 +6119,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44876</v>
+        <v>45530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6134,8 +6134,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6178,7 +6183,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56748-2022</t>
+          <t>A 35863-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6192,10 +6197,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44894</v>
+        <v>45148</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6209,11 +6214,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6256,7 +6261,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34786-2024</t>
+          <t>A 48647-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6270,10 +6275,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45526</v>
+        <v>45593</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6285,13 +6290,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6334,7 +6334,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29231-2023</t>
+          <t>A 14382-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6344,14 +6344,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45105</v>
+        <v>45012</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6363,8 +6363,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6407,7 +6412,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28242-2024</t>
+          <t>A 2812-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6421,10 +6426,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45477</v>
+        <v>44944</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6437,7 +6442,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6480,7 +6485,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28271-2024</t>
+          <t>A 6909-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6490,14 +6495,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45477</v>
+        <v>45701</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6509,8 +6514,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6553,7 +6563,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19323-2023</t>
+          <t>A 9693-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6567,10 +6577,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45049</v>
+        <v>45716</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6582,8 +6592,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6626,7 +6641,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40080-2025</t>
+          <t>A 6118-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6640,10 +6655,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45894</v>
+        <v>45337</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6656,7 +6671,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6699,7 +6714,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39748-2025</t>
+          <t>A 13198-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6713,10 +6728,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45891</v>
+        <v>45386</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6728,13 +6743,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6777,7 +6787,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29188-2025</t>
+          <t>A 33218-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6791,10 +6801,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45821</v>
+        <v>45127</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6806,8 +6816,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6850,7 +6865,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30853-2025</t>
+          <t>A 33224-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6864,10 +6879,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45831</v>
+        <v>45127</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6879,8 +6894,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6923,7 +6943,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32680-2023</t>
+          <t>A 64121-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6933,14 +6953,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45121</v>
+        <v>45279</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6952,13 +6972,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7001,7 +7016,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40744-2025</t>
+          <t>A 16885-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7015,10 +7030,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45897</v>
+        <v>45755</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7030,13 +7045,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7079,7 +7089,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35335-2024</t>
+          <t>A 20862-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7093,10 +7103,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45530</v>
+        <v>45439</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7108,13 +7118,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7157,7 +7162,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 73267-2021</t>
+          <t>A 27995-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7171,10 +7176,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44550</v>
+        <v>45476</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7187,7 +7192,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7230,7 +7235,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42441-2025</t>
+          <t>A 19823-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7244,10 +7249,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45905</v>
+        <v>46135</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7260,7 +7265,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7303,7 +7308,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48630-2024</t>
+          <t>A 17135-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7317,10 +7322,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45593</v>
+        <v>45755</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7333,7 +7338,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7376,7 +7381,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 27995-2024</t>
+          <t>A 9524-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7386,14 +7391,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45476</v>
+        <v>45359</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7405,8 +7410,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7449,7 +7459,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42572-2025</t>
+          <t>A 65915-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7463,10 +7473,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45905</v>
+        <v>44517</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7479,7 +7489,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>12.5</v>
+        <v>17.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7522,7 +7532,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29427-2024</t>
+          <t>A 39407-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7536,10 +7546,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45483</v>
+        <v>45551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7552,7 +7562,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7595,7 +7605,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34849-2024</t>
+          <t>A 39748-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7605,14 +7615,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45527</v>
+        <v>45891</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7626,11 +7636,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7673,7 +7683,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 23451-2024</t>
+          <t>A 30853-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7687,10 +7697,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45453</v>
+        <v>45831</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7703,7 +7713,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7746,7 +7756,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15553-2022</t>
+          <t>A 53678-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7760,10 +7770,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44662</v>
+        <v>45960</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7776,7 +7786,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7819,7 +7829,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 25462-2025</t>
+          <t>A 29188-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7833,10 +7843,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45802</v>
+        <v>45821</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7848,13 +7858,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7897,7 +7902,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28321-2023</t>
+          <t>A 17519-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7911,10 +7916,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45099</v>
+        <v>45415</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7926,8 +7931,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7970,7 +7980,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35855-2023</t>
+          <t>A 40080-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7984,10 +7994,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45148</v>
+        <v>45894</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7999,13 +8009,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8048,7 +8053,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 25008-2023</t>
+          <t>A 40744-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8062,10 +8067,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45085</v>
+        <v>45897</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8077,8 +8082,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8121,7 +8131,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33219-2023</t>
+          <t>A 11196-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8135,10 +8145,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45127</v>
+        <v>45371</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8150,13 +8160,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8199,7 +8204,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48590-2024</t>
+          <t>A 28242-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8209,14 +8214,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45593</v>
+        <v>45477</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8228,13 +8233,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8277,7 +8277,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13198-2024</t>
+          <t>A 42441-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45386</v>
+        <v>45905</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11765-2025</t>
+          <t>A 42572-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45727</v>
+        <v>45905</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8379,13 +8379,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8428,7 +8423,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 20244-2023</t>
+          <t>A 58688-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8442,10 +8437,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45055</v>
+        <v>45251</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8458,7 +8453,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8501,7 +8496,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17519-2024</t>
+          <t>A 35855-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8515,10 +8510,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45415</v>
+        <v>45148</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8532,11 +8527,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8579,7 +8574,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 65915-2021</t>
+          <t>A 32796-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8593,10 +8588,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44517</v>
+        <v>45124</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8608,8 +8603,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>17.2</v>
+        <v>5.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 46868-2025</t>
+          <t>A 32822-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45929</v>
+        <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8681,8 +8681,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8725,7 +8730,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62922-2023</t>
+          <t>A 28271-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45272</v>
+        <v>45477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8755,7 +8760,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8798,7 +8803,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34886-2024</t>
+          <t>A 34849-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8808,14 +8813,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8833,7 +8838,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8876,7 +8881,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47893-2025</t>
+          <t>A 34886-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8890,10 +8895,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45932</v>
+        <v>45527</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8905,8 +8910,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8949,7 +8959,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47917-2025</t>
+          <t>A 58121-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8963,10 +8973,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45932</v>
+        <v>45632</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8979,7 +8989,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9022,7 +9032,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 47940-2025</t>
+          <t>A 46868-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9036,10 +9046,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45932</v>
+        <v>45929</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9052,7 +9062,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9095,7 +9105,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32796-2023</t>
+          <t>A 18229-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9109,10 +9119,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45124</v>
+        <v>45761</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9124,13 +9134,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9173,7 +9178,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26869-2024</t>
+          <t>A 47893-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9183,14 +9188,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45470</v>
+        <v>45932</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9202,13 +9207,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9251,7 +9251,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 2818-2022</t>
+          <t>A 54170-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44581</v>
+        <v>44881</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>11</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9324,7 +9324,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 33222-2023</t>
+          <t>A 29427-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45127</v>
+        <v>45483</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9353,13 +9353,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9402,7 +9397,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33229-2023</t>
+          <t>A 15563-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9416,10 +9411,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45127</v>
+        <v>44662</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9431,13 +9426,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9480,7 +9470,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7273-2023</t>
+          <t>A 47917-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9494,10 +9484,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44970</v>
+        <v>45932</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9510,7 +9500,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9553,7 +9543,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20862-2024</t>
+          <t>A 47940-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9567,10 +9557,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45439</v>
+        <v>45932</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9583,7 +9573,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>9.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9626,7 +9616,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6909-2025</t>
+          <t>A 60850-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9636,14 +9626,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45701</v>
+        <v>45999</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9655,13 +9645,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9704,7 +9689,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 33224-2023</t>
+          <t>A 51123-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9718,10 +9703,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45127</v>
+        <v>45947</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9733,13 +9718,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9782,7 +9762,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2278-2022</t>
+          <t>A 46300-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9796,10 +9776,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44578</v>
+        <v>44847</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9811,13 +9791,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9860,7 +9835,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 39407-2024</t>
+          <t>A 56280-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9874,10 +9849,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45551</v>
+        <v>45241</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9890,7 +9865,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9933,7 +9908,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51123-2025</t>
+          <t>A 47734-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9947,10 +9922,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45947</v>
+        <v>45931</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9962,8 +9937,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10006,7 +9986,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 14988-2024</t>
+          <t>A 10989-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10020,10 +10000,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45399</v>
+        <v>45723</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10036,7 +10016,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10079,7 +10059,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 2843-2022</t>
+          <t>A 65062-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10093,10 +10073,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44581</v>
+        <v>45287</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10108,8 +10088,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2.7</v>
+        <v>11.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10152,7 +10137,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 58688-2023</t>
+          <t>A 58714-2021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10166,10 +10151,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45251</v>
+        <v>44489</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10182,7 +10167,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10225,7 +10210,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 14382-2023</t>
+          <t>A 67617-2021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10235,14 +10220,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45012</v>
+        <v>44524</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10254,13 +10239,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10303,7 +10283,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61463-2022</t>
+          <t>A 55835-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10317,10 +10297,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44916</v>
+        <v>45623</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10333,7 +10313,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10376,7 +10356,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 7299-2023</t>
+          <t>A 30859-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10390,10 +10370,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44970</v>
+        <v>45497</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10406,7 +10386,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10449,7 +10429,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 53596-2024</t>
+          <t>A 35831-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10463,10 +10443,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45614</v>
+        <v>45148</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10478,8 +10458,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10522,7 +10507,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19996-2022</t>
+          <t>A 22582-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10532,14 +10517,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44697</v>
+        <v>45447</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10551,8 +10536,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10595,7 +10585,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 29852-2022</t>
+          <t>A 7297-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10609,10 +10599,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44756</v>
+        <v>44970</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10625,7 +10615,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10668,7 +10658,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21295-2023</t>
+          <t>A 15663-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10678,14 +10668,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45062</v>
+        <v>45404</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10697,13 +10687,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10746,7 +10731,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19069-2025</t>
+          <t>A 55433-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10760,10 +10745,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45765</v>
+        <v>45971</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10776,7 +10761,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>14.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10819,7 +10804,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12484-2022</t>
+          <t>A 1409-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10833,10 +10818,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44638</v>
+        <v>45667</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10849,7 +10834,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10892,7 +10877,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35850-2023</t>
+          <t>A 59298-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10906,10 +10891,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45148</v>
+        <v>45988</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10921,13 +10906,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10970,7 +10950,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 58121-2024</t>
+          <t>A 21106-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10984,10 +10964,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45632</v>
+        <v>46146</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10999,8 +10979,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>8.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11043,7 +11028,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 9524-2024</t>
+          <t>A 21081-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11053,14 +11038,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45359</v>
+        <v>46146</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11074,11 +11059,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>14.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11121,7 +11106,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 55835-2024</t>
+          <t>A 21137-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11135,10 +11120,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45623</v>
+        <v>46146</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11151,7 +11136,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11194,7 +11179,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 53573-2024</t>
+          <t>A 59090-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11208,10 +11193,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45614</v>
+        <v>45988</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11267,7 +11252,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60045-2022</t>
+          <t>A 60893-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11281,10 +11266,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44902</v>
+        <v>45999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11297,7 +11282,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11340,7 +11325,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 8399-2025</t>
+          <t>A 21146-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11350,14 +11335,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45709</v>
+        <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11369,13 +11354,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11418,7 +11398,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 55433-2025</t>
+          <t>A 59933-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11432,10 +11412,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45971</v>
+        <v>45993</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11447,8 +11427,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>14.2</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11491,7 +11476,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 55249-2023</t>
+          <t>A 21634-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11505,10 +11490,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45237</v>
+        <v>46149</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11521,7 +11506,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11564,7 +11549,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 67617-2021</t>
+          <t>A 59919-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11578,10 +11563,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44524</v>
+        <v>45993</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11593,8 +11578,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11637,7 +11627,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 59090-2025</t>
+          <t>A 22192-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11651,10 +11641,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45988</v>
+        <v>46153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11667,7 +11657,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11710,7 +11700,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 39213-2023</t>
+          <t>A 22222-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11724,10 +11714,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45166</v>
+        <v>46153</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11739,13 +11729,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11788,7 +11773,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 23117-2023</t>
+          <t>A 59955-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11802,10 +11787,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45075</v>
+        <v>45993</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11823,7 +11808,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11866,7 +11851,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 59298-2025</t>
+          <t>A 22221-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11880,10 +11865,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45988</v>
+        <v>46153</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11896,7 +11881,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11939,7 +11924,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 48647-2024</t>
+          <t>A 19996-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11953,10 +11938,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45593</v>
+        <v>44697</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11969,7 +11954,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12012,7 +11997,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59933-2025</t>
+          <t>A 63318-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12026,10 +12011,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45993</v>
+        <v>45274</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12041,13 +12026,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12090,7 +12070,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 59919-2025</t>
+          <t>A 61896-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12104,10 +12084,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12119,13 +12099,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12168,7 +12143,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 59955-2025</t>
+          <t>A 60045-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12182,10 +12157,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45993</v>
+        <v>44902</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12197,13 +12172,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12246,7 +12216,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 18439-2025</t>
+          <t>A 10383-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12260,10 +12230,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45762</v>
+        <v>44987</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12275,13 +12245,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12324,7 +12289,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 40968-2022</t>
+          <t>A 21745-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12338,10 +12303,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44823</v>
+        <v>45442</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12354,7 +12319,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>16.5</v>
+        <v>2.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12397,7 +12362,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 64121-2023</t>
+          <t>A 21836-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12407,14 +12372,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45279</v>
+        <v>45784</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12427,7 +12392,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.1</v>
+        <v>4.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12470,7 +12435,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31831-2025</t>
+          <t>A 22362-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12484,10 +12449,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45834</v>
+        <v>45446</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12500,7 +12465,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12543,7 +12508,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 827-2026</t>
+          <t>A 29852-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12557,10 +12522,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46030</v>
+        <v>44756</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12573,7 +12538,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12616,7 +12581,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 34427-2024</t>
+          <t>A 23505-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12626,14 +12591,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45525</v>
+        <v>46163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12647,11 +12612,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12694,7 +12659,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 61896-2025</t>
+          <t>A 23516-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12708,10 +12673,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46003</v>
+        <v>46163</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12723,8 +12688,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12767,7 +12737,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 12320-2024</t>
+          <t>A 827-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12777,14 +12747,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45378</v>
+        <v>46030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12796,13 +12766,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12845,7 +12810,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 31968-2025</t>
+          <t>A 56748-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12859,10 +12824,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45835</v>
+        <v>44894</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12874,8 +12839,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12935,7 +12905,7 @@
         <v>45237</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13008,7 +12978,7 @@
         <v>44550</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13081,7 +13051,7 @@
         <v>44550</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13137,7 +13107,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 21745-2024</t>
+          <t>A 7299-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13151,10 +13121,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45442</v>
+        <v>44970</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13167,7 +13137,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13210,7 +13180,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 61231-2022</t>
+          <t>A 28517-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13224,10 +13194,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44915</v>
+        <v>45478</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13239,8 +13209,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13283,7 +13258,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22362-2024</t>
+          <t>A 42370-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13293,14 +13268,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45446</v>
+        <v>45905</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13312,8 +13287,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13356,7 +13336,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 42370-2025</t>
+          <t>A 14988-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13366,14 +13346,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45905</v>
+        <v>45399</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13385,13 +13365,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13451,7 +13426,7 @@
         <v>46052</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13507,7 +13482,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 1338-2023</t>
+          <t>A 48630-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13521,10 +13496,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44936</v>
+        <v>45593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13537,7 +13512,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13580,7 +13555,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 35654-2024</t>
+          <t>A 62922-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13594,10 +13569,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45532</v>
+        <v>45272</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13610,7 +13585,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13653,7 +13628,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 39366-2026</t>
+          <t>A 53074-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13667,10 +13642,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46288</v>
+        <v>44876</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13683,7 +13658,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13726,7 +13701,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 20928-2024</t>
+          <t>A 35850-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13740,10 +13715,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45439</v>
+        <v>45148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13755,8 +13730,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13799,7 +13779,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 33085-2026</t>
+          <t>A 2278-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13813,10 +13793,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46245</v>
+        <v>44578</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13834,7 +13814,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>10.6</v>
+        <v>3.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13877,7 +13857,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 33136-2026</t>
+          <t>A 32680-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13891,10 +13871,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46245</v>
+        <v>45121</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13908,11 +13888,11 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13955,7 +13935,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 33054-2026</t>
+          <t>A 61457-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13969,10 +13949,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46245</v>
+        <v>44916</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13984,13 +13964,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14033,7 +14008,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 33055-2026</t>
+          <t>A 40968-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14047,10 +14022,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46245</v>
+        <v>44823</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14062,13 +14037,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>11.8</v>
+        <v>16.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14111,7 +14081,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 39368-2026</t>
+          <t>A 10987-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14125,10 +14095,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46288</v>
+        <v>46079</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14140,8 +14110,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14184,7 +14159,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 10987-2026</t>
+          <t>A 12484-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14198,10 +14173,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46079</v>
+        <v>44638</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14213,13 +14188,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14262,7 +14232,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 12086-2026</t>
+          <t>A 19069-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14272,14 +14242,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46086</v>
+        <v>45765</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14291,13 +14261,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14340,7 +14305,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 7297-2023</t>
+          <t>A 70214-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14354,10 +14319,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44970</v>
+        <v>44535</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14370,7 +14335,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14413,7 +14378,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 33227-2023</t>
+          <t>A 12086-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14423,14 +14388,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45127</v>
+        <v>46086</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14444,11 +14409,11 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14491,7 +14456,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 38261-2022</t>
+          <t>A 61231-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14505,10 +14470,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44812</v>
+        <v>44915</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14521,7 +14486,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14564,7 +14529,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 54170-2022</t>
+          <t>A 2818-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14578,10 +14543,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44881</v>
+        <v>44581</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14594,7 +14559,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14637,7 +14602,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 24036-2023</t>
+          <t>A 7919-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14651,10 +14616,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45078</v>
+        <v>44973</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14710,7 +14675,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 60043-2022</t>
+          <t>A 33222-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14724,10 +14689,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44902</v>
+        <v>45127</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14739,8 +14704,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14783,7 +14753,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 15563-2022</t>
+          <t>A 33229-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14797,10 +14767,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44662</v>
+        <v>45127</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14812,8 +14782,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14856,7 +14831,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 16109-2026</t>
+          <t>A 26325-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14870,10 +14845,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46108</v>
+        <v>46182</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14885,13 +14860,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14934,7 +14904,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 56280-2023</t>
+          <t>A 26104-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14948,10 +14918,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45241</v>
+        <v>46181</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14964,7 +14934,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15007,7 +14977,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 58714-2021</t>
+          <t>A 15553-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15021,10 +14991,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44489</v>
+        <v>44662</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15037,7 +15007,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>7.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15080,7 +15050,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 17720-2026</t>
+          <t>A 26129-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15094,10 +15064,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46121</v>
+        <v>46181</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15110,7 +15080,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15153,7 +15123,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 17897-2026</t>
+          <t>A 27075-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15167,10 +15137,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46122</v>
+        <v>46186</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15182,13 +15152,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>8.4</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15231,7 +15196,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 18285-2026</t>
+          <t>A 27080-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15245,10 +15210,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46126</v>
+        <v>46186</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15261,7 +15226,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15304,7 +15269,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 19079-2026</t>
+          <t>A 35940-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15318,10 +15283,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46132</v>
+        <v>45533</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15334,7 +15299,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>10.1</v>
+        <v>6.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15377,7 +15342,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 18916-2026</t>
+          <t>A 27076-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15391,10 +15356,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46129</v>
+        <v>46186</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15406,13 +15371,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15455,7 +15415,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 28517-2024</t>
+          <t>A 27252-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15469,10 +15429,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45478</v>
+        <v>46188</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15484,13 +15444,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15533,7 +15488,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 7919-2023</t>
+          <t>A 48590-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15543,14 +15498,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44973</v>
+        <v>45593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15562,8 +15517,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15606,7 +15566,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 19823-2026</t>
+          <t>A 16109-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15620,10 +15580,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46135</v>
+        <v>46108</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15635,8 +15595,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15679,7 +15644,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 53585-2024</t>
+          <t>A 12320-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15689,14 +15654,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45614</v>
+        <v>45378</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15708,8 +15673,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15752,7 +15722,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 10383-2023</t>
+          <t>A 53596-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15766,10 +15736,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44987</v>
+        <v>45614</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15782,7 +15752,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15825,7 +15795,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 2812-2023</t>
+          <t>A 17897-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15839,10 +15809,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44944</v>
+        <v>46122</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15854,8 +15824,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>8.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15898,7 +15873,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 17135-2025</t>
+          <t>A 17720-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15912,10 +15887,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45755</v>
+        <v>46121</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15928,7 +15903,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>10.3</v>
+        <v>0.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15971,7 +15946,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 46300-2022</t>
+          <t>A 71625-2021</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15985,10 +15960,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44847</v>
+        <v>44542</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16001,7 +15976,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16044,7 +16019,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 53678-2025</t>
+          <t>A 24036-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16058,10 +16033,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45960</v>
+        <v>45078</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16074,7 +16049,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16117,7 +16092,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 32795-2023</t>
+          <t>A 18285-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16131,10 +16106,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45124</v>
+        <v>46126</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16146,13 +16121,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16195,7 +16165,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 47734-2025</t>
+          <t>A 18916-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16209,10 +16179,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45931</v>
+        <v>46129</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16226,11 +16196,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16273,7 +16243,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 11196-2024</t>
+          <t>A 23020-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16287,10 +16257,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45371</v>
+        <v>44719</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16303,7 +16273,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16346,7 +16316,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 32822-2023</t>
+          <t>A 19079-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16360,10 +16330,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45124</v>
+        <v>46132</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16375,13 +16345,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>10.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16441,7 +16406,7 @@
         <v>45124</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16502,7 +16467,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 34861-2022</t>
+          <t>A 29231-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16516,10 +16481,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44796</v>
+        <v>45105</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16532,7 +16497,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16575,7 +16540,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 18229-2025</t>
+          <t>A 29116-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16589,10 +16554,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45761</v>
+        <v>46201</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16605,7 +16570,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16648,7 +16613,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 1409-2025</t>
+          <t>A 25008-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16662,10 +16627,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45667</v>
+        <v>45085</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16678,7 +16643,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16721,7 +16686,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 60850-2025</t>
+          <t>A 29265-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16735,10 +16700,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45999</v>
+        <v>46202</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16751,7 +16716,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16794,7 +16759,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 6118-2024</t>
+          <t>A 38261-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16808,10 +16773,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45337</v>
+        <v>44812</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16824,7 +16789,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16867,7 +16832,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 22582-2024</t>
+          <t>A 34786-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16877,14 +16842,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45447</v>
+        <v>45526</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16902,7 +16867,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16945,7 +16910,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 50635-2023</t>
+          <t>A 33219-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16959,10 +16924,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45217</v>
+        <v>45127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16974,8 +16939,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17018,7 +16988,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 10989-2025</t>
+          <t>A 33887-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17032,10 +17002,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45723</v>
+        <v>46251</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17047,8 +17017,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17091,7 +17066,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 65062-2023</t>
+          <t>A 33741-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17105,10 +17080,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45287</v>
+        <v>46251</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17126,7 +17101,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>11.3</v>
+        <v>6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17169,7 +17144,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 28327-2022</t>
+          <t>A 30380-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17183,10 +17158,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44747</v>
+        <v>46209</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17199,7 +17174,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17242,7 +17217,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 15663-2024</t>
+          <t>A 30374-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17252,14 +17227,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45404</v>
+        <v>46209</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17272,7 +17247,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17315,7 +17290,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 9693-2025</t>
+          <t>A 8399-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17325,14 +17300,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45716</v>
+        <v>45709</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17350,7 +17325,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17393,7 +17368,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 30859-2024</t>
+          <t>A 34637-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17407,10 +17382,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45497</v>
+        <v>46255</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17423,7 +17398,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17466,7 +17441,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 58114-2024</t>
+          <t>A 55249-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17480,10 +17455,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17496,7 +17471,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17539,7 +17514,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 6947-2025</t>
+          <t>A 28321-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17549,14 +17524,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45701</v>
+        <v>45099</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17568,13 +17543,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17617,7 +17587,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 21081-2026</t>
+          <t>A 58114-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17631,10 +17601,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46146</v>
+        <v>45632</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17646,13 +17616,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>14.8</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17695,7 +17660,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21137-2026</t>
+          <t>A 60043-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17709,10 +17674,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46146</v>
+        <v>44902</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17725,7 +17690,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17768,7 +17733,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 60893-2025</t>
+          <t>A 10996-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17782,10 +17747,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45999</v>
+        <v>45723</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17798,7 +17763,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17841,7 +17806,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21106-2026</t>
+          <t>A 2843-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17855,10 +17820,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46146</v>
+        <v>44581</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17870,13 +17835,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17919,7 +17879,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 21146-2026</t>
+          <t>A 20933-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17933,10 +17893,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46146</v>
+        <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17949,7 +17909,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.4</v>
+        <v>11.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17992,7 +17952,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 21634-2026</t>
+          <t>A 31480-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18002,14 +17962,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46149</v>
+        <v>46222</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18022,7 +17982,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18065,7 +18025,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 22221-2026</t>
+          <t>A 21295-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18079,10 +18039,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46153</v>
+        <v>45062</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18094,8 +18054,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18138,7 +18103,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 22192-2026</t>
+          <t>A 32795-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18152,10 +18117,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46153</v>
+        <v>45124</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18167,8 +18132,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18211,7 +18181,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 35336-2024</t>
+          <t>A 35654-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18225,10 +18195,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45530</v>
+        <v>45532</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18240,13 +18210,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18289,7 +18254,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 22222-2026</t>
+          <t>A 23117-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18303,10 +18268,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46153</v>
+        <v>45075</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18318,8 +18283,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18362,7 +18332,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 63318-2023</t>
+          <t>A 53585-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18376,10 +18346,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45274</v>
+        <v>45614</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18392,7 +18362,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18435,7 +18405,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 21836-2025</t>
+          <t>A 34861-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18449,10 +18419,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45784</v>
+        <v>44796</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18465,7 +18435,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18508,7 +18478,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 23516-2026</t>
+          <t>A 1338-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18522,10 +18492,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46163</v>
+        <v>44936</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18537,13 +18507,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18586,7 +18551,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 23505-2026</t>
+          <t>A 61463-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18600,10 +18565,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46163</v>
+        <v>44916</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18615,13 +18580,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18664,7 +18624,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 70214-2021</t>
+          <t>A 33227-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18678,10 +18638,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44535</v>
+        <v>45127</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18693,8 +18653,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18737,7 +18702,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 26104-2026</t>
+          <t>A 19323-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18751,10 +18716,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46181</v>
+        <v>45049</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18767,7 +18732,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18810,7 +18775,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 26129-2026</t>
+          <t>A 35336-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18824,10 +18789,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46181</v>
+        <v>45530</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18839,8 +18804,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18883,7 +18853,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 26325-2026</t>
+          <t>A 22619-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18897,10 +18867,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46182</v>
+        <v>45789</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18912,8 +18882,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18956,7 +18931,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 27080-2026</t>
+          <t>A 20928-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18970,10 +18945,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46186</v>
+        <v>45439</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18986,7 +18961,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19029,7 +19004,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 27075-2026</t>
+          <t>A 33085-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19043,10 +19018,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46186</v>
+        <v>46245</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19058,8 +19033,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>0.7</v>
+        <v>10.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19102,7 +19082,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 27076-2026</t>
+          <t>A 33136-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19116,10 +19096,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46186</v>
+        <v>46245</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19131,8 +19111,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19175,7 +19160,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 27252-2026</t>
+          <t>A 39507-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19189,10 +19174,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46188</v>
+        <v>46289</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19205,7 +19190,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19248,7 +19233,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 23020-2022</t>
+          <t>A 8952-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19262,10 +19247,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44719</v>
+        <v>45355</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19278,7 +19263,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19321,7 +19306,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 29116-2026</t>
+          <t>A 39366-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19335,10 +19320,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46201</v>
+        <v>46288</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19351,7 +19336,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.1</v>
+        <v>9.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19394,7 +19379,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 29265-2026</t>
+          <t>A 39368-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19408,10 +19393,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46202</v>
+        <v>46288</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19424,7 +19409,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19467,7 +19452,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 33887-2026</t>
+          <t>A 33054-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19481,10 +19466,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19502,7 +19487,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19545,7 +19530,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 33741-2026</t>
+          <t>A 33055-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19559,10 +19544,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19580,7 +19565,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>6</v>
+        <v>11.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19623,7 +19608,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 30374-2026</t>
+          <t>A 25462-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19637,10 +19622,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46209</v>
+        <v>45802</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19652,8 +19637,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19696,7 +19686,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 30380-2026</t>
+          <t>A 20244-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19710,10 +19700,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46209</v>
+        <v>45055</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19726,7 +19716,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19769,7 +19759,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 34637-2026</t>
+          <t>A 11765-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19783,10 +19773,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46255</v>
+        <v>45727</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19798,8 +19788,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19842,7 +19837,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 20933-2024</t>
+          <t>A 26869-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19852,14 +19847,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45439</v>
+        <v>45470</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19871,8 +19866,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>11.3</v>
+        <v>2.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 31480-2026</t>
+          <t>A 31831-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19925,14 +19925,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46222</v>
+        <v>45834</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19988,24 +19988,24 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>S 915-2022</t>
+          <t>A 31968-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44606</v>
+        <v>45835</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20017,13 +20017,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>18.1</v>
+        <v>0.7</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20066,7 +20061,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>S 870-2022</t>
+          <t>S 5497-2022</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20080,10 +20075,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44606</v>
+        <v>44834</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20101,7 +20096,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>15.1</v>
+        <v>31.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20144,7 +20139,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>S 933-2022</t>
+          <t>S 4414-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20158,10 +20153,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20179,7 +20174,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>40.7</v>
+        <v>21</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20222,7 +20217,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>S 5497-2022</t>
+          <t>S 4411-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20236,10 +20231,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44834</v>
+        <v>45266</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20257,7 +20252,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>31.1</v>
+        <v>7.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20300,7 +20295,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>S 4414-2023</t>
+          <t>S 915-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20314,10 +20309,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20335,7 +20330,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>21</v>
+        <v>18.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20378,7 +20373,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>S 4411-2023</t>
+          <t>S 6974-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20392,10 +20387,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20413,7 +20408,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>7.3</v>
+        <v>28.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20456,7 +20451,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>S 6974-2022</t>
+          <t>S 6964-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20473,7 +20468,7 @@
         <v>44901</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20491,7 +20486,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>28.8</v>
+        <v>18.8</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20534,7 +20529,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>S 6964-2022</t>
+          <t>S 4403-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20548,10 +20543,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20569,7 +20564,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>18.8</v>
+        <v>67.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20612,7 +20607,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>S 4403-2023</t>
+          <t>S 4429-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20629,7 +20624,7 @@
         <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20647,7 +20642,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>67.7</v>
+        <v>80.3</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20690,7 +20685,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>S 4429-2023</t>
+          <t>S 870-2022</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20704,10 +20699,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20725,7 +20720,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>80.3</v>
+        <v>15.1</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20765,78 +20760,156 @@
       </c>
       <c r="V259" s="2" t="inlineStr"/>
     </row>
-    <row r="260">
+    <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
+          <t>S 933-2022</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="n">
+        <v>44606</v>
+      </c>
+      <c r="E260" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" t="n">
+        <v>0</v>
+      </c>
+      <c r="M260" t="n">
+        <v>0</v>
+      </c>
+      <c r="N260" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>0</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="n">
+        <v>0</v>
+      </c>
+      <c r="T260" t="n">
+        <v>0</v>
+      </c>
+      <c r="U260" t="n">
+        <v>0</v>
+      </c>
+      <c r="V260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
           <t>S 2011-2025</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D260" s="1" t="n">
+      <c r="D261" s="1" t="n">
         <v>45834</v>
       </c>
-      <c r="E260" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I260" t="n">
+      <c r="E261" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
         <v>0.5</v>
       </c>
-      <c r="J260" t="n">
-        <v>0</v>
-      </c>
-      <c r="K260" t="n">
-        <v>0</v>
-      </c>
-      <c r="L260" t="n">
-        <v>0</v>
-      </c>
-      <c r="M260" t="n">
-        <v>0</v>
-      </c>
-      <c r="N260" t="n">
-        <v>0</v>
-      </c>
-      <c r="O260" t="n">
-        <v>0</v>
-      </c>
-      <c r="P260" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
-      <c r="R260" t="n">
-        <v>0</v>
-      </c>
-      <c r="S260" t="n">
-        <v>0</v>
-      </c>
-      <c r="T260" t="n">
-        <v>0</v>
-      </c>
-      <c r="U260" t="n">
-        <v>0</v>
-      </c>
-      <c r="V260" s="2" t="inlineStr"/>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0</v>
+      </c>
+      <c r="M261" t="n">
+        <v>0</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>0</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0</v>
+      </c>
+      <c r="S261" t="n">
+        <v>0</v>
+      </c>
+      <c r="T261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="n">
+        <v>0</v>
+      </c>
+      <c r="V261" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45526</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46125</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>44517</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>44549</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>46125</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45278</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>44651</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45764</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45147</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44880</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>45530</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>45002</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>44913</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>44785</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>44606</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>45723</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45533</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>44542</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45091</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45197</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>44876</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44894</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45355</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>46030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45477</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45527</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>45477</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44662</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45891</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45821</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>45831</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45897</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45148</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>45905</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45905</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>46052</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>44517</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45905</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>45272</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45527</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45802</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>45127</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45127</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>46079</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45932</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>45932</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45055</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>46086</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45399</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45251</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45012</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>44916</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44970</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44756</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45062</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45947</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45470</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>46108</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45632</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>45359</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>46121</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>46122</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>46126</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44524</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>46132</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45166</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>46129</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45075</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>45971</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45593</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>46135</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>45988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45960</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>45988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45993</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45148</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45148</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45993</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45371</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>46003</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>45999</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45442</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45446</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>45755</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>46146</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>46146</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>46146</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>45127</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>46149</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>45834</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>46153</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>46153</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>46153</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45526</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45835</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45105</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>45274</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>45784</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45049</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>46163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45121</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>46163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>44550</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45593</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44535</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45453</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>46181</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45099</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>46181</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>45085</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45127</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>46182</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>45415</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>46186</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>46186</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>46186</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45124</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>46188</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44581</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44719</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44970</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45439</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45755</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45701</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45127</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>44578</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>46201</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45551</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44581</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45614</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44697</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>46251</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45765</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>46209</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>46209</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>44638</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45148</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45614</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>46255</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45709</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45237</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45762</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>44823</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45279</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45439</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>46222</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45525</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45378</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45237</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44550</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44550</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>44915</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>44936</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45532</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>46288</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45439</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46245</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46245</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46245</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46245</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>46288</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>44970</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45127</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44812</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>44881</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45078</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>46289</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>44902</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>44662</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>45241</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>44489</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45478</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44973</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45614</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44987</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>44944</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44847</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45124</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>45124</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45124</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44796</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45667</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45337</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45447</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45217</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45723</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45287</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>44747</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45404</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45716</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45497</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45632</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45701</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45530</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45789</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44606</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>44606</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44834</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45266</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45266</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>44901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45834</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45526</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46125</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>44517</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>44549</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>46125</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45278</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>44651</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45764</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44480</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>45147</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44880</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>45530</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>45002</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>44913</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>44785</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>44606</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>45723</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45533</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>44542</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>45091</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45197</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>44876</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44894</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45355</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>46030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45477</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45527</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>45477</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44662</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45894</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45891</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45821</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>45831</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45897</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45148</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>45386</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>45905</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45905</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>46052</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>44517</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45905</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>45272</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45527</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45802</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>45127</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45127</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>46079</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45932</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>45932</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45055</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>46086</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45399</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45251</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45012</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>44916</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44970</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44756</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45062</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45947</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45470</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>46108</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45632</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>45359</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45623</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>46121</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>46122</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>46126</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44524</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>46132</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45166</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>46129</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45075</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>45971</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45593</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>46135</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>45988</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45960</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>45988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45993</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45148</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45148</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45993</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45371</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>46003</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>45999</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45442</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45446</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>45755</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>46146</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>46146</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>46146</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>45127</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>46149</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>45834</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>46153</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>46153</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>46153</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45526</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45835</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45105</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>45274</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>45784</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45049</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>46163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45121</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>46163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>44550</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45593</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44535</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45453</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>46181</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45099</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>46181</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>45085</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45127</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>46182</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>45415</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>46186</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>46186</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>46186</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45124</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>46188</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>44581</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44719</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44970</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45439</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45755</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45701</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45127</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>44578</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>46201</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45551</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44581</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45614</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44697</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>46251</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45765</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>46209</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>46209</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>44638</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45148</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45614</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>46255</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45709</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45237</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45762</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>44823</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45279</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45439</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>46222</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45525</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45378</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45237</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44550</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44550</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>44915</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>44936</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45532</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>46288</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45439</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46245</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46245</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46245</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46245</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>46288</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>44970</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45127</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44812</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>44881</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45078</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>46289</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>44902</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>44662</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>45241</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>44489</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45478</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44973</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45614</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44987</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>44944</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44847</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45124</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>45124</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45124</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44796</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45667</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45337</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45447</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45217</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45723</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45287</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>44747</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45404</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45716</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45497</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45632</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45701</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45530</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45789</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44606</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>44606</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44834</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45266</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45266</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>44901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45834</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 34758-2024</t>
+          <t>A 18094-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45526</v>
+        <v>46125</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -875,19 +875,19 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -899,21 +899,247 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blackticka
+Fjällig taggsvamp s.str.
+Brandticka
+Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18094-2026 artfynd.xlsx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18094-2026 karta.png", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18094-2026 georefererad karta.tif", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18094-2026 FSC-klagomål.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18094-2026 FSC-klagomål mail.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18094-2026 tillsynsbegäran.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18094-2026 tillsynsbegäran mail.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 66072-2021</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44517</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Gullklöver
+Skogsklocka
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 66072-2021 artfynd.xlsx", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 66072-2021 karta.png", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 66072-2021 georefererad karta.tif", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 66072-2021 FSC-klagomål.docx", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 66072-2021 FSC-klagomål mail.docx", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 66072-2021 tillsynsbegäran.docx", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 66072-2021 tillsynsbegäran mail.docx", "A 66072-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 34758-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45526</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U6" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp
 Fjällig taggsvamp s.str.
@@ -921,261 +1147,35 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 34758-2024 artfynd.xlsx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 34758-2024 karta.png", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 34758-2024 georefererad karta.tif", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 34758-2024 FSC-klagomål.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 34758-2024 FSC-klagomål mail.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 34758-2024 tillsynsbegäran.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 34758-2024 tillsynsbegäran mail.docx", "A 34758-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 18094-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46125</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Blackticka
-Fjällig taggsvamp s.str.
-Brandticka
-Mörk husmossa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18094-2026 artfynd.xlsx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18094-2026 karta.png", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18094-2026 georefererad karta.tif", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18094-2026 FSC-klagomål.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18094-2026 FSC-klagomål mail.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18094-2026 tillsynsbegäran.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18094-2026 tillsynsbegäran mail.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 66072-2021</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44517</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Gullklöver
-Skogsklocka
-Svart trolldruva
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 66072-2021 artfynd.xlsx", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 66072-2021 karta.png", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 66072-2021 georefererad karta.tif", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 66072-2021 FSC-klagomål.docx", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 66072-2021 FSC-klagomål mail.docx", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 66072-2021 tillsynsbegäran.docx", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 66072-2021 tillsynsbegäran mail.docx", "A 66072-2021")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46051</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46092</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46125</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>45278</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>44651</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44480</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 35573-2023</t>
+          <t>A 13208-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45147</v>
+        <v>45002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2304,13 +2304,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2346,905 +2341,910 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 13208-2023 artfynd.xlsx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 13208-2023 karta.png", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 13208-2023 georefererad karta.tif", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 13208-2023 FSC-klagomål.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 13208-2023 FSC-klagomål mail.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 13208-2023 tillsynsbegäran.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 13208-2023 tillsynsbegäran mail.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 13208-2023 prioriterade fågelarter.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 60736-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44913</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 45484-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45188</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 45484-2023 artfynd.xlsx", "A 45484-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 45484-2023 karta.png", "A 45484-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 45484-2023 georefererad karta.tif", "A 45484-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 45484-2023 FSC-klagomål.docx", "A 45484-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 45484-2023 FSC-klagomål mail.docx", "A 45484-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 45484-2023 tillsynsbegäran.docx", "A 45484-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 45484-2023 tillsynsbegäran mail.docx", "A 45484-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 67321-2021</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44523</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 67321-2021 artfynd.xlsx", "A 67321-2021")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 67321-2021 karta.png", "A 67321-2021")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 67321-2021 georefererad karta.tif", "A 67321-2021")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 67321-2021 FSC-klagomål.docx", "A 67321-2021")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 67321-2021 FSC-klagomål mail.docx", "A 67321-2021")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 67321-2021 tillsynsbegäran.docx", "A 67321-2021")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 67321-2021 tillsynsbegäran mail.docx", "A 67321-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 31980-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45119</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 31980-2023 artfynd.xlsx", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 31980-2023 karta.png", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 31980-2023 georefererad karta.tif", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 31980-2023 FSC-klagomål.docx", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 31980-2023 FSC-klagomål mail.docx", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 31980-2023 tillsynsbegäran.docx", "A 31980-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 31980-2023 tillsynsbegäran mail.docx", "A 31980-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53706-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44880</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 53706-2022 artfynd.xlsx", "A 53706-2022")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 53706-2022 karta.png", "A 53706-2022")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 53706-2022 georefererad karta.tif", "A 53706-2022")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 53706-2022 FSC-klagomål.docx", "A 53706-2022")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 53706-2022 FSC-klagomål mail.docx", "A 53706-2022")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 53706-2022 tillsynsbegäran.docx", "A 53706-2022")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 53706-2022 tillsynsbegäran mail.docx", "A 53706-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 35334-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45530</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 46620-2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45583</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 35573-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45147</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35573-2023 artfynd.xlsx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35573-2023 karta.png", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35573-2023 georefererad karta.tif", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35573-2023 FSC-klagomål.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35573-2023 FSC-klagomål mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35573-2023 tillsynsbegäran.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35573-2023 tillsynsbegäran mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 67321-2021</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44523</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 67321-2021 artfynd.xlsx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 67321-2021 karta.png", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 67321-2021 georefererad karta.tif", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 67321-2021 FSC-klagomål.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 67321-2021 FSC-klagomål mail.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 67321-2021 tillsynsbegäran.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 67321-2021 tillsynsbegäran mail.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53706-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44880</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 53706-2022 artfynd.xlsx", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 53706-2022 karta.png", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 53706-2022 georefererad karta.tif", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 53706-2022 FSC-klagomål.docx", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 53706-2022 FSC-klagomål mail.docx", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 53706-2022 tillsynsbegäran.docx", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 53706-2022 tillsynsbegäran mail.docx", "A 53706-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 31980-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45119</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Springkorn</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 31980-2023 artfynd.xlsx", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 31980-2023 karta.png", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 31980-2023 georefererad karta.tif", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 31980-2023 FSC-klagomål.docx", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 31980-2023 FSC-klagomål mail.docx", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 31980-2023 tillsynsbegäran.docx", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 31980-2023 tillsynsbegäran mail.docx", "A 31980-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 35334-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45530</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Nattviol</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 13208-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Mindre flugsnappare</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 13208-2023 artfynd.xlsx", "A 13208-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 13208-2023 karta.png", "A 13208-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 13208-2023 georefererad karta.tif", "A 13208-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 13208-2023 FSC-klagomål.docx", "A 13208-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 13208-2023 FSC-klagomål mail.docx", "A 13208-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 13208-2023 tillsynsbegäran.docx", "A 13208-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 13208-2023 tillsynsbegäran mail.docx", "A 13208-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 13208-2023 prioriterade fågelarter.docx", "A 13208-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 45484-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45188</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 45484-2023 artfynd.xlsx", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 45484-2023 karta.png", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 45484-2023 georefererad karta.tif", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 45484-2023 FSC-klagomål.docx", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 45484-2023 FSC-klagomål mail.docx", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 45484-2023 tillsynsbegäran.docx", "A 45484-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 45484-2023 tillsynsbegäran mail.docx", "A 45484-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 60736-2022</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44913</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 46620-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45583</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9271-2022</t>
+          <t>A 7828-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44616</v>
+        <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7828-2022</t>
+          <t>A 9271-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3737,14 +3737,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44608</v>
+        <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>44735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44785</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>44606</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46530-2023</t>
+          <t>A 6947-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5222,14 +5222,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45197</v>
+        <v>45701</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10996-2025</t>
+          <t>A 23451-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45723</v>
+        <v>45453</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5363,7 +5363,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35940-2024</t>
+          <t>A 34427-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45533</v>
+        <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5392,8 +5392,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>6.7</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5436,7 +5441,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26037-2023</t>
+          <t>A 50635-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5450,10 +5455,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45091</v>
+        <v>45217</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5466,7 +5471,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5509,7 +5514,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 71625-2021</t>
+          <t>A 39213-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5523,10 +5528,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44542</v>
+        <v>45166</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5538,8 +5543,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5582,7 +5592,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53074-2022</t>
+          <t>A 7273-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5596,10 +5606,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44876</v>
+        <v>44970</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5612,7 +5622,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5655,7 +5665,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56748-2022</t>
+          <t>A 22619-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5669,10 +5679,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44894</v>
+        <v>45789</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5690,7 +5700,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5733,7 +5743,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8952-2024</t>
+          <t>A 28327-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5747,10 +5757,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45355</v>
+        <v>44747</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5763,7 +5773,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5806,7 +5816,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 827-2026</t>
+          <t>A 53573-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5820,10 +5830,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46030</v>
+        <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5836,7 +5846,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5879,7 +5889,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35335-2024</t>
+          <t>A 61896-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5893,10 +5903,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45530</v>
+        <v>46003</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5908,13 +5918,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5957,7 +5962,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28242-2024</t>
+          <t>A 28271-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5974,7 +5979,7 @@
         <v>45477</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5987,7 +5992,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6030,7 +6035,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28271-2024</t>
+          <t>A 21745-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6044,10 +6049,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45477</v>
+        <v>45442</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6060,7 +6065,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6103,7 +6108,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27995-2024</t>
+          <t>A 22362-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6117,10 +6122,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45476</v>
+        <v>45446</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6133,7 +6138,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6176,7 +6181,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 40080-2025</t>
+          <t>A 18439-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6190,10 +6195,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45894</v>
+        <v>45762</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6205,8 +6210,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6266,7 +6276,7 @@
         <v>45891</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6327,7 +6337,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29427-2024</t>
+          <t>A 30853-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6341,10 +6351,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45483</v>
+        <v>45831</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6357,7 +6367,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6417,7 +6427,7 @@
         <v>45821</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6473,7 +6483,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30853-2025</t>
+          <t>A 40080-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6487,10 +6497,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45831</v>
+        <v>45894</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6503,7 +6513,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6546,7 +6556,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42370-2025</t>
+          <t>A 40744-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6556,14 +6566,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45905</v>
+        <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6577,11 +6587,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>5.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6624,7 +6634,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34849-2024</t>
+          <t>A 827-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6634,14 +6644,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45527</v>
+        <v>46030</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6653,13 +6663,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6702,7 +6707,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40744-2025</t>
+          <t>A 46530-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6716,10 +6721,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45897</v>
+        <v>45197</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6733,11 +6738,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6780,7 +6785,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5971-2026</t>
+          <t>A 42441-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6794,10 +6799,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46052</v>
+        <v>45905</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6810,7 +6815,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6853,7 +6858,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15553-2022</t>
+          <t>A 73267-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6867,10 +6872,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44662</v>
+        <v>44550</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6883,7 +6888,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.8</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6926,7 +6931,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42441-2025</t>
+          <t>A 42572-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6943,7 +6948,7 @@
         <v>45905</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6956,7 +6961,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6999,7 +7004,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42572-2025</t>
+          <t>A 26037-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7013,10 +7018,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45905</v>
+        <v>45091</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7029,7 +7034,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>12.5</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7072,7 +7077,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35855-2023</t>
+          <t>A 8952-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7086,10 +7091,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45148</v>
+        <v>45355</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7101,13 +7106,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13198-2024</t>
+          <t>A 25462-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45386</v>
+        <v>45802</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7179,8 +7179,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7223,7 +7228,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 65915-2021</t>
+          <t>A 35335-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7237,10 +7242,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44517</v>
+        <v>45530</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7252,8 +7257,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>17.2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7296,7 +7306,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62922-2023</t>
+          <t>A 42370-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7306,14 +7316,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45272</v>
+        <v>45905</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7325,8 +7335,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7369,7 +7384,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 34886-2024</t>
+          <t>A 5971-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7383,10 +7398,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45527</v>
+        <v>46052</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7398,13 +7413,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7447,7 +7457,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25462-2025</t>
+          <t>A 35863-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7461,10 +7471,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45802</v>
+        <v>45148</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7478,11 +7488,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7542,7 +7552,7 @@
         <v>45929</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7598,7 +7608,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10987-2026</t>
+          <t>A 48647-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7612,10 +7622,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46079</v>
+        <v>45593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7627,13 +7637,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7693,7 +7698,7 @@
         <v>45932</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7749,7 +7754,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47917-2025</t>
+          <t>A 14382-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7759,14 +7764,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45932</v>
+        <v>45012</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7778,8 +7783,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7822,7 +7832,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47940-2025</t>
+          <t>A 47917-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7839,7 +7849,7 @@
         <v>45932</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7852,7 +7862,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7895,7 +7905,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 33222-2023</t>
+          <t>A 47940-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7909,10 +7919,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45127</v>
+        <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7924,13 +7934,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7973,7 +7978,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33229-2023</t>
+          <t>A 20244-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7987,10 +7992,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45127</v>
+        <v>45055</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8002,13 +8007,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8051,7 +8051,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12086-2026</t>
+          <t>A 11765-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46086</v>
+        <v>45727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8129,7 +8129,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11765-2025</t>
+          <t>A 51123-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45727</v>
+        <v>45947</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8158,13 +8158,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8207,7 +8202,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20244-2023</t>
+          <t>A 20862-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8221,10 +8216,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45055</v>
+        <v>45439</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8237,7 +8232,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8280,7 +8275,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14988-2024</t>
+          <t>A 10987-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8294,10 +8289,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45399</v>
+        <v>46079</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8309,8 +8304,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51123-2025</t>
+          <t>A 2812-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45947</v>
+        <v>44944</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58688-2023</t>
+          <t>A 26869-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8436,14 +8436,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45251</v>
+        <v>45470</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8455,8 +8455,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8499,7 +8504,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26869-2024</t>
+          <t>A 6909-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8513,10 +8518,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45470</v>
+        <v>45701</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8534,7 +8539,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8577,7 +8582,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14382-2023</t>
+          <t>A 9693-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8587,14 +8592,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45012</v>
+        <v>45716</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8612,7 +8617,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8655,7 +8660,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61463-2022</t>
+          <t>A 12086-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8665,14 +8670,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44916</v>
+        <v>46086</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8684,8 +8689,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8728,7 +8738,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7299-2023</t>
+          <t>A 6118-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8742,10 +8752,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44970</v>
+        <v>45337</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8758,7 +8768,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8801,7 +8811,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 29852-2022</t>
+          <t>A 13198-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8815,10 +8825,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44756</v>
+        <v>45386</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8831,7 +8841,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8874,7 +8884,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21295-2023</t>
+          <t>A 64121-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8884,14 +8894,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45062</v>
+        <v>45279</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8903,13 +8913,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8952,7 +8957,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16109-2026</t>
+          <t>A 33218-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8966,10 +8971,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46108</v>
+        <v>45127</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8983,11 +8988,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9030,7 +9035,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17720-2026</t>
+          <t>A 33224-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9044,10 +9049,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46121</v>
+        <v>45127</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9059,8 +9064,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9103,7 +9113,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17897-2026</t>
+          <t>A 16885-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9117,10 +9127,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46122</v>
+        <v>45755</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9132,13 +9142,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9181,7 +9186,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58121-2024</t>
+          <t>A 27995-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9195,10 +9200,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45632</v>
+        <v>45476</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9211,7 +9216,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9254,7 +9259,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9524-2024</t>
+          <t>A 55433-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9264,14 +9269,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45359</v>
+        <v>45971</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9283,13 +9288,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>14.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 55835-2024</t>
+          <t>A 9524-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9342,14 +9342,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45623</v>
+        <v>45359</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,8 +9361,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9405,7 +9410,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60045-2022</t>
+          <t>A 65915-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9419,10 +9424,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44902</v>
+        <v>44517</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9435,7 +9440,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6</v>
+        <v>17.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9478,7 +9483,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 18285-2026</t>
+          <t>A 16109-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9492,10 +9497,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46126</v>
+        <v>46108</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9507,8 +9512,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9551,7 +9561,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 55433-2025</t>
+          <t>A 39407-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9565,10 +9575,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45971</v>
+        <v>45551</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9581,7 +9591,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>14.2</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9624,7 +9634,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 19079-2026</t>
+          <t>A 17519-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9638,10 +9648,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46132</v>
+        <v>45415</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9653,8 +9663,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>10.1</v>
+        <v>4.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9697,7 +9712,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 18916-2026</t>
+          <t>A 59298-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9711,10 +9726,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46129</v>
+        <v>45988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9726,13 +9741,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9792,7 +9802,7 @@
         <v>45988</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9848,7 +9858,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 67617-2021</t>
+          <t>A 59933-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9862,10 +9872,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44524</v>
+        <v>45993</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9877,8 +9887,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9921,7 +9936,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 19823-2026</t>
+          <t>A 59919-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9935,10 +9950,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46135</v>
+        <v>45993</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9950,8 +9965,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9994,7 +10014,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 39213-2023</t>
+          <t>A 17897-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10008,10 +10028,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45166</v>
+        <v>46122</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10025,11 +10045,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10072,7 +10092,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 59298-2025</t>
+          <t>A 17720-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10086,10 +10106,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45988</v>
+        <v>46121</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10102,7 +10122,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10145,7 +10165,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23117-2023</t>
+          <t>A 59955-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10159,10 +10179,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45075</v>
+        <v>45993</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10180,7 +10200,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10223,7 +10243,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53678-2025</t>
+          <t>A 18285-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10237,10 +10257,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45960</v>
+        <v>46126</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10253,7 +10273,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10296,7 +10316,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 48647-2024</t>
+          <t>A 18916-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10310,10 +10330,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45593</v>
+        <v>46129</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10325,8 +10345,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10369,7 +10394,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 59933-2025</t>
+          <t>A 58688-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10383,10 +10408,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45993</v>
+        <v>45251</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10396,11 +10421,6 @@
       <c r="G121" t="inlineStr">
         <is>
           <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -10447,7 +10467,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 59919-2025</t>
+          <t>A 35855-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10461,10 +10481,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45993</v>
+        <v>45148</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10478,11 +10498,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10525,7 +10545,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59955-2025</t>
+          <t>A 19079-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10539,10 +10559,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45993</v>
+        <v>46132</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10554,13 +10574,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4.6</v>
+        <v>10.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10603,7 +10618,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 47734-2025</t>
+          <t>A 32796-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10617,10 +10632,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45931</v>
+        <v>45124</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10638,7 +10653,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10681,7 +10696,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 11196-2024</t>
+          <t>A 32822-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10695,10 +10710,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45371</v>
+        <v>45124</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10710,8 +10725,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10754,7 +10774,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 35831-2023</t>
+          <t>A 34849-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10764,14 +10784,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45148</v>
+        <v>45527</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10785,11 +10805,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10832,7 +10852,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 35863-2023</t>
+          <t>A 19823-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10846,10 +10866,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45148</v>
+        <v>46135</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10861,13 +10881,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10910,7 +10925,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61896-2025</t>
+          <t>A 31831-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10924,10 +10939,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46003</v>
+        <v>45834</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10940,7 +10955,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10983,7 +10998,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60850-2025</t>
+          <t>A 34886-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10997,10 +11012,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45999</v>
+        <v>45527</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11012,8 +11027,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11056,7 +11076,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 21745-2024</t>
+          <t>A 31968-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11070,10 +11090,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45442</v>
+        <v>45835</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11086,7 +11106,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11129,7 +11149,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 31831-2025</t>
+          <t>A 58121-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11143,10 +11163,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45834</v>
+        <v>45632</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11159,7 +11179,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11202,7 +11222,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 31968-2025</t>
+          <t>A 53678-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11216,10 +11236,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45835</v>
+        <v>45960</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11232,7 +11252,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11275,7 +11295,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22362-2024</t>
+          <t>A 18229-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11289,10 +11309,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45446</v>
+        <v>45761</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11305,7 +11325,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11348,7 +11368,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 16885-2025</t>
+          <t>A 54170-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11362,10 +11382,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45755</v>
+        <v>44881</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11378,7 +11398,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.1</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11421,7 +11441,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 17135-2025</t>
+          <t>A 29427-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11435,10 +11455,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45755</v>
+        <v>45483</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11451,7 +11471,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>10.3</v>
+        <v>3.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11494,7 +11514,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21081-2026</t>
+          <t>A 15563-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11508,10 +11528,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46146</v>
+        <v>44662</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11523,13 +11543,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>14.8</v>
+        <v>3.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11572,7 +11587,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 21137-2026</t>
+          <t>A 11196-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11586,10 +11601,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46146</v>
+        <v>45371</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11602,7 +11617,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11645,7 +11660,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 33218-2023</t>
+          <t>A 46300-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11659,10 +11674,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45127</v>
+        <v>44847</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11674,13 +11689,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11723,7 +11733,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 61457-2022</t>
+          <t>A 56280-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11737,10 +11747,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44916</v>
+        <v>45241</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11753,7 +11763,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11796,7 +11806,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 60893-2025</t>
+          <t>A 60850-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11813,7 +11823,7 @@
         <v>45999</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11826,7 +11836,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11869,7 +11879,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 21106-2026</t>
+          <t>A 47734-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11883,10 +11893,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46146</v>
+        <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11900,11 +11910,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>8.1</v>
+        <v>2.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11947,7 +11957,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 21146-2026</t>
+          <t>A 10989-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11961,10 +11971,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46146</v>
+        <v>45723</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11977,7 +11987,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12020,7 +12030,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 21634-2026</t>
+          <t>A 65062-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12034,10 +12044,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46149</v>
+        <v>45287</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12049,8 +12059,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>11.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12093,7 +12108,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 34786-2024</t>
+          <t>A 58714-2021</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12107,10 +12122,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45526</v>
+        <v>44489</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12122,13 +12137,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12171,7 +12181,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 29231-2023</t>
+          <t>A 67617-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12185,10 +12195,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45105</v>
+        <v>44524</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12201,7 +12211,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12244,7 +12254,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 22221-2026</t>
+          <t>A 55835-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12258,10 +12268,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46153</v>
+        <v>45623</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12274,7 +12284,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12317,7 +12327,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 22192-2026</t>
+          <t>A 30859-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12331,10 +12341,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46153</v>
+        <v>45497</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12347,7 +12357,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12390,7 +12400,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 22222-2026</t>
+          <t>A 35831-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12404,10 +12414,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46153</v>
+        <v>45148</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12419,8 +12429,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12463,7 +12478,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19323-2023</t>
+          <t>A 22582-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12473,14 +12488,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45049</v>
+        <v>45447</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12492,8 +12507,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12536,7 +12556,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 63318-2023</t>
+          <t>A 7297-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12550,10 +12570,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45274</v>
+        <v>44970</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12566,7 +12586,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12609,7 +12629,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32680-2023</t>
+          <t>A 15663-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12619,14 +12639,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45121</v>
+        <v>45404</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12638,13 +12658,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12687,7 +12702,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21836-2025</t>
+          <t>A 21106-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12701,10 +12716,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45784</v>
+        <v>46146</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12716,8 +12731,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12760,7 +12780,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 73267-2021</t>
+          <t>A 21081-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12774,10 +12794,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44550</v>
+        <v>46146</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12789,8 +12809,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>14.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12833,7 +12858,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 48630-2024</t>
+          <t>A 21137-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12847,10 +12872,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45593</v>
+        <v>46146</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12863,7 +12888,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12906,7 +12931,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23516-2026</t>
+          <t>A 1409-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12920,10 +12945,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46163</v>
+        <v>45667</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12935,13 +12960,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12984,7 +13004,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 23505-2026</t>
+          <t>A 60893-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12998,10 +13018,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46163</v>
+        <v>45999</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13013,13 +13033,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13062,7 +13077,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23451-2024</t>
+          <t>A 21146-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13076,10 +13091,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45453</v>
+        <v>46146</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13092,7 +13107,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13135,7 +13150,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 70214-2021</t>
+          <t>A 21634-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13149,10 +13164,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44535</v>
+        <v>46149</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13165,7 +13180,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13208,7 +13223,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28321-2023</t>
+          <t>A 22192-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13222,10 +13237,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45099</v>
+        <v>46153</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13238,7 +13253,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13281,7 +13296,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 25008-2023</t>
+          <t>A 22222-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13295,10 +13310,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45085</v>
+        <v>46153</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13311,7 +13326,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13354,7 +13369,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 33219-2023</t>
+          <t>A 22221-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13368,10 +13383,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45127</v>
+        <v>46153</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13383,13 +13398,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13432,7 +13442,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 48590-2024</t>
+          <t>A 63318-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13442,14 +13452,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45593</v>
+        <v>45274</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13461,13 +13471,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>7.9</v>
+        <v>5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13510,7 +13515,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 17519-2024</t>
+          <t>A 19996-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13524,10 +13529,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45415</v>
+        <v>44697</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13539,13 +13544,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13588,7 +13588,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 32796-2023</t>
+          <t>A 21836-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13602,10 +13602,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45124</v>
+        <v>45784</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13617,13 +13617,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13666,7 +13661,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 26104-2026</t>
+          <t>A 60045-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13680,10 +13675,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46181</v>
+        <v>44902</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13696,7 +13691,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13739,7 +13734,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 2818-2022</t>
+          <t>A 10383-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13753,10 +13748,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44581</v>
+        <v>44987</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13769,7 +13764,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>11</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13812,7 +13807,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 7273-2023</t>
+          <t>A 23505-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13826,10 +13821,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44970</v>
+        <v>46163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13841,8 +13836,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13885,7 +13885,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20862-2024</t>
+          <t>A 23516-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13899,10 +13899,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45439</v>
+        <v>46163</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13914,8 +13914,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13958,7 +13963,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 6909-2025</t>
+          <t>A 17135-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13968,14 +13973,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45701</v>
+        <v>45755</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13987,13 +13992,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>10.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14036,7 +14036,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 33224-2023</t>
+          <t>A 29852-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14050,10 +14050,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45127</v>
+        <v>44756</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14065,13 +14065,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14114,7 +14109,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 26129-2026</t>
+          <t>A 70214-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14128,10 +14123,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46181</v>
+        <v>44535</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14144,7 +14139,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14187,7 +14182,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 2278-2022</t>
+          <t>A 56748-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14201,10 +14196,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44578</v>
+        <v>44894</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14222,7 +14217,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14265,7 +14260,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 39407-2024</t>
+          <t>A 28242-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14279,10 +14274,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45551</v>
+        <v>45477</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14295,7 +14290,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14338,7 +14333,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 26325-2026</t>
+          <t>A 55137-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14352,10 +14347,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46182</v>
+        <v>45237</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14368,7 +14363,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14411,7 +14406,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 2843-2022</t>
+          <t>A 73264-2021</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14425,10 +14420,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44581</v>
+        <v>44550</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14441,7 +14436,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14484,7 +14479,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 27080-2026</t>
+          <t>A 73266-2021</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14498,10 +14493,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46186</v>
+        <v>44550</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14514,7 +14509,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14557,7 +14552,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27075-2026</t>
+          <t>A 7299-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14571,10 +14566,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46186</v>
+        <v>44970</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14587,7 +14582,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14630,7 +14625,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27076-2026</t>
+          <t>A 26325-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14644,10 +14639,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46186</v>
+        <v>46182</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14660,7 +14655,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14703,7 +14698,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 27252-2026</t>
+          <t>A 26104-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14717,10 +14712,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14733,7 +14728,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14776,7 +14771,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 53596-2024</t>
+          <t>A 26129-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14790,10 +14785,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45614</v>
+        <v>46181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14806,7 +14801,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14849,7 +14844,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 19996-2022</t>
+          <t>A 27075-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14863,10 +14858,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44697</v>
+        <v>46186</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14879,7 +14874,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14922,7 +14917,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 19069-2025</t>
+          <t>A 27080-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14936,10 +14931,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45765</v>
+        <v>46186</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14952,7 +14947,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14995,7 +14990,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 23020-2022</t>
+          <t>A 27076-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15009,10 +15004,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44719</v>
+        <v>46186</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15025,7 +15020,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15068,7 +15063,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 12484-2022</t>
+          <t>A 27252-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15082,10 +15077,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44638</v>
+        <v>46188</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15098,7 +15093,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15141,7 +15136,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 29116-2026</t>
+          <t>A 28517-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15155,10 +15150,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46201</v>
+        <v>45478</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15170,8 +15165,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15214,7 +15214,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 35850-2023</t>
+          <t>A 14988-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45148</v>
+        <v>45399</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15243,13 +15243,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15292,7 +15287,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 29265-2026</t>
+          <t>A 48630-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15306,10 +15301,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46202</v>
+        <v>45593</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15322,7 +15317,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15365,7 +15360,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 53573-2024</t>
+          <t>A 62922-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15379,10 +15374,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45614</v>
+        <v>45272</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15395,7 +15390,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15438,7 +15433,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 8399-2025</t>
+          <t>A 23020-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15448,14 +15443,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45709</v>
+        <v>44719</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15467,13 +15462,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15516,7 +15506,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 55249-2023</t>
+          <t>A 53074-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15530,10 +15520,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45237</v>
+        <v>44876</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15546,7 +15536,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15589,7 +15579,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30374-2026</t>
+          <t>A 35850-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15603,10 +15593,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46209</v>
+        <v>45148</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15618,8 +15608,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15662,7 +15657,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30380-2026</t>
+          <t>A 2278-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15676,10 +15671,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46209</v>
+        <v>44578</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15691,8 +15686,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15735,7 +15735,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 18439-2025</t>
+          <t>A 32680-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15749,10 +15749,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45762</v>
+        <v>45121</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15766,11 +15766,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15813,7 +15813,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34637-2026</t>
+          <t>A 29116-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15827,10 +15827,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46255</v>
+        <v>46201</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15886,7 +15886,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 40968-2022</t>
+          <t>A 29265-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15900,10 +15900,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44823</v>
+        <v>46202</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>16.5</v>
+        <v>2.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15959,7 +15959,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 64121-2023</t>
+          <t>A 61457-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15969,14 +15969,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45279</v>
+        <v>44916</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.1</v>
+        <v>4.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16032,7 +16032,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 34427-2024</t>
+          <t>A 40968-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16042,14 +16042,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45525</v>
+        <v>44823</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16061,13 +16061,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16110,7 +16105,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 12320-2024</t>
+          <t>A 12484-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16120,14 +16115,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45378</v>
+        <v>44638</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16139,13 +16134,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16188,7 +16178,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 55137-2023</t>
+          <t>A 19069-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16202,10 +16192,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45237</v>
+        <v>45765</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16218,7 +16208,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16261,7 +16251,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 73264-2021</t>
+          <t>A 30380-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16275,10 +16265,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44550</v>
+        <v>46209</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16291,7 +16281,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16334,7 +16324,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 73266-2021</t>
+          <t>A 30374-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16348,10 +16338,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44550</v>
+        <v>46209</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16364,7 +16354,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16407,7 +16397,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 20933-2024</t>
+          <t>A 61231-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16421,10 +16411,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45439</v>
+        <v>44915</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16437,7 +16427,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>11.3</v>
+        <v>2.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16480,7 +16470,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 61231-2022</t>
+          <t>A 2818-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16494,10 +16484,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44915</v>
+        <v>44581</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16510,7 +16500,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>11</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16553,7 +16543,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 31480-2026</t>
+          <t>A 7919-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16563,14 +16553,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46222</v>
+        <v>44973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16583,7 +16573,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16626,7 +16616,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 1338-2023</t>
+          <t>A 33222-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16640,10 +16630,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44936</v>
+        <v>45127</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16655,8 +16645,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16699,7 +16694,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 35654-2024</t>
+          <t>A 33229-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16713,10 +16708,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45532</v>
+        <v>45127</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16728,8 +16723,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16772,7 +16772,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 7297-2023</t>
+          <t>A 15553-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16786,10 +16786,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44970</v>
+        <v>44662</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16845,7 +16845,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 33227-2023</t>
+          <t>A 35940-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16859,10 +16859,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45127</v>
+        <v>45533</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16874,13 +16874,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>2.9</v>
+        <v>6.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16923,7 +16918,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 38261-2022</t>
+          <t>A 48590-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16933,14 +16928,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44812</v>
+        <v>45593</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16952,8 +16947,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16996,7 +16996,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 54170-2022</t>
+          <t>A 12320-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17006,14 +17006,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44881</v>
+        <v>45378</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17025,8 +17025,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17069,7 +17074,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 24036-2023</t>
+          <t>A 53596-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17083,10 +17088,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45078</v>
+        <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17099,7 +17104,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17142,7 +17147,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 60043-2022</t>
+          <t>A 20933-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17156,10 +17161,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44902</v>
+        <v>45439</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17172,7 +17177,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>11.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17215,7 +17220,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 15563-2022</t>
+          <t>A 31480-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17225,14 +17230,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44662</v>
+        <v>46222</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17245,7 +17250,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17288,7 +17293,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 39366-2026</t>
+          <t>A 71625-2021</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17302,10 +17307,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46288</v>
+        <v>44542</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17318,7 +17323,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17361,7 +17366,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 56280-2023</t>
+          <t>A 24036-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17375,10 +17380,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45241</v>
+        <v>45078</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17391,7 +17396,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17434,7 +17439,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 20928-2024</t>
+          <t>A 32830-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17448,10 +17453,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45439</v>
+        <v>45124</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17463,8 +17468,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17507,7 +17517,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 33085-2026</t>
+          <t>A 29231-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17521,10 +17531,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46245</v>
+        <v>45105</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17536,13 +17546,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>10.6</v>
+        <v>1.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17585,7 +17590,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 33136-2026</t>
+          <t>A 25008-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17599,10 +17604,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46245</v>
+        <v>45085</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17612,11 +17617,6 @@
       <c r="G218" t="inlineStr">
         <is>
           <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I218" t="n">
@@ -17663,7 +17663,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 33054-2026</t>
+          <t>A 38261-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17677,10 +17677,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46245</v>
+        <v>44812</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17692,13 +17692,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17741,7 +17736,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 33055-2026</t>
+          <t>A 34786-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17755,10 +17750,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46245</v>
+        <v>45526</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17776,7 +17771,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>11.8</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17819,7 +17814,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 39368-2026</t>
+          <t>A 33219-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17833,10 +17828,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46288</v>
+        <v>45127</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17848,8 +17843,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 58714-2021</t>
+          <t>A 20928-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17906,10 +17906,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44489</v>
+        <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17965,7 +17965,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 39507-2026</t>
+          <t>A 33085-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17979,10 +17979,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46289</v>
+        <v>46245</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17994,8 +17994,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>1.9</v>
+        <v>10.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18038,7 +18043,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 28517-2024</t>
+          <t>A 33136-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18052,10 +18057,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45478</v>
+        <v>46245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18073,7 +18078,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18116,7 +18121,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 7919-2023</t>
+          <t>A 39507-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18130,10 +18135,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44973</v>
+        <v>46289</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18146,7 +18151,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18189,7 +18194,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 53585-2024</t>
+          <t>A 39366-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18203,10 +18208,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45614</v>
+        <v>46288</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18219,7 +18224,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.3</v>
+        <v>9.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18262,7 +18267,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 10383-2023</t>
+          <t>A 39368-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18276,10 +18281,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44987</v>
+        <v>46288</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18292,7 +18297,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18335,7 +18340,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 2812-2023</t>
+          <t>A 33054-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18349,10 +18354,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44944</v>
+        <v>46245</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18364,8 +18369,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18408,7 +18418,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 46300-2022</t>
+          <t>A 33055-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18422,10 +18432,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44847</v>
+        <v>46245</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18437,8 +18447,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>0.7</v>
+        <v>11.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18481,7 +18496,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 40732-2026</t>
+          <t>A 8399-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18491,14 +18506,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46296</v>
+        <v>45709</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18508,6 +18523,11 @@
       <c r="G230" t="inlineStr">
         <is>
           <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I230" t="n">
@@ -18554,7 +18574,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 33887-2026</t>
+          <t>A 55249-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18568,10 +18588,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46251</v>
+        <v>45237</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18583,13 +18603,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18632,7 +18647,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 33741-2026</t>
+          <t>A 28321-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18646,10 +18661,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46251</v>
+        <v>45099</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18661,13 +18676,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18710,7 +18720,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 32795-2023</t>
+          <t>A 33741-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18724,10 +18734,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45124</v>
+        <v>46251</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18741,11 +18751,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18788,7 +18798,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 32822-2023</t>
+          <t>A 33887-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18802,10 +18812,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45124</v>
+        <v>46251</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18819,11 +18829,11 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18866,7 +18876,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 32830-2023</t>
+          <t>A 58114-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18880,10 +18890,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45124</v>
+        <v>45632</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18895,13 +18905,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18944,7 +18949,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 34861-2022</t>
+          <t>A 34637-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18958,10 +18963,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44796</v>
+        <v>46255</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18974,7 +18979,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19017,7 +19022,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 18229-2025</t>
+          <t>A 60043-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19031,10 +19036,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45761</v>
+        <v>44902</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19047,7 +19052,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19090,7 +19095,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 1409-2025</t>
+          <t>A 10996-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19104,10 +19109,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45667</v>
+        <v>45723</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19120,7 +19125,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19163,7 +19168,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 6118-2024</t>
+          <t>A 40732-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19177,10 +19182,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45337</v>
+        <v>46296</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19193,7 +19198,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19236,7 +19241,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 22582-2024</t>
+          <t>A 2843-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19246,14 +19251,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45447</v>
+        <v>44581</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19265,13 +19270,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19314,7 +19314,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 50635-2023</t>
+          <t>A 21295-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19328,10 +19328,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45217</v>
+        <v>45062</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19343,8 +19343,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19387,7 +19392,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 10989-2025</t>
+          <t>A 32795-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19401,10 +19406,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45723</v>
+        <v>45124</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19416,8 +19421,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19460,7 +19470,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 65062-2023</t>
+          <t>A 35654-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19474,10 +19484,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45287</v>
+        <v>45532</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19489,13 +19499,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>11.3</v>
+        <v>0.9</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19538,7 +19543,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 28327-2022</t>
+          <t>A 23117-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19552,10 +19557,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44747</v>
+        <v>45075</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19567,8 +19572,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19611,7 +19621,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 15663-2024</t>
+          <t>A 53585-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19621,14 +19631,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45404</v>
+        <v>45614</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19641,7 +19651,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19684,7 +19694,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 9693-2025</t>
+          <t>A 34861-2022</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19698,10 +19708,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45716</v>
+        <v>44796</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19713,13 +19723,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19762,7 +19767,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 30859-2024</t>
+          <t>A 1338-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19776,10 +19781,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45497</v>
+        <v>44936</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19792,7 +19797,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19835,7 +19840,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 58114-2024</t>
+          <t>A 61463-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19849,10 +19854,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45632</v>
+        <v>44916</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19865,7 +19870,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19908,7 +19913,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 6947-2025</t>
+          <t>A 33227-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19918,14 +19923,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45701</v>
+        <v>45127</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19939,11 +19944,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19986,7 +19991,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 35336-2024</t>
+          <t>A 19323-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20000,10 +20005,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45530</v>
+        <v>45049</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20015,13 +20020,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20064,7 +20064,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 22619-2025</t>
+          <t>A 35336-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20078,10 +20078,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45789</v>
+        <v>45530</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20095,11 +20095,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I251" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20142,7 +20142,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>S 915-2022</t>
+          <t>S 5497-2022</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20156,10 +20156,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44606</v>
+        <v>44834</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>18.1</v>
+        <v>31.1</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20220,7 +20220,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>S 870-2022</t>
+          <t>S 4414-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20234,10 +20234,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>15.1</v>
+        <v>21</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20298,7 +20298,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>S 933-2022</t>
+          <t>S 4411-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20312,10 +20312,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>40.7</v>
+        <v>7.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20376,7 +20376,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>S 5497-2022</t>
+          <t>S 915-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20390,10 +20390,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44834</v>
+        <v>44606</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>31.1</v>
+        <v>18.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20454,7 +20454,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>S 4414-2023</t>
+          <t>S 6974-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20468,10 +20468,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>21</v>
+        <v>28.8</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20532,7 +20532,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>S 4411-2023</t>
+          <t>S 6964-2022</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20546,10 +20546,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>7.3</v>
+        <v>18.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20610,7 +20610,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>S 6974-2022</t>
+          <t>S 4403-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20624,10 +20624,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>28.8</v>
+        <v>67.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20688,7 +20688,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>S 6964-2022</t>
+          <t>S 4429-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20702,10 +20702,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>18.8</v>
+        <v>80.3</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20766,7 +20766,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>S 4403-2023</t>
+          <t>S 870-2022</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20780,10 +20780,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>67.7</v>
+        <v>15.1</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20844,7 +20844,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>S 4429-2023</t>
+          <t>S 933-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20858,10 +20858,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>80.3</v>
+        <v>40.7</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20939,7 +20939,7 @@
         <v>45834</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>46125</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44517</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45526</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46051</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46092</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46125</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>45278</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>44651</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44480</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44913</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45188</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44523</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44880</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45583</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>45147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>44735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44785</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>44606</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45701</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45453</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>45217</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45166</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>44970</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45789</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44747</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>46003</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45477</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45442</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45446</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45762</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45891</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>45831</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>45821</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>45894</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>46030</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45197</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45905</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44550</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45905</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45091</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45355</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45802</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45530</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45905</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>46052</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45148</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>45929</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45932</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45012</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>45932</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>45055</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>45727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>45947</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>45439</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>46079</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>44944</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45470</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45701</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45716</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>46086</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>45337</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45386</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45279</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>45127</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>45127</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>45755</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45476</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45971</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>45359</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>44517</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>46108</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>45551</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45415</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45988</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45988</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45993</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45993</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>46122</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>46121</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>45993</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>46126</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>46129</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45251</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45148</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>46132</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45124</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45124</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45527</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>46135</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45834</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45527</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45835</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45632</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45960</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45761</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44881</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45483</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44662</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>45371</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44847</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>45241</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>45999</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45723</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45287</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>44489</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44524</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45623</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45497</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45148</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45447</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>44970</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45404</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>46146</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>46146</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>46146</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>45667</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45999</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>46146</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>46149</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>46153</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>46153</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>46153</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45274</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44697</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45784</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44902</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>44987</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>46163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>46163</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45755</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>44756</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44535</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>44894</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45477</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45237</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>44550</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44550</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44970</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>46182</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>46181</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>46181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>46186</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>46186</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>46186</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>46188</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45478</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45399</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45593</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45272</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44719</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44876</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45148</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>44578</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45121</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>46201</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46202</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>44916</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44823</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44638</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45765</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>46209</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>46209</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>44915</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>44581</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>44973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45127</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45127</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44662</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45533</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45593</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45378</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45439</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>46222</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>44542</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45078</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45124</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45105</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45085</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>44812</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45526</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45127</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>46245</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>46245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>46289</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>46288</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>46288</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46245</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>46245</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45709</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45237</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45099</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>46251</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>46251</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45632</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>46255</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>44902</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45723</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>46296</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>44581</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45062</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45124</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45532</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45075</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45614</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>44796</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>44936</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>44916</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>45127</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45049</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45530</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44834</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45266</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45266</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44606</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44901</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>44901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>44606</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44606</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45834</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>46125</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44517</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45526</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46051</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46092</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46125</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>45278</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>44651</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44480</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44913</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45188</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44523</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44880</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35334-2024</t>
+          <t>A 12320-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2933,14 +2933,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45530</v>
+        <v>45378</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2954,11 +2954,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2994,448 +2994,485 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12320-2024 artfynd.xlsx", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12320-2024 karta.png", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12320-2024 georefererad karta.tif", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12320-2024 FSC-klagomål.docx", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12320-2024 FSC-klagomål mail.docx", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12320-2024 tillsynsbegäran.docx", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12320-2024 tillsynsbegäran mail.docx", "A 12320-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 35334-2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45530</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>Nattviol</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 46620-2024</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>45583</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>2.5</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Mattlummer</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 35573-2023</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45147</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="E26" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>3</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35573-2023 artfynd.xlsx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35573-2023 karta.png", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35573-2023 georefererad karta.tif", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35573-2023 FSC-klagomål.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35573-2023 FSC-klagomål mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35573-2023 tillsynsbegäran.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35573-2023 tillsynsbegäran mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>S 107-2026</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D27" s="1" t="n">
         <v>46037</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="E27" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>111.4</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/S 107-2026 artfynd.xlsx", "S 107-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/S 107-2026 karta.png", "S 107-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/S 107-2026 georefererad karta.tif", "S 107-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/S 107-2026 FSC-klagomål.docx", "S 107-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/S 107-2026 FSC-klagomål mail.docx", "S 107-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/S 107-2026 tillsynsbegäran.docx", "S 107-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/S 107-2026 tillsynsbegäran mail.docx", "S 107-2026")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/S 107-2026 prioriterade fågelarter.docx", "S 107-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 72688-2021</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>44546</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr"/>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 72991-2021</t>
+          <t>A 72688-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3449,10 +3486,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44549</v>
+        <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3465,7 +3502,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3508,7 +3545,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9349-2022</t>
+          <t>A 72991-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3522,10 +3559,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44616</v>
+        <v>44549</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3538,7 +3575,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3581,7 +3618,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33951-2022</t>
+          <t>A 9349-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3595,10 +3632,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44790</v>
+        <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3611,7 +3648,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3654,7 +3691,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7828-2022</t>
+          <t>A 33951-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3664,14 +3701,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44608</v>
+        <v>44790</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3684,7 +3721,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3727,7 +3764,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9271-2022</t>
+          <t>A 7828-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3737,14 +3774,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44616</v>
+        <v>44608</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3757,7 +3794,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3800,7 +3837,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24414-2022</t>
+          <t>A 9271-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3814,10 +3851,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44726</v>
+        <v>44616</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3830,7 +3867,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3873,7 +3910,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 53910-2022</t>
+          <t>A 24414-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3887,10 +3924,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44880</v>
+        <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3903,7 +3940,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3946,7 +3983,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 63739-2021</t>
+          <t>A 53910-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3960,10 +3997,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44509</v>
+        <v>44880</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3976,7 +4013,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4019,7 +4056,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 67179-2021</t>
+          <t>A 63739-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4033,10 +4070,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44523</v>
+        <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4049,7 +4086,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4092,7 +4129,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5758-2022</t>
+          <t>A 67179-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4106,10 +4143,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44596</v>
+        <v>44523</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4121,13 +4158,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4170,7 +4202,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31251-2022</t>
+          <t>A 5758-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4184,10 +4216,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44771</v>
+        <v>44596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4199,8 +4231,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4243,7 +4280,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10765-2022</t>
+          <t>A 31251-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4257,10 +4294,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44627</v>
+        <v>44771</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4273,7 +4310,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4316,7 +4353,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51296-2022</t>
+          <t>A 10765-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4330,10 +4367,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44868</v>
+        <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4346,7 +4383,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4389,7 +4426,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29507-2022</t>
+          <t>A 51296-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4403,10 +4440,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44753</v>
+        <v>44868</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4418,13 +4455,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4467,7 +4499,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26154-2022</t>
+          <t>A 29507-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4477,14 +4509,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44735</v>
+        <v>44753</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4498,11 +4530,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4545,7 +4577,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 53913-2022</t>
+          <t>A 26154-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4555,14 +4587,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44880</v>
+        <v>44735</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4574,8 +4606,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4618,7 +4655,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2834-2022</t>
+          <t>A 53913-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4632,10 +4669,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44581</v>
+        <v>44880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4648,7 +4685,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4691,7 +4728,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 66111-2021</t>
+          <t>A 2834-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4705,10 +4742,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44517</v>
+        <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4721,7 +4758,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4764,7 +4801,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33033-2022</t>
+          <t>A 66111-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4778,10 +4815,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44785</v>
+        <v>44517</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4793,13 +4830,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4842,7 +4874,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50060-2022</t>
+          <t>A 33033-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4856,10 +4888,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44865</v>
+        <v>44785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4871,8 +4903,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4915,7 +4952,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29520-2022</t>
+          <t>A 50060-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4929,10 +4966,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44753</v>
+        <v>44865</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4944,13 +4981,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4993,7 +5025,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7289-2022</t>
+          <t>A 29520-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5007,10 +5039,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44606</v>
+        <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5022,8 +5054,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5066,7 +5103,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 67198-2021</t>
+          <t>A 7289-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5080,10 +5117,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44523</v>
+        <v>44606</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5096,7 +5133,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5139,7 +5176,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 72240-2021</t>
+          <t>A 67198-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5153,10 +5190,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44544</v>
+        <v>44523</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5169,7 +5206,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5212,7 +5249,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6947-2025</t>
+          <t>A 72240-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5222,14 +5259,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45701</v>
+        <v>44544</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5241,13 +5278,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5290,7 +5322,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23451-2024</t>
+          <t>A 6947-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5300,14 +5332,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45453</v>
+        <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5319,8 +5351,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5363,7 +5400,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34427-2024</t>
+          <t>A 23451-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5373,14 +5410,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45525</v>
+        <v>45453</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5392,13 +5429,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5441,7 +5473,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 50635-2023</t>
+          <t>A 34427-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5451,14 +5483,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45217</v>
+        <v>45525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5470,8 +5502,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5514,7 +5551,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39213-2023</t>
+          <t>A 50635-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5528,10 +5565,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45166</v>
+        <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5543,13 +5580,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5592,7 +5624,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7273-2023</t>
+          <t>A 39213-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5606,10 +5638,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44970</v>
+        <v>45166</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5621,8 +5653,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5665,7 +5702,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22619-2025</t>
+          <t>A 7273-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5679,10 +5716,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45789</v>
+        <v>44970</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5694,13 +5731,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5743,7 +5775,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28327-2022</t>
+          <t>A 22619-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5757,10 +5789,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44747</v>
+        <v>45789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5772,8 +5804,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5816,7 +5853,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53573-2024</t>
+          <t>A 28327-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5830,10 +5867,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45614</v>
+        <v>44747</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5846,7 +5883,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5889,7 +5926,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61896-2025</t>
+          <t>A 53573-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5903,10 +5940,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46003</v>
+        <v>45614</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5919,7 +5956,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5962,7 +5999,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28271-2024</t>
+          <t>A 61896-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5976,10 +6013,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45477</v>
+        <v>46003</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5992,7 +6029,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6035,7 +6072,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21745-2024</t>
+          <t>A 28271-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6049,10 +6086,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45442</v>
+        <v>45477</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6065,7 +6102,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6108,7 +6145,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22362-2024</t>
+          <t>A 21745-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6122,10 +6159,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45446</v>
+        <v>45442</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6138,7 +6175,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6181,7 +6218,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18439-2025</t>
+          <t>A 22362-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6195,10 +6232,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45762</v>
+        <v>45446</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6210,13 +6247,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6259,7 +6291,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39748-2025</t>
+          <t>A 18439-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6273,10 +6305,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45891</v>
+        <v>45762</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6290,11 +6322,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6337,7 +6369,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30853-2025</t>
+          <t>A 39748-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6351,10 +6383,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45831</v>
+        <v>45891</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6366,8 +6398,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6410,7 +6447,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29188-2025</t>
+          <t>A 30853-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6424,10 +6461,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45821</v>
+        <v>45831</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6440,7 +6477,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6483,7 +6520,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40080-2025</t>
+          <t>A 29188-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6497,10 +6534,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45894</v>
+        <v>45821</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6513,7 +6550,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6556,7 +6593,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40744-2025</t>
+          <t>A 40080-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6570,10 +6607,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45897</v>
+        <v>45894</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6585,13 +6622,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6634,7 +6666,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 827-2026</t>
+          <t>A 40744-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6648,10 +6680,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46030</v>
+        <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6663,8 +6695,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6707,7 +6744,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46530-2023</t>
+          <t>A 827-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6721,10 +6758,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45197</v>
+        <v>46030</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6736,13 +6773,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6785,7 +6817,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42441-2025</t>
+          <t>A 46530-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6799,10 +6831,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45905</v>
+        <v>45197</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6812,6 +6844,11 @@
       <c r="G73" t="inlineStr">
         <is>
           <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -6858,7 +6895,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 73267-2021</t>
+          <t>A 42441-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6872,10 +6909,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44550</v>
+        <v>45905</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6888,7 +6925,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6931,7 +6968,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42572-2025</t>
+          <t>A 73267-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6945,10 +6982,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45905</v>
+        <v>44550</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6961,7 +6998,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>12.5</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7004,7 +7041,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26037-2023</t>
+          <t>A 42572-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7018,10 +7055,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45091</v>
+        <v>45905</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7034,7 +7071,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>12.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7077,7 +7114,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8952-2024</t>
+          <t>A 26037-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7091,10 +7128,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45355</v>
+        <v>45091</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7107,7 +7144,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7150,7 +7187,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25462-2025</t>
+          <t>A 8952-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7164,10 +7201,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45802</v>
+        <v>45355</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7179,13 +7216,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7228,7 +7260,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35335-2024</t>
+          <t>A 25462-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7242,10 +7274,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45530</v>
+        <v>45802</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7259,11 +7291,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7306,7 +7338,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42370-2025</t>
+          <t>A 35335-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7316,14 +7348,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45905</v>
+        <v>45530</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7341,7 +7373,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7384,7 +7416,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5971-2026</t>
+          <t>A 42370-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7394,14 +7426,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46052</v>
+        <v>45905</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7413,8 +7445,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7457,7 +7494,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35863-2023</t>
+          <t>A 5971-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7471,10 +7508,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45148</v>
+        <v>46052</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7484,11 +7521,6 @@
       <c r="G82" t="inlineStr">
         <is>
           <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -7535,7 +7567,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46868-2025</t>
+          <t>A 35863-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7549,10 +7581,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45929</v>
+        <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7564,8 +7596,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7608,7 +7645,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48647-2024</t>
+          <t>A 46868-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7622,10 +7659,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45593</v>
+        <v>45929</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7638,7 +7675,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7681,7 +7718,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47893-2025</t>
+          <t>A 48647-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7695,10 +7732,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45932</v>
+        <v>45593</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7711,7 +7748,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7754,7 +7791,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14382-2023</t>
+          <t>A 47893-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7764,14 +7801,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45012</v>
+        <v>45932</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7783,13 +7820,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7832,7 +7864,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47917-2025</t>
+          <t>A 14382-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7842,14 +7874,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45932</v>
+        <v>45012</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7861,8 +7893,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7905,7 +7942,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47940-2025</t>
+          <t>A 47917-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7922,7 +7959,7 @@
         <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7935,7 +7972,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7978,7 +8015,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20244-2023</t>
+          <t>A 47940-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7992,10 +8029,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45055</v>
+        <v>45932</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8008,7 +8045,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8051,7 +8088,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11765-2025</t>
+          <t>A 20244-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8065,10 +8102,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45727</v>
+        <v>45055</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8080,13 +8117,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8129,7 +8161,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51123-2025</t>
+          <t>A 11765-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8143,10 +8175,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45947</v>
+        <v>45727</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8158,8 +8190,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8202,7 +8239,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20862-2024</t>
+          <t>A 51123-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8216,10 +8253,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45439</v>
+        <v>45947</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8232,7 +8269,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>9.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8275,7 +8312,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10987-2026</t>
+          <t>A 20862-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8289,10 +8326,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46079</v>
+        <v>45439</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8304,13 +8341,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8353,7 +8385,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2812-2023</t>
+          <t>A 10987-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8367,10 +8399,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44944</v>
+        <v>46079</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8382,8 +8414,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8426,7 +8463,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26869-2024</t>
+          <t>A 2812-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8436,14 +8473,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45470</v>
+        <v>44944</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8455,13 +8492,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8504,7 +8536,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 6909-2025</t>
+          <t>A 26869-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8518,10 +8550,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45701</v>
+        <v>45470</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8539,7 +8571,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8582,7 +8614,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9693-2025</t>
+          <t>A 6909-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8592,14 +8624,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45716</v>
+        <v>45701</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8617,7 +8649,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8660,7 +8692,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12086-2026</t>
+          <t>A 9693-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8670,14 +8702,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46086</v>
+        <v>45716</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8695,7 +8727,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8738,7 +8770,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6118-2024</t>
+          <t>A 12086-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8748,14 +8780,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45337</v>
+        <v>46086</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8767,8 +8799,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8811,7 +8848,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13198-2024</t>
+          <t>A 6118-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8825,10 +8862,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45386</v>
+        <v>45337</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8841,7 +8878,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8884,7 +8921,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 64121-2023</t>
+          <t>A 13198-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8894,14 +8931,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45279</v>
+        <v>45386</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8914,7 +8951,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.1</v>
+        <v>4.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8957,7 +8994,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33218-2023</t>
+          <t>A 64121-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8967,14 +9004,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45127</v>
+        <v>45279</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8986,13 +9023,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9035,7 +9067,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33224-2023</t>
+          <t>A 33218-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9052,7 +9084,7 @@
         <v>45127</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9070,7 +9102,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9113,7 +9145,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16885-2025</t>
+          <t>A 33224-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9127,10 +9159,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45755</v>
+        <v>45127</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9142,8 +9174,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>7.1</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9186,7 +9223,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27995-2024</t>
+          <t>A 16885-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9200,10 +9237,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45476</v>
+        <v>45755</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9216,7 +9253,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.8</v>
+        <v>7.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9259,7 +9296,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 55433-2025</t>
+          <t>A 27995-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9273,10 +9310,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45971</v>
+        <v>45476</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9289,7 +9326,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>14.2</v>
+        <v>3.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9332,7 +9369,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9524-2024</t>
+          <t>A 55433-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9342,14 +9379,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45359</v>
+        <v>45971</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9361,13 +9398,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>14.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9410,7 +9442,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 65915-2021</t>
+          <t>A 9524-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9420,14 +9452,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44517</v>
+        <v>45359</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9439,8 +9471,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>17.2</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9483,7 +9520,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16109-2026</t>
+          <t>A 65915-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9497,10 +9534,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46108</v>
+        <v>44517</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9512,13 +9549,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>17.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9561,7 +9593,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39407-2024</t>
+          <t>A 16109-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9575,10 +9607,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45551</v>
+        <v>46108</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9590,8 +9622,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9634,7 +9671,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17519-2024</t>
+          <t>A 39407-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9648,10 +9685,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45415</v>
+        <v>45551</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9663,13 +9700,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9712,7 +9744,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 59298-2025</t>
+          <t>A 17519-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9726,10 +9758,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45988</v>
+        <v>45415</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9741,8 +9773,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9785,7 +9822,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59090-2025</t>
+          <t>A 59298-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9802,7 +9839,7 @@
         <v>45988</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9815,7 +9852,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9858,7 +9895,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 59933-2025</t>
+          <t>A 59090-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9872,10 +9909,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45993</v>
+        <v>45988</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9887,13 +9924,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9936,7 +9968,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 59919-2025</t>
+          <t>A 59933-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9953,7 +9985,7 @@
         <v>45993</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9971,7 +10003,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10014,7 +10046,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 17897-2026</t>
+          <t>A 59919-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10028,10 +10060,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46122</v>
+        <v>45993</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10045,11 +10077,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10092,7 +10124,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 17720-2026</t>
+          <t>A 17897-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10106,10 +10138,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10121,8 +10153,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10165,7 +10202,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59955-2025</t>
+          <t>A 17720-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10179,10 +10216,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45993</v>
+        <v>46121</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10194,13 +10231,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10243,7 +10275,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 18285-2026</t>
+          <t>A 59955-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10257,10 +10289,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46126</v>
+        <v>45993</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10272,8 +10304,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10316,7 +10353,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 18916-2026</t>
+          <t>A 18285-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10330,10 +10367,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46129</v>
+        <v>46126</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10345,13 +10382,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10394,7 +10426,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 58688-2023</t>
+          <t>A 18916-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10408,10 +10440,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45251</v>
+        <v>46129</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10423,8 +10455,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10467,7 +10504,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 35855-2023</t>
+          <t>A 58688-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10481,10 +10518,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45148</v>
+        <v>45251</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10496,13 +10533,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10545,7 +10577,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19079-2026</t>
+          <t>A 35855-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10559,10 +10591,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46132</v>
+        <v>45148</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10574,8 +10606,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>10.1</v>
+        <v>0.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10618,7 +10655,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32796-2023</t>
+          <t>A 19079-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10632,10 +10669,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45124</v>
+        <v>46132</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10647,13 +10684,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>5.7</v>
+        <v>10.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10696,7 +10728,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32822-2023</t>
+          <t>A 32796-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10713,7 +10745,7 @@
         <v>45124</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10731,7 +10763,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10774,7 +10806,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 34849-2024</t>
+          <t>A 32822-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10784,14 +10816,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45527</v>
+        <v>45124</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10805,11 +10837,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10852,7 +10884,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19823-2026</t>
+          <t>A 34849-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10862,14 +10894,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46135</v>
+        <v>45527</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10881,8 +10913,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10925,7 +10962,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31831-2025</t>
+          <t>A 19823-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10939,10 +10976,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45834</v>
+        <v>46135</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10955,7 +10992,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10998,7 +11035,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34886-2024</t>
+          <t>A 31831-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11012,10 +11049,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45527</v>
+        <v>45834</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11027,13 +11064,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>6.3</v>
+        <v>0.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11076,7 +11108,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31968-2025</t>
+          <t>A 34886-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11090,10 +11122,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45835</v>
+        <v>45527</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11105,8 +11137,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11149,7 +11186,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 58121-2024</t>
+          <t>A 31968-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11163,10 +11200,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45632</v>
+        <v>45835</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11179,7 +11216,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11222,7 +11259,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 53678-2025</t>
+          <t>A 58121-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11236,10 +11273,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45960</v>
+        <v>45632</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11252,7 +11289,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11295,7 +11332,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 18229-2025</t>
+          <t>A 53678-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11309,10 +11346,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45761</v>
+        <v>45960</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11325,7 +11362,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11368,7 +11405,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 54170-2022</t>
+          <t>A 18229-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11382,10 +11419,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44881</v>
+        <v>45761</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11398,7 +11435,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11441,7 +11478,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29427-2024</t>
+          <t>A 54170-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11455,10 +11492,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45483</v>
+        <v>44881</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11471,7 +11508,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11514,7 +11551,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 15563-2022</t>
+          <t>A 29427-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11528,10 +11565,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44662</v>
+        <v>45483</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11587,7 +11624,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11196-2024</t>
+          <t>A 15563-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11601,10 +11638,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45371</v>
+        <v>44662</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11617,7 +11654,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11660,7 +11697,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 46300-2022</t>
+          <t>A 11196-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11674,10 +11711,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44847</v>
+        <v>45371</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11690,7 +11727,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11733,7 +11770,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56280-2023</t>
+          <t>A 46300-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11747,10 +11784,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45241</v>
+        <v>44847</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11763,7 +11800,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11806,7 +11843,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 60850-2025</t>
+          <t>A 56280-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11820,10 +11857,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45999</v>
+        <v>45241</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11836,7 +11873,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11879,7 +11916,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 47734-2025</t>
+          <t>A 60850-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11893,10 +11930,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45931</v>
+        <v>45999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11908,13 +11945,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11957,7 +11989,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 10989-2025</t>
+          <t>A 47734-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11971,10 +12003,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45723</v>
+        <v>45931</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11986,8 +12018,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12030,7 +12067,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 65062-2023</t>
+          <t>A 10989-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12044,10 +12081,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45287</v>
+        <v>45723</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12059,13 +12096,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>11.3</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12108,7 +12140,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58714-2021</t>
+          <t>A 65062-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12122,10 +12154,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44489</v>
+        <v>45287</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12137,8 +12169,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>11.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12181,7 +12218,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 67617-2021</t>
+          <t>A 58714-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12195,10 +12232,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44524</v>
+        <v>44489</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12211,7 +12248,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12254,7 +12291,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 55835-2024</t>
+          <t>A 67617-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12268,10 +12305,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45623</v>
+        <v>44524</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12284,7 +12321,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12327,7 +12364,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 30859-2024</t>
+          <t>A 55835-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12341,10 +12378,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45497</v>
+        <v>45623</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12357,7 +12394,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12400,7 +12437,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 35831-2023</t>
+          <t>A 30859-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12414,10 +12451,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45148</v>
+        <v>45497</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12429,13 +12466,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12478,7 +12510,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 22582-2024</t>
+          <t>A 35831-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12488,14 +12520,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45447</v>
+        <v>45148</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12509,11 +12541,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12556,7 +12588,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 7297-2023</t>
+          <t>A 22582-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12566,14 +12598,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44970</v>
+        <v>45447</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12585,8 +12617,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12629,7 +12666,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 15663-2024</t>
+          <t>A 7297-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12639,14 +12676,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45404</v>
+        <v>44970</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12659,7 +12696,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12702,7 +12739,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21106-2026</t>
+          <t>A 15663-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12712,14 +12749,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46146</v>
+        <v>45404</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12731,13 +12768,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>8.1</v>
+        <v>0.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12780,7 +12812,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 21081-2026</t>
+          <t>A 21106-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12797,7 +12829,7 @@
         <v>46146</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12815,7 +12847,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>14.8</v>
+        <v>8.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12858,7 +12890,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 21137-2026</t>
+          <t>A 21081-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12875,7 +12907,7 @@
         <v>46146</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12887,8 +12919,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>3.4</v>
+        <v>14.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12931,7 +12968,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1409-2025</t>
+          <t>A 21137-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12945,10 +12982,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45667</v>
+        <v>46146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12961,7 +12998,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13004,7 +13041,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 60893-2025</t>
+          <t>A 1409-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13018,10 +13055,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45999</v>
+        <v>45667</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13034,7 +13071,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13077,7 +13114,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21146-2026</t>
+          <t>A 60893-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13091,10 +13128,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46146</v>
+        <v>45999</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13107,7 +13144,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13150,7 +13187,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 21634-2026</t>
+          <t>A 21146-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13164,10 +13201,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13180,7 +13217,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13223,7 +13260,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22192-2026</t>
+          <t>A 21634-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13237,10 +13274,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13253,7 +13290,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13296,7 +13333,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22222-2026</t>
+          <t>A 22192-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13313,7 +13350,7 @@
         <v>46153</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13326,7 +13363,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13369,7 +13406,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22221-2026</t>
+          <t>A 22222-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13386,7 +13423,7 @@
         <v>46153</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13399,7 +13436,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13442,7 +13479,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 63318-2023</t>
+          <t>A 22221-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13456,10 +13493,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45274</v>
+        <v>46153</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13472,7 +13509,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13515,7 +13552,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 19996-2022</t>
+          <t>A 63318-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13529,10 +13566,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44697</v>
+        <v>45274</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13545,7 +13582,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13588,7 +13625,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 21836-2025</t>
+          <t>A 19996-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13602,10 +13639,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45784</v>
+        <v>44697</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13618,7 +13655,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13661,7 +13698,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 60045-2022</t>
+          <t>A 21836-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13675,10 +13712,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44902</v>
+        <v>45784</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13691,7 +13728,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13734,7 +13771,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 10383-2023</t>
+          <t>A 60045-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13748,10 +13785,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44987</v>
+        <v>44902</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13764,7 +13801,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13807,7 +13844,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 23505-2026</t>
+          <t>A 10383-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13821,10 +13858,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46163</v>
+        <v>44987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13836,13 +13873,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13885,7 +13917,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 23516-2026</t>
+          <t>A 23505-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13902,7 +13934,7 @@
         <v>46163</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13920,7 +13952,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13963,7 +13995,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 17135-2025</t>
+          <t>A 23516-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13977,10 +14009,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45755</v>
+        <v>46163</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13992,8 +14024,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>10.3</v>
+        <v>3.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14036,7 +14073,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 29852-2022</t>
+          <t>A 17135-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14050,10 +14087,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44756</v>
+        <v>45755</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14066,7 +14103,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.9</v>
+        <v>10.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14109,7 +14146,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 70214-2021</t>
+          <t>A 29852-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14123,10 +14160,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44535</v>
+        <v>44756</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14139,7 +14176,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14182,7 +14219,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 56748-2022</t>
+          <t>A 70214-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14196,10 +14233,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44894</v>
+        <v>44535</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14211,13 +14248,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14260,7 +14292,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 28242-2024</t>
+          <t>A 56748-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14274,10 +14306,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45477</v>
+        <v>44894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14289,8 +14321,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14333,7 +14370,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 55137-2023</t>
+          <t>A 28242-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14347,10 +14384,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45237</v>
+        <v>45477</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14363,7 +14400,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14406,7 +14443,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 73264-2021</t>
+          <t>A 55137-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14420,10 +14457,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44550</v>
+        <v>45237</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14436,7 +14473,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14479,7 +14516,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 73266-2021</t>
+          <t>A 73264-2021</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14496,7 +14533,7 @@
         <v>44550</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14509,7 +14546,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>7.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14552,7 +14589,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 7299-2023</t>
+          <t>A 73266-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14566,10 +14603,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44970</v>
+        <v>44550</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14582,7 +14619,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14625,7 +14662,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 26325-2026</t>
+          <t>A 7299-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14639,10 +14676,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46182</v>
+        <v>44970</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14655,7 +14692,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14698,7 +14735,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 26104-2026</t>
+          <t>A 26325-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14712,10 +14749,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14728,7 +14765,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14771,7 +14808,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 26129-2026</t>
+          <t>A 26104-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14788,7 +14825,7 @@
         <v>46181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14801,7 +14838,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14844,7 +14881,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 27075-2026</t>
+          <t>A 26129-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14858,10 +14895,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46186</v>
+        <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14874,7 +14911,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14917,7 +14954,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 27080-2026</t>
+          <t>A 27075-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14934,7 +14971,7 @@
         <v>46186</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14947,7 +14984,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14990,7 +15027,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 27076-2026</t>
+          <t>A 27080-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15007,7 +15044,7 @@
         <v>46186</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15020,7 +15057,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15063,7 +15100,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 27252-2026</t>
+          <t>A 27076-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15077,10 +15114,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46188</v>
+        <v>46186</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15093,7 +15130,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15136,7 +15173,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 28517-2024</t>
+          <t>A 27252-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15150,10 +15187,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45478</v>
+        <v>46188</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15165,13 +15202,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15214,7 +15246,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 14988-2024</t>
+          <t>A 28517-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15228,10 +15260,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45399</v>
+        <v>45478</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15243,8 +15275,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15287,7 +15324,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 48630-2024</t>
+          <t>A 14988-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15301,10 +15338,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45593</v>
+        <v>45399</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15317,7 +15354,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15360,7 +15397,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 62922-2023</t>
+          <t>A 48630-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15374,10 +15411,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45272</v>
+        <v>45593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15390,7 +15427,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15433,7 +15470,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 23020-2022</t>
+          <t>A 62922-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15447,10 +15484,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44719</v>
+        <v>45272</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15463,7 +15500,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15506,7 +15543,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 53074-2022</t>
+          <t>A 23020-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15520,10 +15557,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44876</v>
+        <v>44719</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15536,7 +15573,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15579,7 +15616,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35850-2023</t>
+          <t>A 53074-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15593,10 +15630,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45148</v>
+        <v>44876</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15608,13 +15645,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15657,7 +15689,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 2278-2022</t>
+          <t>A 35850-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15671,10 +15703,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44578</v>
+        <v>45148</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15688,11 +15720,11 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15735,7 +15767,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32680-2023</t>
+          <t>A 2278-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15749,10 +15781,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45121</v>
+        <v>44578</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15766,11 +15798,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15813,7 +15845,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 29116-2026</t>
+          <t>A 32680-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15827,10 +15859,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46201</v>
+        <v>45121</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15842,8 +15874,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15886,7 +15923,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 29265-2026</t>
+          <t>A 29116-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15900,10 +15937,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46202</v>
+        <v>46201</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15916,7 +15953,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15959,7 +15996,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 61457-2022</t>
+          <t>A 29265-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15973,10 +16010,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44916</v>
+        <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15989,7 +16026,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16032,7 +16069,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 40968-2022</t>
+          <t>A 61457-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16046,10 +16083,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44823</v>
+        <v>44916</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16062,7 +16099,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>16.5</v>
+        <v>4.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16105,7 +16142,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 12484-2022</t>
+          <t>A 40968-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16119,10 +16156,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44638</v>
+        <v>44823</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16135,7 +16172,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16178,7 +16215,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 19069-2025</t>
+          <t>A 12484-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16192,10 +16229,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45765</v>
+        <v>44638</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16208,7 +16245,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16251,7 +16288,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 30380-2026</t>
+          <t>A 19069-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16265,10 +16302,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46209</v>
+        <v>45765</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16281,7 +16318,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16324,7 +16361,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 30374-2026</t>
+          <t>A 30380-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16341,7 +16378,7 @@
         <v>46209</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16354,7 +16391,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16397,7 +16434,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 61231-2022</t>
+          <t>A 30374-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16411,10 +16448,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44915</v>
+        <v>46209</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16427,7 +16464,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16470,7 +16507,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 2818-2022</t>
+          <t>A 61231-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16484,10 +16521,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44581</v>
+        <v>44915</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16500,7 +16537,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>11</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16543,7 +16580,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 7919-2023</t>
+          <t>A 2818-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16557,10 +16594,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44973</v>
+        <v>44581</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16573,7 +16610,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>11</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16616,7 +16653,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 33222-2023</t>
+          <t>A 7919-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16630,10 +16667,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45127</v>
+        <v>44973</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16645,13 +16682,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16694,7 +16726,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 33229-2023</t>
+          <t>A 33222-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16711,7 +16743,7 @@
         <v>45127</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16729,7 +16761,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16772,7 +16804,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 15553-2022</t>
+          <t>A 33229-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16786,10 +16818,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44662</v>
+        <v>45127</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16801,8 +16833,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16845,7 +16882,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35940-2024</t>
+          <t>A 15553-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16859,10 +16896,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45533</v>
+        <v>44662</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16875,7 +16912,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16918,7 +16955,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 48590-2024</t>
+          <t>A 35940-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16928,14 +16965,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45593</v>
+        <v>45533</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16947,13 +16984,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16996,7 +17028,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 12320-2024</t>
+          <t>A 48590-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17010,10 +17042,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45378</v>
+        <v>45593</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17031,7 +17063,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>7.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17091,7 +17123,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17164,7 +17196,7 @@
         <v>45439</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17237,7 +17269,7 @@
         <v>46222</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17310,7 +17342,7 @@
         <v>44542</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17383,7 +17415,7 @@
         <v>45078</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17456,7 +17488,7 @@
         <v>45124</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17534,7 +17566,7 @@
         <v>45105</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17607,7 +17639,7 @@
         <v>45085</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17680,7 +17712,7 @@
         <v>44812</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17753,7 +17785,7 @@
         <v>45526</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17831,7 +17863,7 @@
         <v>45127</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17909,7 +17941,7 @@
         <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17982,7 +18014,7 @@
         <v>46245</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18060,7 +18092,7 @@
         <v>46245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18138,7 +18170,7 @@
         <v>46289</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18211,7 +18243,7 @@
         <v>46288</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18284,7 +18316,7 @@
         <v>46288</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18357,7 +18389,7 @@
         <v>46245</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18435,7 +18467,7 @@
         <v>46245</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18513,7 +18545,7 @@
         <v>45709</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18591,7 +18623,7 @@
         <v>45237</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18664,7 +18696,7 @@
         <v>45099</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18737,7 +18769,7 @@
         <v>46251</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18815,7 +18847,7 @@
         <v>46251</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18893,7 +18925,7 @@
         <v>45632</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18966,7 +18998,7 @@
         <v>46255</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19039,7 +19071,7 @@
         <v>44902</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19112,7 +19144,7 @@
         <v>45723</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19185,7 +19217,7 @@
         <v>46296</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19258,7 +19290,7 @@
         <v>44581</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19331,7 +19363,7 @@
         <v>45062</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19409,7 +19441,7 @@
         <v>45124</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19487,7 +19519,7 @@
         <v>45532</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19560,7 +19592,7 @@
         <v>45075</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19638,7 +19670,7 @@
         <v>45614</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19711,7 +19743,7 @@
         <v>44796</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19784,7 +19816,7 @@
         <v>44936</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19857,7 +19889,7 @@
         <v>44916</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19930,7 +19962,7 @@
         <v>45127</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20008,7 +20040,7 @@
         <v>45049</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20081,7 +20113,7 @@
         <v>45530</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20159,7 +20191,7 @@
         <v>44834</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20237,7 +20269,7 @@
         <v>45266</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20315,7 +20347,7 @@
         <v>45266</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20393,7 +20425,7 @@
         <v>44606</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20471,7 +20503,7 @@
         <v>44901</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20549,7 +20581,7 @@
         <v>44901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20627,7 +20659,7 @@
         <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20705,7 +20737,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20783,7 +20815,7 @@
         <v>44606</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20861,7 +20893,7 @@
         <v>44606</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20939,7 +20971,7 @@
         <v>45834</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 66072-2021</t>
+          <t>A 18094-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,14 +850,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44517</v>
+        <v>46125</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -875,19 +875,19 @@
         </is>
       </c>
       <c r="I4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -911,9 +911,122 @@
         <v>4</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Blackticka
+Fjällig taggsvamp s.str.
+Brandticka
+Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18094-2026 artfynd.xlsx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18094-2026 karta.png", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18094-2026 georefererad karta.tif", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18094-2026 FSC-klagomål.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18094-2026 FSC-klagomål mail.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18094-2026 tillsynsbegäran.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18094-2026 tillsynsbegäran mail.docx", "A 18094-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 66072-2021</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44517</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Skogsklocka
@@ -921,112 +1034,112 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 66072-2021 artfynd.xlsx", "A 66072-2021")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 66072-2021 karta.png", "A 66072-2021")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 66072-2021 georefererad karta.tif", "A 66072-2021")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 66072-2021 FSC-klagomål.docx", "A 66072-2021")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 66072-2021 FSC-klagomål mail.docx", "A 66072-2021")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 66072-2021 tillsynsbegäran.docx", "A 66072-2021")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 66072-2021 tillsynsbegäran mail.docx", "A 66072-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 34758-2024</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45526</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="E6" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>6.2</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>6</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp
 Fjällig taggsvamp s.str.
@@ -1034,148 +1147,35 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 34758-2024 artfynd.xlsx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 34758-2024 karta.png", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 34758-2024 georefererad karta.tif", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 34758-2024 FSC-klagomål.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 34758-2024 FSC-klagomål mail.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 34758-2024 tillsynsbegäran.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 34758-2024 tillsynsbegäran mail.docx", "A 34758-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 18094-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46125</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Blackticka
-Fjällig taggsvamp s.str.
-Brandticka
-Mörk husmossa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18094-2026 artfynd.xlsx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18094-2026 karta.png", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18094-2026 georefererad karta.tif", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18094-2026 FSC-klagomål.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18094-2026 FSC-klagomål mail.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18094-2026 tillsynsbegäran.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18094-2026 tillsynsbegäran mail.docx", "A 18094-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 63799-2023</t>
+          <t>A 12854-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45278</v>
+        <v>46092</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>12.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1364,488 +1364,488 @@
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ävjepilört
+Springkorn
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12854-2026 artfynd.xlsx", "A 12854-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12854-2026 karta.png", "A 12854-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12854-2026 georefererad karta.tif", "A 12854-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12854-2026 FSC-klagomål.docx", "A 12854-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12854-2026 FSC-klagomål mail.docx", "A 12854-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12854-2026 tillsynsbegäran.docx", "A 12854-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12854-2026 tillsynsbegäran mail.docx", "A 12854-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 63799-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåtryffel
 Svart trolldruva
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 63799-2023 artfynd.xlsx", "A 63799-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 63799-2023 karta.png", "A 63799-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 63799-2023 georefererad karta.tif", "A 63799-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 63799-2023 FSC-klagomål.docx", "A 63799-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 63799-2023 FSC-klagomål mail.docx", "A 63799-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 63799-2023 tillsynsbegäran.docx", "A 63799-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 63799-2023 tillsynsbegäran mail.docx", "A 63799-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 18103-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Gransotdyna
+Mörk husmossa
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18103-2026 artfynd.xlsx", "A 18103-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18103-2026 karta.png", "A 18103-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18103-2026 georefererad karta.tif", "A 18103-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18103-2026 FSC-klagomål.docx", "A 18103-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18103-2026 FSC-klagomål mail.docx", "A 18103-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18103-2026 tillsynsbegäran.docx", "A 18103-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18103-2026 tillsynsbegäran mail.docx", "A 18103-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 14114-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44651</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril
+Göktyta
+Sotnätfjäril</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 14114-2022 artfynd.xlsx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 14114-2022 karta.png", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 14114-2022 georefererad karta.tif", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 14114-2022 FSC-klagomål.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 14114-2022 FSC-klagomål mail.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 14114-2022 tillsynsbegäran.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 14114-2022 tillsynsbegäran mail.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 14114-2022 prioriterade fågelarter.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 5766-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>46051</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.2</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Nästrot
 Svart trolldruva
 Blåsippa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 5766-2026 artfynd.xlsx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 5766-2026 karta.png", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 5766-2026 georefererad karta.tif", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 5766-2026 FSC-klagomål.docx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 5766-2026 FSC-klagomål mail.docx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 5766-2026 tillsynsbegäran.docx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 5766-2026 tillsynsbegäran mail.docx", "A 5766-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 14114-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44651</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril
-Göktyta
-Sotnätfjäril</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 14114-2022 artfynd.xlsx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 14114-2022 karta.png", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 14114-2022 georefererad karta.tif", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 14114-2022 FSC-klagomål.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 14114-2022 FSC-klagomål mail.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 14114-2022 tillsynsbegäran.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 14114-2022 tillsynsbegäran mail.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 14114-2022 prioriterade fågelarter.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 12854-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ävjepilört
-Springkorn
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12854-2026 artfynd.xlsx", "A 12854-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12854-2026 karta.png", "A 12854-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12854-2026 georefererad karta.tif", "A 12854-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12854-2026 FSC-klagomål.docx", "A 12854-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12854-2026 FSC-klagomål mail.docx", "A 12854-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12854-2026 tillsynsbegäran.docx", "A 12854-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12854-2026 tillsynsbegäran mail.docx", "A 12854-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 18103-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46125</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Gransotdyna
-Mörk husmossa
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18103-2026 artfynd.xlsx", "A 18103-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18103-2026 karta.png", "A 18103-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18103-2026 georefererad karta.tif", "A 18103-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18103-2026 FSC-klagomål.docx", "A 18103-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18103-2026 FSC-klagomål mail.docx", "A 18103-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18103-2026 tillsynsbegäran.docx", "A 18103-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18103-2026 tillsynsbegäran mail.docx", "A 18103-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44480</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 35334-2024</t>
+          <t>A 13208-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45530</v>
+        <v>45002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2304,13 +2304,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2350,42 +2345,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 13208-2023 artfynd.xlsx", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 13208-2023 karta.png", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 13208-2023 georefererad karta.tif", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 13208-2023 FSC-klagomål.docx", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 13208-2023 FSC-klagomål mail.docx", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 13208-2023 tillsynsbegäran.docx", "A 13208-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 13208-2023 tillsynsbegäran mail.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 13208-2023 prioriterade fågelarter.docx", "A 13208-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13208-2023</t>
+          <t>A 60736-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2399,10 +2398,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45002</v>
+        <v>44913</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2415,7 +2414,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2424,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2439,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2451,50 +2450,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 13208-2023 artfynd.xlsx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 13208-2023 karta.png", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 13208-2023 georefererad karta.tif", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 13208-2023 FSC-klagomål.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 13208-2023 FSC-klagomål mail.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 13208-2023 tillsynsbegäran.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 13208-2023 tillsynsbegäran mail.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 13208-2023 prioriterade fågelarter.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46620-2024</t>
+          <t>A 45484-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2508,10 +2507,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45583</v>
+        <v>45188</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2524,13 +2523,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2557,49 +2556,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 45484-2023 artfynd.xlsx", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 45484-2023 karta.png", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 45484-2023 georefererad karta.tif", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 45484-2023 FSC-klagomål.docx", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 45484-2023 FSC-klagomål mail.docx", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 45484-2023 tillsynsbegäran.docx", "A 45484-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 45484-2023 tillsynsbegäran mail.docx", "A 45484-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 35573-2023</t>
+          <t>A 67321-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2613,10 +2612,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45147</v>
+        <v>44523</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2628,13 +2627,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2670,46 +2664,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35573-2023 artfynd.xlsx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 67321-2021 artfynd.xlsx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35573-2023 karta.png", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 67321-2021 karta.png", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35573-2023 georefererad karta.tif", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 67321-2021 georefererad karta.tif", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35573-2023 FSC-klagomål.docx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 67321-2021 FSC-klagomål.docx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35573-2023 FSC-klagomål mail.docx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 67321-2021 FSC-klagomål mail.docx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35573-2023 tillsynsbegäran.docx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 67321-2021 tillsynsbegäran.docx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35573-2023 tillsynsbegäran mail.docx", "A 35573-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 67321-2021 tillsynsbegäran mail.docx", "A 67321-2021")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 67321-2021</t>
+          <t>A 31980-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2719,14 +2713,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44523</v>
+        <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2738,14 +2732,19 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2779,35 +2778,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 67321-2021 artfynd.xlsx", "A 67321-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 31980-2023 artfynd.xlsx", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 67321-2021 karta.png", "A 67321-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 31980-2023 karta.png", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 67321-2021 georefererad karta.tif", "A 67321-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 31980-2023 georefererad karta.tif", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 67321-2021 FSC-klagomål.docx", "A 67321-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 31980-2023 FSC-klagomål.docx", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 67321-2021 FSC-klagomål mail.docx", "A 67321-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 31980-2023 FSC-klagomål mail.docx", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 67321-2021 tillsynsbegäran.docx", "A 67321-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 31980-2023 tillsynsbegäran.docx", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 67321-2021 tillsynsbegäran mail.docx", "A 67321-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 31980-2023 tillsynsbegäran mail.docx", "A 31980-2023")</f>
         <v/>
       </c>
     </row>
@@ -2831,7 +2830,7 @@
         <v>44880</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2924,7 +2923,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 45484-2023</t>
+          <t>A 12320-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,14 +2933,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45188</v>
+        <v>45378</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2953,14 +2952,19 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2990,46 +2994,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 45484-2023 artfynd.xlsx", "A 45484-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12320-2024 artfynd.xlsx", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 45484-2023 karta.png", "A 45484-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12320-2024 karta.png", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 45484-2023 georefererad karta.tif", "A 45484-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12320-2024 georefererad karta.tif", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 45484-2023 FSC-klagomål.docx", "A 45484-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12320-2024 FSC-klagomål.docx", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 45484-2023 FSC-klagomål mail.docx", "A 45484-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12320-2024 FSC-klagomål mail.docx", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 45484-2023 tillsynsbegäran.docx", "A 45484-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12320-2024 tillsynsbegäran.docx", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 45484-2023 tillsynsbegäran mail.docx", "A 45484-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12320-2024 tillsynsbegäran mail.docx", "A 12320-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31980-2023</t>
+          <t>A 35334-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,14 +3043,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45119</v>
+        <v>45530</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,17 +3064,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3104,42 +3108,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 31980-2023 artfynd.xlsx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 31980-2023 karta.png", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 31980-2023 georefererad karta.tif", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 31980-2023 FSC-klagomål.docx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 31980-2023 FSC-klagomål mail.docx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 31980-2023 tillsynsbegäran.docx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 31980-2023 tillsynsbegäran mail.docx", "A 31980-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12320-2024</t>
+          <t>A 46620-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3149,14 +3153,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45378</v>
+        <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3168,13 +3172,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3207,49 +3206,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12320-2024 artfynd.xlsx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12320-2024 karta.png", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12320-2024 georefererad karta.tif", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12320-2024 FSC-klagomål.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12320-2024 FSC-klagomål mail.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12320-2024 tillsynsbegäran.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12320-2024 tillsynsbegäran mail.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60736-2022</t>
+          <t>A 35573-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3263,10 +3262,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44913</v>
+        <v>45147</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3278,8 +3277,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3288,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3303,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3319,39 +3323,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35573-2023 artfynd.xlsx", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35573-2023 karta.png", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35573-2023 georefererad karta.tif", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35573-2023 FSC-klagomål.docx", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35573-2023 FSC-klagomål mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35573-2023 tillsynsbegäran.docx", "A 35573-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35573-2023 tillsynsbegäran mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
         <v>46037</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>44549</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>44790</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44608</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44616</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>44880</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>44523</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>44771</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>44868</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>44753</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44735</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7289-2022</t>
+          <t>A 2834-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44606</v>
+        <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4801,7 +4801,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2834-2022</t>
+          <t>A 66111-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44581</v>
+        <v>44517</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4874,7 +4874,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 72240-2021</t>
+          <t>A 33033-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44544</v>
+        <v>44785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4903,8 +4903,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4947,7 +4952,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 66111-2021</t>
+          <t>A 50060-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4961,10 +4966,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44517</v>
+        <v>44865</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4977,7 +4982,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5020,7 +5025,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46530-2023</t>
+          <t>A 29520-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5034,10 +5039,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45197</v>
+        <v>44753</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5051,11 +5056,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5098,7 +5103,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 67198-2021</t>
+          <t>A 7289-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5112,10 +5117,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44523</v>
+        <v>44606</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5128,7 +5133,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5171,7 +5176,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33033-2022</t>
+          <t>A 67198-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5185,10 +5190,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44785</v>
+        <v>44523</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5200,13 +5205,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5249,7 +5249,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 50060-2022</t>
+          <t>A 72240-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44865</v>
+        <v>44544</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29520-2022</t>
+          <t>A 34427-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5410,14 +5410,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44753</v>
+        <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5431,11 +5431,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10996-2025</t>
+          <t>A 39213-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45723</v>
+        <v>45166</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5507,8 +5507,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5551,7 +5556,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16885-2025</t>
+          <t>A 50635-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5565,10 +5570,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45755</v>
+        <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5581,7 +5586,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5624,7 +5629,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35336-2024</t>
+          <t>A 7273-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5638,10 +5643,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45530</v>
+        <v>44970</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5653,13 +5658,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5702,7 +5702,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35940-2024</t>
+          <t>A 23451-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45533</v>
+        <v>45453</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5775,7 +5775,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26037-2023</t>
+          <t>A 28327-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45091</v>
+        <v>44747</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 71625-2021</t>
+          <t>A 53573-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44542</v>
+        <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5921,7 +5921,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33218-2023</t>
+          <t>A 18439-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45127</v>
+        <v>45762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5952,11 +5952,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5999,7 +5999,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61457-2022</t>
+          <t>A 46530-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44916</v>
+        <v>45197</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6028,8 +6028,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6072,7 +6077,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22619-2025</t>
+          <t>A 73267-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6086,10 +6091,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45789</v>
+        <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6101,13 +6106,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53074-2022</t>
+          <t>A 26037-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6164,10 +6164,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44876</v>
+        <v>45091</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28242-2024</t>
+          <t>A 35335-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45477</v>
+        <v>45530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6252,8 +6252,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6296,7 +6301,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28271-2024</t>
+          <t>A 48647-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6310,10 +6315,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45477</v>
+        <v>45593</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6326,7 +6331,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6369,7 +6374,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34786-2024</t>
+          <t>A 35863-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6383,10 +6388,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45526</v>
+        <v>45148</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6400,11 +6405,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6447,7 +6452,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29231-2023</t>
+          <t>A 14382-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6457,14 +6462,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45105</v>
+        <v>45012</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6476,8 +6481,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6520,7 +6530,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8952-2024</t>
+          <t>A 20862-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6534,10 +6544,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45355</v>
+        <v>45439</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6550,7 +6560,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6593,7 +6603,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56748-2022</t>
+          <t>A 2812-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6607,10 +6617,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44894</v>
+        <v>44944</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6622,13 +6632,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6671,7 +6676,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40080-2025</t>
+          <t>A 12086-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6681,14 +6686,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45894</v>
+        <v>46086</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6700,8 +6705,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6744,7 +6754,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39748-2025</t>
+          <t>A 6909-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6754,14 +6764,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45891</v>
+        <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6775,11 +6785,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6822,7 +6832,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29188-2025</t>
+          <t>A 9693-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6836,10 +6846,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45821</v>
+        <v>45716</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6851,8 +6861,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6895,7 +6910,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30853-2025</t>
+          <t>A 6118-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6909,10 +6924,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45831</v>
+        <v>45337</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6925,7 +6940,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6968,7 +6983,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40744-2025</t>
+          <t>A 13198-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6982,10 +6997,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45897</v>
+        <v>45386</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6997,13 +7012,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7046,7 +7056,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19323-2023</t>
+          <t>A 64121-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7056,14 +7066,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45049</v>
+        <v>45279</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7076,7 +7086,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7119,7 +7129,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 42441-2025</t>
+          <t>A 33218-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7133,10 +7143,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45905</v>
+        <v>45127</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7148,8 +7158,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7192,7 +7207,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32680-2023</t>
+          <t>A 33224-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7206,10 +7221,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45121</v>
+        <v>45127</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7227,7 +7242,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7270,7 +7285,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42572-2025</t>
+          <t>A 39748-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7284,10 +7299,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45905</v>
+        <v>45891</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7299,8 +7314,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>12.5</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7343,7 +7363,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25462-2025</t>
+          <t>A 16885-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7357,10 +7377,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45802</v>
+        <v>45755</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7372,13 +7392,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7421,7 +7436,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11765-2025</t>
+          <t>A 30853-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7435,10 +7450,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45727</v>
+        <v>45831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7450,13 +7465,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7499,7 +7509,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20244-2023</t>
+          <t>A 29188-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7513,10 +7523,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45055</v>
+        <v>45821</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7529,7 +7539,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7572,7 +7582,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35335-2024</t>
+          <t>A 40080-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7586,10 +7596,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45530</v>
+        <v>45894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7601,13 +7611,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7650,7 +7655,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 73267-2021</t>
+          <t>A 40744-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7664,10 +7669,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44550</v>
+        <v>45897</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7679,8 +7684,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7723,7 +7733,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26869-2024</t>
+          <t>A 27995-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7733,14 +7743,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45470</v>
+        <v>45476</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7752,13 +7762,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7801,7 +7806,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48630-2024</t>
+          <t>A 17135-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7815,10 +7820,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45593</v>
+        <v>45755</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7831,7 +7836,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7874,7 +7879,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 27995-2024</t>
+          <t>A 9524-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7884,14 +7889,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45476</v>
+        <v>45359</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7903,8 +7908,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7947,7 +7957,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 29427-2024</t>
+          <t>A 65915-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7961,10 +7971,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45483</v>
+        <v>44517</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7977,7 +7987,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.7</v>
+        <v>17.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8020,7 +8030,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23451-2024</t>
+          <t>A 39407-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8034,10 +8044,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45453</v>
+        <v>45551</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8050,7 +8060,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8093,7 +8103,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46868-2025</t>
+          <t>A 42441-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8107,10 +8117,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45929</v>
+        <v>45905</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8123,7 +8133,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8166,7 +8176,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34849-2024</t>
+          <t>A 17519-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8176,14 +8186,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45527</v>
+        <v>45415</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8201,7 +8211,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8244,7 +8254,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47893-2025</t>
+          <t>A 42572-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8258,10 +8268,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45932</v>
+        <v>45905</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8274,7 +8284,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8317,7 +8327,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47917-2025</t>
+          <t>A 28242-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8331,10 +8341,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45932</v>
+        <v>45477</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8347,7 +8357,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8390,7 +8400,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47940-2025</t>
+          <t>A 58688-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8404,10 +8414,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45932</v>
+        <v>45251</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8420,7 +8430,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8463,7 +8473,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28321-2023</t>
+          <t>A 35855-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8477,10 +8487,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45099</v>
+        <v>45148</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8492,8 +8502,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8536,7 +8551,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15553-2022</t>
+          <t>A 46868-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8550,10 +8565,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44662</v>
+        <v>45929</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8566,7 +8581,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8609,7 +8624,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 25008-2023</t>
+          <t>A 28271-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8623,10 +8638,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45085</v>
+        <v>45477</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8639,7 +8654,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8682,7 +8697,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 33219-2023</t>
+          <t>A 32796-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8696,10 +8711,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45127</v>
+        <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8717,7 +8732,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8760,7 +8775,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48590-2024</t>
+          <t>A 32822-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8770,14 +8785,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45593</v>
+        <v>45124</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8791,11 +8806,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8838,7 +8853,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31831-2025</t>
+          <t>A 34849-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8848,14 +8863,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45834</v>
+        <v>45527</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8867,8 +8882,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8911,7 +8931,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31968-2025</t>
+          <t>A 47893-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8925,10 +8945,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45835</v>
+        <v>45932</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8941,7 +8961,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8984,7 +9004,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 35855-2023</t>
+          <t>A 34886-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8998,10 +9018,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45148</v>
+        <v>45527</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9015,11 +9035,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.2</v>
+        <v>6.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9062,7 +9082,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17519-2024</t>
+          <t>A 47917-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9076,10 +9096,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45415</v>
+        <v>45932</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9091,13 +9111,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9140,7 +9155,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13198-2024</t>
+          <t>A 47940-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9154,10 +9169,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45386</v>
+        <v>45932</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9170,7 +9185,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9213,7 +9228,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32796-2023</t>
+          <t>A 58121-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9227,10 +9242,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45124</v>
+        <v>45632</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9242,13 +9257,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9291,7 +9301,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 65915-2021</t>
+          <t>A 16109-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9305,10 +9315,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44517</v>
+        <v>46108</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9320,8 +9330,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>17.2</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9364,7 +9379,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62922-2023</t>
+          <t>A 18229-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9378,10 +9393,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45272</v>
+        <v>45761</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9394,7 +9409,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9437,7 +9452,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 34886-2024</t>
+          <t>A 54170-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9451,10 +9466,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45527</v>
+        <v>44881</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9466,13 +9481,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9515,7 +9525,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 2818-2022</t>
+          <t>A 29427-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9529,10 +9539,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44581</v>
+        <v>45483</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9545,7 +9555,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>11</v>
+        <v>3.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9588,7 +9598,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 51123-2025</t>
+          <t>A 15563-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9602,10 +9612,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45947</v>
+        <v>44662</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9618,7 +9628,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9661,7 +9671,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7273-2023</t>
+          <t>A 51123-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9675,10 +9685,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44970</v>
+        <v>45947</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9691,7 +9701,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9734,7 +9744,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20862-2024</t>
+          <t>A 46300-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9748,10 +9758,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45439</v>
+        <v>44847</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9764,7 +9774,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>9.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9807,7 +9817,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 33222-2023</t>
+          <t>A 56280-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9821,10 +9831,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45127</v>
+        <v>45241</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9836,13 +9846,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9885,7 +9890,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 33229-2023</t>
+          <t>A 17897-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9899,10 +9904,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45127</v>
+        <v>46122</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9916,11 +9921,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9963,7 +9968,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6909-2025</t>
+          <t>A 17720-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9973,14 +9978,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45701</v>
+        <v>46121</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9992,13 +9997,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10041,7 +10041,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33224-2023</t>
+          <t>A 18285-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10055,10 +10055,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45127</v>
+        <v>46126</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10070,13 +10070,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10119,7 +10114,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 2278-2022</t>
+          <t>A 10989-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10133,10 +10128,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44578</v>
+        <v>45723</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10148,13 +10143,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10197,7 +10187,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 39407-2024</t>
+          <t>A 65062-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10211,10 +10201,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45551</v>
+        <v>45287</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10226,8 +10216,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>11.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10270,7 +10265,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 2843-2022</t>
+          <t>A 58714-2021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10284,10 +10279,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44581</v>
+        <v>44489</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10300,7 +10295,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10343,7 +10338,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 17135-2025</t>
+          <t>A 67617-2021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10357,10 +10352,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45755</v>
+        <v>44524</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10373,7 +10368,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>10.3</v>
+        <v>6.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10416,7 +10411,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53596-2024</t>
+          <t>A 55835-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10430,10 +10425,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45614</v>
+        <v>45623</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10446,7 +10441,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10489,7 +10484,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 14988-2024</t>
+          <t>A 18916-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10503,10 +10498,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45399</v>
+        <v>46129</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10518,8 +10513,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10562,7 +10562,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19996-2022</t>
+          <t>A 30859-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44697</v>
+        <v>45497</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58688-2023</t>
+          <t>A 35831-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45251</v>
+        <v>45148</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10664,8 +10664,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10708,7 +10713,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14382-2023</t>
+          <t>A 22582-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10722,10 +10727,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45012</v>
+        <v>45447</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10743,7 +10748,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10786,7 +10791,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19069-2025</t>
+          <t>A 55433-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10800,10 +10805,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45765</v>
+        <v>45971</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10816,7 +10821,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>14.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10859,7 +10864,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61463-2022</t>
+          <t>A 7297-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10873,10 +10878,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44916</v>
+        <v>44970</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10889,7 +10894,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10932,7 +10937,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7299-2023</t>
+          <t>A 19079-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10946,10 +10951,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44970</v>
+        <v>46132</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10962,7 +10967,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>10.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11005,7 +11010,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60850-2025</t>
+          <t>A 15663-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11015,14 +11020,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45999</v>
+        <v>45404</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11035,7 +11040,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11078,7 +11083,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 29852-2022</t>
+          <t>A 59298-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11092,10 +11097,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44756</v>
+        <v>45988</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11108,7 +11113,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11151,7 +11156,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 55433-2025</t>
+          <t>A 19823-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11165,10 +11170,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45971</v>
+        <v>46135</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11181,7 +11186,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>14.2</v>
+        <v>2.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11224,7 +11229,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 21295-2023</t>
+          <t>A 59090-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11238,10 +11243,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45062</v>
+        <v>45988</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11253,13 +11258,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 12484-2022</t>
+          <t>A 59933-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44638</v>
+        <v>45993</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11331,8 +11331,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11375,7 +11380,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 35850-2023</t>
+          <t>A 1409-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11389,10 +11394,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45148</v>
+        <v>45667</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11404,13 +11409,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11453,7 +11453,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 59090-2025</t>
+          <t>A 59919-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11467,10 +11467,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45988</v>
+        <v>45993</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11482,8 +11482,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11526,7 +11531,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21081-2026</t>
+          <t>A 59955-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11540,10 +11545,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46146</v>
+        <v>45993</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11557,11 +11562,11 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>14.8</v>
+        <v>4.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11604,7 +11609,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 21137-2026</t>
+          <t>A 53678-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11618,10 +11623,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46146</v>
+        <v>45960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11634,7 +11639,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11677,7 +11682,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60893-2025</t>
+          <t>A 19996-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11691,10 +11696,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45999</v>
+        <v>44697</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11707,7 +11712,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11750,7 +11755,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 21106-2026</t>
+          <t>A 61896-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11764,10 +11769,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46146</v>
+        <v>46003</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11779,13 +11784,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11828,7 +11828,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 21146-2026</t>
+          <t>A 11196-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11842,10 +11842,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46146</v>
+        <v>45371</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11901,7 +11901,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 21634-2026</t>
+          <t>A 60045-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11915,10 +11915,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46149</v>
+        <v>44902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11974,7 +11974,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 22221-2026</t>
+          <t>A 10383-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46153</v>
+        <v>44987</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 22192-2026</t>
+          <t>A 21745-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12061,10 +12061,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46153</v>
+        <v>45442</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 22222-2026</t>
+          <t>A 22362-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12134,10 +12134,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46153</v>
+        <v>45446</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12193,7 +12193,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 59298-2025</t>
+          <t>A 60850-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12207,10 +12207,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45988</v>
+        <v>45999</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12266,7 +12266,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53573-2024</t>
+          <t>A 827-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45614</v>
+        <v>46030</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12339,7 +12339,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 59933-2025</t>
+          <t>A 29852-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12353,10 +12353,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45993</v>
+        <v>44756</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12368,13 +12368,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12417,7 +12412,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 58121-2024</t>
+          <t>A 47734-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12431,10 +12426,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45632</v>
+        <v>45931</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12446,8 +12441,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12490,7 +12490,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 9524-2024</t>
+          <t>A 56748-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12500,14 +12500,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45359</v>
+        <v>44894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12521,11 +12521,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 55835-2024</t>
+          <t>A 55137-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12582,10 +12582,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45623</v>
+        <v>45237</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12641,7 +12641,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 59919-2025</t>
+          <t>A 73264-2021</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45993</v>
+        <v>44550</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12670,13 +12670,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12719,7 +12714,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60045-2022</t>
+          <t>A 73266-2021</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12733,10 +12728,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44902</v>
+        <v>44550</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12749,7 +12744,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12792,7 +12787,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 8399-2025</t>
+          <t>A 7299-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12802,14 +12797,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45709</v>
+        <v>44970</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12821,13 +12816,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12870,7 +12860,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59955-2025</t>
+          <t>A 42370-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12880,14 +12870,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45993</v>
+        <v>45905</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12901,11 +12891,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.6</v>
+        <v>0.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12948,7 +12938,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 63318-2023</t>
+          <t>A 5971-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12962,10 +12952,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45274</v>
+        <v>46052</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12978,7 +12968,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13021,7 +13011,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 55249-2023</t>
+          <t>A 28517-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13035,10 +13025,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45237</v>
+        <v>45478</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13050,8 +13040,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13094,7 +13089,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21836-2025</t>
+          <t>A 14988-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13108,10 +13103,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45784</v>
+        <v>45399</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13124,7 +13119,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13167,7 +13162,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 67617-2021</t>
+          <t>A 48630-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13181,10 +13176,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44524</v>
+        <v>45593</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13197,7 +13192,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13240,7 +13235,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 61896-2025</t>
+          <t>A 62922-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13254,10 +13249,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46003</v>
+        <v>45272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13270,7 +13265,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13313,7 +13308,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 39213-2023</t>
+          <t>A 53074-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13327,10 +13322,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45166</v>
+        <v>44876</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13342,13 +13337,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13391,7 +13381,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 23516-2026</t>
+          <t>A 35850-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13405,10 +13395,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46163</v>
+        <v>45148</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13422,11 +13412,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13469,7 +13459,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 23117-2023</t>
+          <t>A 2278-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13483,10 +13473,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45075</v>
+        <v>44578</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13500,11 +13490,11 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13547,7 +13537,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 23505-2026</t>
+          <t>A 10987-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13561,10 +13551,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46163</v>
+        <v>46079</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13578,11 +13568,11 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13625,7 +13615,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 21745-2024</t>
+          <t>A 32680-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13639,10 +13629,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45442</v>
+        <v>45121</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13654,8 +13644,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13698,7 +13693,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 48647-2024</t>
+          <t>A 21106-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13712,10 +13707,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45593</v>
+        <v>46146</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13727,8 +13722,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.2</v>
+        <v>8.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13771,7 +13771,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 18439-2025</t>
+          <t>A 21081-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13785,10 +13785,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45762</v>
+        <v>46146</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13849,7 +13849,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 40968-2022</t>
+          <t>A 21137-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13863,10 +13863,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44823</v>
+        <v>46146</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>16.5</v>
+        <v>3.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13922,7 +13922,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 64121-2023</t>
+          <t>A 61457-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13932,14 +13932,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45279</v>
+        <v>44916</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.1</v>
+        <v>4.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13995,7 +13995,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 22362-2024</t>
+          <t>A 60893-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45446</v>
+        <v>45999</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14068,7 +14068,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 34427-2024</t>
+          <t>A 21146-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14078,14 +14078,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45525</v>
+        <v>46146</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14097,13 +14097,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14146,7 +14141,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 70214-2021</t>
+          <t>A 40968-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14160,10 +14155,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44535</v>
+        <v>44823</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14176,7 +14171,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14219,7 +14214,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 55137-2023</t>
+          <t>A 21634-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14233,10 +14228,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45237</v>
+        <v>46149</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14249,7 +14244,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14292,7 +14287,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 35831-2023</t>
+          <t>A 12484-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14306,10 +14301,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45148</v>
+        <v>44638</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14321,13 +14316,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14370,7 +14360,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35863-2023</t>
+          <t>A 19069-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14384,10 +14374,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45148</v>
+        <v>45765</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14399,13 +14389,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14448,7 +14433,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 827-2026</t>
+          <t>A 22192-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14462,10 +14447,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46030</v>
+        <v>46153</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14463,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14521,7 +14506,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 73264-2021</t>
+          <t>A 22222-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14535,10 +14520,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44550</v>
+        <v>46153</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14551,7 +14536,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>7.9</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14594,7 +14579,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 73266-2021</t>
+          <t>A 22221-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14608,10 +14593,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44550</v>
+        <v>46153</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14624,7 +14609,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14667,7 +14652,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 61231-2022</t>
+          <t>A 63318-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14681,10 +14666,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44915</v>
+        <v>45274</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14697,7 +14682,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14740,7 +14725,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 26104-2026</t>
+          <t>A 61231-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14754,10 +14739,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46181</v>
+        <v>44915</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14770,7 +14755,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14813,7 +14798,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 26129-2026</t>
+          <t>A 2818-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14827,10 +14812,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46181</v>
+        <v>44581</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14843,7 +14828,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14886,7 +14871,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 26325-2026</t>
+          <t>A 7919-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14900,10 +14885,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46182</v>
+        <v>44973</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14916,7 +14901,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14959,7 +14944,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 1338-2023</t>
+          <t>A 33222-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14973,10 +14958,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44936</v>
+        <v>45127</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14988,8 +14973,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15032,7 +15022,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35654-2024</t>
+          <t>A 33229-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15046,10 +15036,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45532</v>
+        <v>45127</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15061,8 +15051,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15105,7 +15100,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 42370-2025</t>
+          <t>A 15553-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15115,14 +15110,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45905</v>
+        <v>44662</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15134,13 +15129,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.2</v>
+        <v>7.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15183,7 +15173,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 27080-2026</t>
+          <t>A 21836-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15197,10 +15187,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46186</v>
+        <v>45784</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15213,7 +15203,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15256,7 +15246,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 5971-2026</t>
+          <t>A 35940-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15270,10 +15260,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46052</v>
+        <v>45533</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15286,7 +15276,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15329,7 +15319,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27075-2026</t>
+          <t>A 48590-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15339,14 +15329,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46186</v>
+        <v>45593</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15358,8 +15348,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.7</v>
+        <v>7.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15402,7 +15397,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27076-2026</t>
+          <t>A 23505-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15416,10 +15411,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46186</v>
+        <v>46163</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15431,8 +15426,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15475,7 +15475,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 27252-2026</t>
+          <t>A 23516-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15489,10 +15489,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46188</v>
+        <v>46163</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15504,8 +15504,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15548,7 +15553,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 23020-2022</t>
+          <t>A 53596-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15562,10 +15567,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44719</v>
+        <v>45614</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15578,7 +15583,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15621,7 +15626,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 7297-2023</t>
+          <t>A 71625-2021</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15635,10 +15640,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44970</v>
+        <v>44542</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15651,7 +15656,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15694,7 +15699,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 10987-2026</t>
+          <t>A 24036-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15708,10 +15713,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46079</v>
+        <v>45078</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15723,13 +15728,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15772,7 +15772,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 29116-2026</t>
+          <t>A 70214-2021</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15786,10 +15786,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46201</v>
+        <v>44535</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15845,7 +15845,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 33227-2023</t>
+          <t>A 32830-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15859,10 +15859,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45127</v>
+        <v>45124</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15923,7 +15923,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 38261-2022</t>
+          <t>A 29231-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15937,10 +15937,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44812</v>
+        <v>45105</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15996,7 +15996,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 54170-2022</t>
+          <t>A 25008-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44881</v>
+        <v>45085</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16069,7 +16069,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 24036-2023</t>
+          <t>A 26325-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16083,10 +16083,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45078</v>
+        <v>46182</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16142,7 +16142,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 12086-2026</t>
+          <t>A 26104-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16152,14 +16152,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46086</v>
+        <v>46181</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16171,13 +16171,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16220,7 +16215,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 29265-2026</t>
+          <t>A 38261-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16234,10 +16229,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46202</v>
+        <v>44812</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16250,7 +16245,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16293,7 +16288,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 60043-2022</t>
+          <t>A 34786-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16307,10 +16302,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44902</v>
+        <v>45526</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16322,8 +16317,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16366,7 +16366,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15563-2022</t>
+          <t>A 26129-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16380,10 +16380,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44662</v>
+        <v>46181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16439,7 +16439,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 56280-2023</t>
+          <t>A 33219-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16453,10 +16453,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45241</v>
+        <v>45127</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16468,8 +16468,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16512,7 +16517,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30374-2026</t>
+          <t>A 27075-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16526,10 +16531,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46209</v>
+        <v>46186</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16542,7 +16547,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16585,7 +16590,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 30380-2026</t>
+          <t>A 27080-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16599,10 +16604,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46209</v>
+        <v>46186</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16615,7 +16620,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16658,7 +16663,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 58714-2021</t>
+          <t>A 27076-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16672,10 +16677,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44489</v>
+        <v>46186</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16688,7 +16693,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16731,7 +16736,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 16109-2026</t>
+          <t>A 27252-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16745,10 +16750,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46108</v>
+        <v>46188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16760,13 +16765,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16809,7 +16809,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 17720-2026</t>
+          <t>A 23020-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16823,10 +16823,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46121</v>
+        <v>44719</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16882,7 +16882,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 17897-2026</t>
+          <t>A 8399-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16892,14 +16892,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46122</v>
+        <v>45709</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16960,7 +16960,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 18285-2026</t>
+          <t>A 55249-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46126</v>
+        <v>45237</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17033,7 +17033,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 19079-2026</t>
+          <t>A 29116-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17047,10 +17047,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46132</v>
+        <v>46201</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17106,7 +17106,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28517-2024</t>
+          <t>A 29265-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17120,10 +17120,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45478</v>
+        <v>46202</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17135,13 +17135,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17184,7 +17179,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 7919-2023</t>
+          <t>A 28321-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17198,10 +17193,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44973</v>
+        <v>45099</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17214,7 +17209,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17257,7 +17252,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 53585-2024</t>
+          <t>A 58114-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17271,10 +17266,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45614</v>
+        <v>45632</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17287,7 +17282,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17330,7 +17325,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 10383-2023</t>
+          <t>A 60043-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17344,10 +17339,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44987</v>
+        <v>44902</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17360,7 +17355,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17403,7 +17398,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 2812-2023</t>
+          <t>A 30380-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17417,10 +17412,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44944</v>
+        <v>46209</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17433,7 +17428,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17476,7 +17471,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 46300-2022</t>
+          <t>A 10996-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17490,10 +17485,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44847</v>
+        <v>45723</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17506,7 +17501,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17549,7 +17544,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 18916-2026</t>
+          <t>A 30374-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17563,10 +17558,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46129</v>
+        <v>46209</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17578,13 +17573,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17627,7 +17617,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 19823-2026</t>
+          <t>A 2843-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17641,10 +17631,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46135</v>
+        <v>44581</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17657,7 +17647,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17700,7 +17690,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 53678-2025</t>
+          <t>A 21295-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17714,10 +17704,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45960</v>
+        <v>45062</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17729,8 +17719,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17773,7 +17768,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32795-2023</t>
+          <t>A 20933-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17787,10 +17782,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45124</v>
+        <v>45439</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17802,13 +17797,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>11.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17851,7 +17841,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 32822-2023</t>
+          <t>A 32795-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17868,7 +17858,7 @@
         <v>45124</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17886,7 +17876,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17929,7 +17919,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 32830-2023</t>
+          <t>A 31480-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17939,14 +17929,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45124</v>
+        <v>46222</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17958,13 +17948,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18007,7 +17992,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 20933-2024</t>
+          <t>A 35654-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18021,10 +18006,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45439</v>
+        <v>45532</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18037,7 +18022,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>11.3</v>
+        <v>0.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18080,7 +18065,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 34861-2022</t>
+          <t>A 23117-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18094,10 +18079,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44796</v>
+        <v>45075</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18109,8 +18094,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18153,7 +18143,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 31480-2026</t>
+          <t>A 53585-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18163,14 +18153,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46222</v>
+        <v>45614</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18183,7 +18173,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18226,7 +18216,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 18229-2025</t>
+          <t>A 34861-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18240,10 +18230,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45761</v>
+        <v>44796</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18256,7 +18246,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18299,7 +18289,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 47734-2025</t>
+          <t>A 1338-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18313,10 +18303,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45931</v>
+        <v>44936</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18328,13 +18318,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18377,7 +18362,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 11196-2024</t>
+          <t>A 61463-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18391,10 +18376,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45371</v>
+        <v>44916</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18407,7 +18392,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18450,7 +18435,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 1409-2025</t>
+          <t>A 33227-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18464,10 +18449,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45667</v>
+        <v>45127</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18479,8 +18464,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18523,7 +18513,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 6118-2024</t>
+          <t>A 19323-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18537,10 +18527,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45337</v>
+        <v>45049</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18553,7 +18543,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18596,7 +18586,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 22582-2024</t>
+          <t>A 35336-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18606,14 +18596,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45447</v>
+        <v>45530</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18627,11 +18617,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18674,7 +18664,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 50635-2023</t>
+          <t>A 22619-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18688,10 +18678,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45217</v>
+        <v>45789</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18703,8 +18693,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18747,7 +18742,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 10989-2025</t>
+          <t>A 20928-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18761,10 +18756,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45723</v>
+        <v>45439</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18777,7 +18772,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18820,7 +18815,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 65062-2023</t>
+          <t>A 33085-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18834,10 +18829,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45287</v>
+        <v>46245</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18855,7 +18850,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18898,7 +18893,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 28327-2022</t>
+          <t>A 33136-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18912,10 +18907,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44747</v>
+        <v>46245</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18927,8 +18922,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18971,7 +18971,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 15663-2024</t>
+          <t>A 8952-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18981,14 +18981,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45404</v>
+        <v>45355</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19044,7 +19044,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 9693-2025</t>
+          <t>A 39507-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19058,10 +19058,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45716</v>
+        <v>46289</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19073,13 +19073,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19122,7 +19117,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 30859-2024</t>
+          <t>A 39366-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19136,10 +19131,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45497</v>
+        <v>46288</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19152,7 +19147,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.8</v>
+        <v>9.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19195,7 +19190,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 58114-2024</t>
+          <t>A 39368-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19209,10 +19204,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45632</v>
+        <v>46288</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19225,7 +19220,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19268,7 +19263,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 39366-2026</t>
+          <t>A 33054-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19282,10 +19277,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46288</v>
+        <v>46245</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19297,8 +19292,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19341,7 +19341,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 20928-2024</t>
+          <t>A 33055-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19355,10 +19355,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45439</v>
+        <v>46245</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19370,8 +19370,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>2.9</v>
+        <v>11.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19414,7 +19419,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 33085-2026</t>
+          <t>A 25462-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19428,10 +19433,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46245</v>
+        <v>45802</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19449,7 +19454,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>10.6</v>
+        <v>0.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19492,7 +19497,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 33136-2026</t>
+          <t>A 20244-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19506,10 +19511,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46245</v>
+        <v>45055</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19521,13 +19526,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19570,7 +19570,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 33054-2026</t>
+          <t>A 11765-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19584,10 +19584,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46245</v>
+        <v>45727</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19648,7 +19648,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 33055-2026</t>
+          <t>A 26869-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19658,14 +19658,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46245</v>
+        <v>45470</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>11.8</v>
+        <v>2.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19726,7 +19726,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 39368-2026</t>
+          <t>A 33741-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19740,10 +19740,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46288</v>
+        <v>46251</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19755,8 +19755,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19799,7 +19804,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 39507-2026</t>
+          <t>A 33887-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19813,10 +19818,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46289</v>
+        <v>46251</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19828,8 +19833,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I247" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19872,7 +19882,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 40732-2026</t>
+          <t>A 31831-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19886,10 +19896,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46296</v>
+        <v>45834</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19902,7 +19912,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19945,7 +19955,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 33887-2026</t>
+          <t>A 31968-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19959,10 +19969,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46251</v>
+        <v>45835</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19974,13 +19984,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20023,7 +20028,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 33741-2026</t>
+          <t>A 40732-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20037,10 +20042,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46251</v>
+        <v>46296</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20052,13 +20057,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>46301</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>46302</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46255</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>S 915-2022</t>
+          <t>S 5497-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20334,10 +20334,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44606</v>
+        <v>44834</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>18.1</v>
+        <v>31.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20398,7 +20398,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>S 870-2022</t>
+          <t>S 4414-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20412,10 +20412,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>15.1</v>
+        <v>21</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20476,7 +20476,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>S 933-2022</t>
+          <t>S 4411-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20490,10 +20490,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>40.7</v>
+        <v>7.3</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20554,7 +20554,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>S 5497-2022</t>
+          <t>S 915-2022</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20568,10 +20568,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44834</v>
+        <v>44606</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>31.1</v>
+        <v>18.1</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20632,7 +20632,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>S 4414-2023</t>
+          <t>S 6974-2022</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20646,10 +20646,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>21</v>
+        <v>28.8</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20710,7 +20710,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>S 4411-2023</t>
+          <t>S 6964-2022</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20724,10 +20724,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>7.3</v>
+        <v>18.8</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20788,7 +20788,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>S 6974-2022</t>
+          <t>S 4403-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>28.8</v>
+        <v>67.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20866,7 +20866,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>S 6964-2022</t>
+          <t>S 4429-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20880,10 +20880,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>18.8</v>
+        <v>80.3</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20944,7 +20944,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>S 4403-2023</t>
+          <t>S 870-2022</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20958,10 +20958,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>67.7</v>
+        <v>15.1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21022,7 +21022,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 4429-2023</t>
+          <t>S 933-2022</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21036,10 +21036,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>80.3</v>
+        <v>40.7</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21117,7 +21117,7 @@
         <v>45834</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44517</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45526</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>46125</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46125</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>44651</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46051</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44480</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45147</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44913</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45583</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44880</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45188</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45378</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45530</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>45002</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>46037</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>44549</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>44790</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44608</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44616</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>44880</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>44523</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>44581</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>44517</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>44771</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>44785</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44523</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>44735</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44627</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>44753</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>44880</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45533</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>44544</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>44542</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45478</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45614</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45197</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>44987</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45105</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>44847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44876</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>45723</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>45049</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45124</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44894</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45124</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>45124</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45121</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44796</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45761</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45667</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44550</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45337</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45447</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45530</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45217</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45723</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45287</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45477</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45477</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45476</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44747</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45483</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45894</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45891</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45821</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45831</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45404</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45897</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>45716</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>45497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45527</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>45632</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45701</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45453</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44662</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45905</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45099</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45085</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45386</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45127</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45593</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>45530</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44517</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>45415</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45272</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45527</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>45124</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>45127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45127</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>44970</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>45439</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45929</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45701</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45355</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45127</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>44578</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45551</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45932</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45932</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>45932</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45399</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44581</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>45251</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45012</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44916</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45614</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44970</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>45802</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44697</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44756</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45765</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45727</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>45062</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45055</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45470</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44638</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45148</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45632</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45359</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45623</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44902</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45614</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45947</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45709</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45237</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>45834</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>44524</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45835</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45166</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45075</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45593</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45762</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44823</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>45279</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45148</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>45148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45525</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45237</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44550</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44550</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44915</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45971</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45755</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45755</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44936</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>45532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45988</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>46108</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45988</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45127</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>44916</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45993</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45993</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46121</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45993</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>46122</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>46126</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>46132</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>46129</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>46003</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>44970</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>46135</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45127</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>44812</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44881</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45078</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45442</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45960</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45446</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45931</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45371</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>46030</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>44902</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44662</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45999</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45241</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44489</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45905</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>46052</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>46146</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>46146</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45999</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>46146</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>46146</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>46149</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>46153</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>46153</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46153</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>46079</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>46086</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45274</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45784</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>46163</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>46163</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>44535</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46181</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>46181</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>46182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>46186</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>46186</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46186</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>44719</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46201</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46202</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>46209</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>46209</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45439</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46222</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>46288</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45439</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>46245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>46245</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>46245</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>46288</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>46289</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>46296</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>46251</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>46251</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>46301</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>46302</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46255</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>44606</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>44606</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>44606</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>44834</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>44901</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45266</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>45266</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45834</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44517</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45526</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>46125</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46125</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>44651</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46051</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44480</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>44601</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45147</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>44523</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44913</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45583</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44880</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45188</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45378</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45530</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>45002</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>46037</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>44546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>44549</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>44790</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44608</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44616</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>44880</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>44523</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>44581</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>44517</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>44771</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>44785</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44523</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>44735</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44627</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>44753</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>44880</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45533</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>44544</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>44542</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45478</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45614</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45197</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>44987</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45105</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>44847</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44876</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>45723</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>45049</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45124</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44894</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45124</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>45124</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45121</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44796</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45761</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45667</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44550</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45337</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45447</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45530</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45217</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45723</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45287</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45477</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45477</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45476</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44747</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45483</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45894</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45891</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45821</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45831</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45404</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45897</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>45716</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>45497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45527</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>45632</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>45701</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45453</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44662</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45905</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45099</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45085</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45386</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45127</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45593</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>45530</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44517</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>45415</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45272</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45527</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>45124</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>45127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45127</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>44970</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>45439</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45929</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45701</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45355</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45127</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>44578</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45551</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45932</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45932</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>45932</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45399</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44581</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>45251</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45012</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44916</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45614</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44970</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>45802</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44697</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44756</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45765</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45727</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>45062</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45055</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45470</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44638</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45148</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45632</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45359</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45623</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44902</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45614</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45947</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45709</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45237</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>45834</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>44524</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45835</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45166</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45075</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45593</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45762</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44823</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>45279</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45148</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>45148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45525</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45237</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44550</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44550</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44915</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45971</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45755</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45755</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44936</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>45532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45988</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>46108</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45988</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45127</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>44916</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45993</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45993</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46121</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45993</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>46122</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>46126</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>46132</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>46129</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>46003</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>44970</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>46135</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45127</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>44812</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44881</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45078</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45442</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45960</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45446</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45931</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45371</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>46030</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>44902</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44662</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45999</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45241</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44489</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45905</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>46052</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>46146</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>46146</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45999</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>46146</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>46146</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>46149</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>46153</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>46153</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46153</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>46079</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>46086</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45274</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45784</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>46163</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>46163</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>44535</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46181</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>46181</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>46182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>46186</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>46186</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46186</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>44719</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46201</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46202</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>46209</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>46209</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45439</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46222</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>46288</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45439</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>46245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>46245</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>46245</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>46288</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>46289</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>46296</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>46251</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>46251</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>46301</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>46302</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46255</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>44606</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>44606</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>44606</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>44834</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>44901</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45266</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>45266</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45834</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44517</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>46125</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45526</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>44651</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>46051</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>46092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46125</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45278</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>45002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44913</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45188</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44880</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>45378</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45583</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44785</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>44606</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45453</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45217</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45166</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44970</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44747</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45762</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44550</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45148</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45012</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45593</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44944</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45439</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45716</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45337</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45127</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45127</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45386</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>45279</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>45755</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>45476</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45359</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45551</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>44517</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>45371</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45415</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45477</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45891</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>45999</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45831</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>45821</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45251</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45148</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45897</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45124</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45124</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>45477</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>45527</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45527</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45905</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45632</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45905</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45761</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>46146</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>46146</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>46146</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44881</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45483</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44662</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45999</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>46146</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>45929</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>46149</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45932</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>46153</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>46153</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45932</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45932</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44847</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>46153</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45241</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45723</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45947</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45287</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44489</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44524</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45497</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45274</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45148</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45447</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44970</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45784</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45404</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>46163</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>46163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>45667</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45971</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44697</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45988</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45988</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45993</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44987</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45993</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>45993</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>46003</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44756</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45442</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45446</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44535</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45237</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44550</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44550</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44970</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>46030</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45478</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45399</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45593</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45272</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45905</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>46052</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>46182</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44876</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>46181</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>46181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45148</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44578</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45121</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>46186</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>46186</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>46186</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44916</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>46188</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44823</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>46079</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44638</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>45765</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>46086</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>44915</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44581</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44719</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44973</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45127</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45127</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>44662</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45533</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45614</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>46108</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>44542</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>46122</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>46121</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>45078</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>46201</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>46126</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>46129</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>46202</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>46132</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>46135</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45124</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45105</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45960</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>45085</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>44812</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>46209</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45526</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>46209</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45439</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>46222</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45709</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45237</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45099</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45632</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45723</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44581</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45062</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45439</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45124</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45532</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46245</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45075</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45614</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>46289</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>46288</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>46288</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>46245</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>44936</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44916</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>46251</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>46251</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45127</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45049</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>46296</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45530</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45789</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>46301</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>46302</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>46255</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45355</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45802</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>45055</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45727</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45470</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45834</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45835</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44834</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45266</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45266</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44606</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>44606</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>44606</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45834</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44517</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>46125</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45526</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>44651</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>46051</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>46092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46125</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45278</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>45002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44913</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45188</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44880</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>45378</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45583</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44785</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>44606</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45453</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45701</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45217</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>45166</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44970</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44747</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45762</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44550</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45148</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45012</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45593</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44944</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45439</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45716</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>45337</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45127</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45127</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45386</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>45279</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>45755</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>45476</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45359</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45551</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>44517</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>45371</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45415</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45477</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45891</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>45999</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45831</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>45821</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45251</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45148</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45897</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45124</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45124</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>45477</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>45527</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45527</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45905</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45632</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45905</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45761</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>46146</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>46146</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>46146</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44881</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45483</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44662</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45999</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>46146</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>45929</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>46149</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45932</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>46153</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>46153</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45932</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45932</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44847</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>46153</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>45241</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45723</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45947</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45287</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44489</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44524</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45497</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45274</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45148</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45447</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44970</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45784</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45404</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>46163</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>46163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>45667</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45971</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44697</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45988</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45988</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45993</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44987</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45993</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>45993</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>46003</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44756</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45442</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45446</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44535</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45237</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44550</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44550</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44970</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>46030</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45478</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45399</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45593</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45272</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45905</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>46052</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>46182</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44876</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>46181</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>46181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45148</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44578</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45121</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>46186</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>46186</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>46186</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44916</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>46188</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44823</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>46079</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44638</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>45765</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>46086</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>44915</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44581</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44719</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44973</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45127</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45127</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>44662</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45533</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45614</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>46108</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>44542</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>46122</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>46121</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>45078</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>46201</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>46126</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>46129</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>46202</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>46132</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>46135</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45124</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45105</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45960</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>45085</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>44812</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>46209</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45526</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>46209</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45439</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>46222</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45709</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45237</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45099</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45632</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45723</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44581</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45062</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45439</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45124</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45532</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46245</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46245</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45075</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45614</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>46289</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>46288</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>46288</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>46245</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>44936</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44916</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>46251</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>46251</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45127</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45049</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>46296</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45530</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45789</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>46301</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>46302</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>46255</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45355</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45802</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>45055</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45727</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45470</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45834</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45835</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44834</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45266</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45266</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44606</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>44606</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>44606</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45834</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>46125</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44517</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46051</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>46125</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>44651</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46174</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35573-2023</t>
+          <t>A 13208-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45147</v>
+        <v>45002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2199,13 +2199,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2241,481 +2236,485 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 13208-2023 artfynd.xlsx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 13208-2023 karta.png", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 13208-2023 georefererad karta.tif", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 13208-2023 FSC-klagomål.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 13208-2023 FSC-klagomål mail.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 13208-2023 tillsynsbegäran.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 13208-2023 tillsynsbegäran mail.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 13208-2023 prioriterade fågelarter.docx", "A 13208-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 12320-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45378</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12320-2024 artfynd.xlsx", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12320-2024 karta.png", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12320-2024 georefererad karta.tif", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12320-2024 FSC-klagomål.docx", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12320-2024 FSC-klagomål mail.docx", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12320-2024 tillsynsbegäran.docx", "A 12320-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12320-2024 tillsynsbegäran mail.docx", "A 12320-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 35334-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45530</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 46620-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45583</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 35573-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45147</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35573-2023 artfynd.xlsx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35573-2023 karta.png", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35573-2023 georefererad karta.tif", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35573-2023 FSC-klagomål.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35573-2023 FSC-klagomål mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35573-2023 tillsynsbegäran.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35573-2023 tillsynsbegäran mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 67321-2021</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44523</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 67321-2021 artfynd.xlsx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 67321-2021 karta.png", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 67321-2021 georefererad karta.tif", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 67321-2021 FSC-klagomål.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 67321-2021 FSC-klagomål mail.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 67321-2021 tillsynsbegäran.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 67321-2021 tillsynsbegäran mail.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 53706-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44880</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 53706-2022 artfynd.xlsx", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 53706-2022 karta.png", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 53706-2022 georefererad karta.tif", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 53706-2022 FSC-klagomål.docx", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 53706-2022 FSC-klagomål mail.docx", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 53706-2022 tillsynsbegäran.docx", "A 53706-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 53706-2022 tillsynsbegäran mail.docx", "A 53706-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 31980-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45119</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Springkorn</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 31980-2023 artfynd.xlsx", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 31980-2023 karta.png", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 31980-2023 georefererad karta.tif", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 31980-2023 FSC-klagomål.docx", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 31980-2023 FSC-klagomål mail.docx", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 31980-2023 tillsynsbegäran.docx", "A 31980-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 31980-2023 tillsynsbegäran mail.docx", "A 31980-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 35334-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45530</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Nattviol</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 13208-2023</t>
+          <t>A 60736-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2729,10 +2728,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45002</v>
+        <v>44913</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2745,7 +2744,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2754,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2769,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2781,43 +2780,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Mindre flugsnappare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 13208-2023 artfynd.xlsx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 13208-2023 karta.png", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 13208-2023 georefererad karta.tif", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 13208-2023 FSC-klagomål.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 13208-2023 FSC-klagomål mail.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 13208-2023 tillsynsbegäran.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 13208-2023 tillsynsbegäran mail.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 13208-2023 prioriterade fågelarter.docx", "A 13208-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
         <v/>
       </c>
     </row>
@@ -2841,7 +2840,7 @@
         <v>45188</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2929,7 +2928,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12320-2024</t>
+          <t>A 67321-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2939,14 +2938,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45378</v>
+        <v>44523</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2958,13 +2957,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3000,46 +2994,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12320-2024 artfynd.xlsx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 67321-2021 artfynd.xlsx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12320-2024 karta.png", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 67321-2021 karta.png", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12320-2024 georefererad karta.tif", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 67321-2021 georefererad karta.tif", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12320-2024 FSC-klagomål.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 67321-2021 FSC-klagomål.docx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12320-2024 FSC-klagomål mail.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 67321-2021 FSC-klagomål mail.docx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12320-2024 tillsynsbegäran.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 67321-2021 tillsynsbegäran.docx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12320-2024 tillsynsbegäran mail.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 67321-2021 tillsynsbegäran mail.docx", "A 67321-2021")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60736-2022</t>
+          <t>A 31980-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3049,14 +3043,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44913</v>
+        <v>45119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3068,17 +3062,22 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3093,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3105,50 +3104,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 31980-2023 artfynd.xlsx", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 31980-2023 karta.png", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 31980-2023 georefererad karta.tif", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 31980-2023 FSC-klagomål.docx", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 31980-2023 FSC-klagomål mail.docx", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 31980-2023 tillsynsbegäran.docx", "A 31980-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 31980-2023 tillsynsbegäran mail.docx", "A 31980-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46620-2024</t>
+          <t>A 53706-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3162,10 +3157,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45583</v>
+        <v>44880</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,18 +3172,23 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>17.7</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3211,42 +3211,42 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 53706-2022 artfynd.xlsx", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 53706-2022 karta.png", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 53706-2022 georefererad karta.tif", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 53706-2022 FSC-klagomål.docx", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 53706-2022 FSC-klagomål mail.docx", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 53706-2022 tillsynsbegäran.docx", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 53706-2022 tillsynsbegäran mail.docx", "A 53706-2022")</f>
         <v/>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29507-2022</t>
+          <t>A 33033-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44753</v>
+        <v>44785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4425,11 +4425,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4472,7 +4472,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26154-2022</t>
+          <t>A 29507-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4482,14 +4482,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44735</v>
+        <v>44753</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4503,11 +4503,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 53913-2022</t>
+          <t>A 50060-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44880</v>
+        <v>44865</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2834-2022</t>
+          <t>A 67198-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44581</v>
+        <v>44523</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4696,7 +4696,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 66111-2021</t>
+          <t>A 29520-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44517</v>
+        <v>44753</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4725,8 +4725,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4769,7 +4774,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33033-2022</t>
+          <t>A 26154-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4779,14 +4784,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44785</v>
+        <v>44735</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4804,7 +4809,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4847,7 +4852,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50060-2022</t>
+          <t>A 53913-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4861,10 +4866,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44865</v>
+        <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4877,7 +4882,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4920,7 +4925,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29520-2022</t>
+          <t>A 50635-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4934,10 +4939,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44753</v>
+        <v>45217</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4949,13 +4954,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4998,7 +4998,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7289-2022</t>
+          <t>A 2834-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44606</v>
+        <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 67198-2021</t>
+          <t>A 7273-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44523</v>
+        <v>44970</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 72240-2021</t>
+          <t>A 66111-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44544</v>
+        <v>44517</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5217,7 +5217,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46530-2023</t>
+          <t>A 7289-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45197</v>
+        <v>44606</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5246,13 +5246,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5295,7 +5290,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10996-2025</t>
+          <t>A 72240-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5309,10 +5304,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45723</v>
+        <v>44544</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5325,7 +5320,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5368,7 +5363,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35940-2024</t>
+          <t>A 53074-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5382,10 +5377,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45533</v>
+        <v>44876</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5398,7 +5393,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5441,7 +5436,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 71625-2021</t>
+          <t>A 25462-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5455,10 +5450,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44542</v>
+        <v>45802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5470,8 +5465,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5514,7 +5514,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26037-2023</t>
+          <t>A 23451-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45091</v>
+        <v>45453</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>6.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53074-2022</t>
+          <t>A 35850-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44876</v>
+        <v>45148</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5616,8 +5616,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5660,7 +5665,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56748-2022</t>
+          <t>A 2278-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5674,10 +5679,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44894</v>
+        <v>44578</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5695,7 +5700,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5738,7 +5743,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22619-2025</t>
+          <t>A 32680-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5752,10 +5757,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45789</v>
+        <v>45121</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5769,11 +5774,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5816,7 +5821,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8952-2024</t>
+          <t>A 20244-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5830,10 +5835,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45355</v>
+        <v>45055</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5846,7 +5851,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5889,7 +5894,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21745-2024</t>
+          <t>A 11765-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5903,10 +5908,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45442</v>
+        <v>45727</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5918,8 +5923,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5962,7 +5972,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22362-2024</t>
+          <t>A 6947-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5972,14 +5982,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45446</v>
+        <v>45701</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5991,8 +6001,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6035,7 +6050,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28242-2024</t>
+          <t>A 26869-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6045,14 +6060,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45477</v>
+        <v>45470</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6064,8 +6079,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6108,7 +6128,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28271-2024</t>
+          <t>A 34427-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6118,14 +6138,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45477</v>
+        <v>45525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6137,8 +6157,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6181,7 +6206,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35335-2024</t>
+          <t>A 39213-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6195,10 +6220,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45530</v>
+        <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6216,7 +6241,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6259,7 +6284,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40080-2025</t>
+          <t>A 61457-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6273,10 +6298,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45894</v>
+        <v>44916</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6289,7 +6314,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6332,7 +6357,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39748-2025</t>
+          <t>A 28242-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6346,10 +6371,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45891</v>
+        <v>45477</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6361,13 +6386,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6410,7 +6430,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29188-2025</t>
+          <t>A 28327-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6424,10 +6444,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45821</v>
+        <v>44747</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6440,7 +6460,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6483,7 +6503,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30853-2025</t>
+          <t>A 40968-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6497,10 +6517,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45831</v>
+        <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6513,7 +6533,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>16.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6556,7 +6576,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 27995-2024</t>
+          <t>A 12484-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6570,10 +6590,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45476</v>
+        <v>44638</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6586,7 +6606,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6629,7 +6649,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25462-2025</t>
+          <t>A 19069-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6643,10 +6663,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45802</v>
+        <v>45765</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6658,13 +6678,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6707,7 +6722,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40744-2025</t>
+          <t>A 28271-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6721,10 +6736,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45897</v>
+        <v>45477</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6736,13 +6751,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6785,7 +6795,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29427-2024</t>
+          <t>A 61231-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6799,10 +6809,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45483</v>
+        <v>44915</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6815,7 +6825,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6858,7 +6868,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 11765-2025</t>
+          <t>A 2818-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6872,10 +6882,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45727</v>
+        <v>44581</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6887,13 +6897,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6936,7 +6941,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20244-2023</t>
+          <t>A 53573-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6950,10 +6955,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45055</v>
+        <v>45614</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6966,7 +6971,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7009,7 +7014,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 42441-2025</t>
+          <t>A 7919-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7023,10 +7028,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45905</v>
+        <v>44973</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7039,7 +7044,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7082,7 +7087,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34849-2024</t>
+          <t>A 33222-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7092,14 +7097,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45527</v>
+        <v>45127</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7113,11 +7118,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7160,7 +7165,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26869-2024</t>
+          <t>A 33229-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7170,14 +7175,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45470</v>
+        <v>45127</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7191,11 +7196,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7238,7 +7243,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42572-2025</t>
+          <t>A 15553-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7252,10 +7257,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45905</v>
+        <v>44662</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7268,7 +7273,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7311,7 +7316,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15553-2022</t>
+          <t>A 35940-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7325,10 +7330,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44662</v>
+        <v>45533</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7341,7 +7346,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7384,7 +7389,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35855-2023</t>
+          <t>A 31831-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7398,10 +7403,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45148</v>
+        <v>45834</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7413,13 +7418,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7462,7 +7462,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13198-2024</t>
+          <t>A 31968-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45386</v>
+        <v>45835</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7535,7 +7535,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 65915-2021</t>
+          <t>A 48590-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7545,14 +7545,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44517</v>
+        <v>45593</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7564,8 +7564,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>17.2</v>
+        <v>7.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7608,7 +7613,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31831-2025</t>
+          <t>A 53596-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7622,10 +7627,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45834</v>
+        <v>45614</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7638,7 +7643,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7681,7 +7686,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46868-2025</t>
+          <t>A 39748-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7695,10 +7700,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45929</v>
+        <v>45891</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7710,8 +7715,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7754,7 +7764,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62922-2023</t>
+          <t>A 30853-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7768,10 +7778,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45272</v>
+        <v>45831</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7784,7 +7794,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7827,7 +7837,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34886-2024</t>
+          <t>A 29188-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7841,10 +7851,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45527</v>
+        <v>45821</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7856,13 +7866,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>6.3</v>
+        <v>0.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7905,7 +7910,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 827-2026</t>
+          <t>A 40080-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7919,10 +7924,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46030</v>
+        <v>45894</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7935,7 +7940,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7978,7 +7983,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31968-2025</t>
+          <t>A 40744-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7992,10 +7997,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45835</v>
+        <v>45897</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8007,8 +8012,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8051,7 +8061,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47893-2025</t>
+          <t>A 71625-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8065,10 +8075,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45932</v>
+        <v>44542</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8081,7 +8091,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8124,7 +8134,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47917-2025</t>
+          <t>A 24036-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8138,10 +8148,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45932</v>
+        <v>45078</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8154,7 +8164,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8197,7 +8207,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47940-2025</t>
+          <t>A 42441-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8211,10 +8221,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45932</v>
+        <v>45905</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8227,7 +8237,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8270,7 +8280,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33222-2023</t>
+          <t>A 42572-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8284,10 +8294,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45127</v>
+        <v>45905</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8299,13 +8309,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8348,7 +8353,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33229-2023</t>
+          <t>A 32830-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8362,10 +8367,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45127</v>
+        <v>45124</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8383,7 +8388,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8426,7 +8431,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 51123-2025</t>
+          <t>A 29231-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8440,10 +8445,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45947</v>
+        <v>45105</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8456,7 +8461,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8499,7 +8504,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14988-2024</t>
+          <t>A 17135-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8513,10 +8518,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45399</v>
+        <v>45755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8529,7 +8534,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>10.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8572,7 +8577,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58688-2023</t>
+          <t>A 46868-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8586,10 +8591,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45251</v>
+        <v>45929</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8602,7 +8607,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8645,7 +8650,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 14382-2023</t>
+          <t>A 25008-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8655,14 +8660,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45012</v>
+        <v>45085</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8674,13 +8679,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8723,7 +8723,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61463-2022</t>
+          <t>A 38261-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8737,10 +8737,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44916</v>
+        <v>44812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7299-2023</t>
+          <t>A 34786-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8810,10 +8810,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44970</v>
+        <v>45526</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8825,8 +8825,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8869,7 +8874,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17135-2025</t>
+          <t>A 47893-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8883,10 +8888,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45755</v>
+        <v>45932</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8899,7 +8904,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>10.3</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8942,7 +8947,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 29852-2022</t>
+          <t>A 33219-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8956,10 +8961,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44756</v>
+        <v>45127</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8971,8 +8976,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9015,7 +9025,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21295-2023</t>
+          <t>A 47917-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9029,10 +9039,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45062</v>
+        <v>45932</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9044,13 +9054,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9093,7 +9098,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 55433-2025</t>
+          <t>A 47940-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9107,10 +9112,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45971</v>
+        <v>45932</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9123,7 +9128,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>14.2</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9166,7 +9171,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58121-2024</t>
+          <t>A 53678-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9180,10 +9185,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45632</v>
+        <v>45960</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9196,7 +9201,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9239,7 +9244,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9524-2024</t>
+          <t>A 18439-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9249,14 +9254,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45359</v>
+        <v>45762</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9270,11 +9275,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9317,7 +9322,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 55835-2024</t>
+          <t>A 11196-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9331,10 +9336,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45623</v>
+        <v>45371</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9347,7 +9352,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9390,7 +9395,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60045-2022</t>
+          <t>A 51123-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9404,10 +9409,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44902</v>
+        <v>45947</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9420,7 +9425,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9463,7 +9468,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59090-2025</t>
+          <t>A 8399-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9473,14 +9478,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45988</v>
+        <v>45709</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9490,6 +9495,11 @@
       <c r="G109" t="inlineStr">
         <is>
           <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -9536,7 +9546,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 42370-2025</t>
+          <t>A 60850-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9546,14 +9556,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45905</v>
+        <v>45999</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9565,13 +9575,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9614,7 +9619,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59298-2025</t>
+          <t>A 47734-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9628,10 +9633,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45988</v>
+        <v>45931</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9643,8 +9648,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9687,7 +9697,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 67617-2021</t>
+          <t>A 55249-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9701,10 +9711,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44524</v>
+        <v>45237</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9717,7 +9727,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9760,7 +9770,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59933-2025</t>
+          <t>A 28321-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9774,10 +9784,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45993</v>
+        <v>45099</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9789,13 +9799,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9838,7 +9843,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 59919-2025</t>
+          <t>A 58114-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9852,10 +9857,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45993</v>
+        <v>45632</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9867,13 +9872,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 39213-2023</t>
+          <t>A 55433-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45166</v>
+        <v>45971</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9945,13 +9945,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>2.4</v>
+        <v>14.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9994,7 +9989,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 5971-2026</t>
+          <t>A 21106-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10008,10 +10003,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46052</v>
+        <v>46146</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10023,8 +10018,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10067,7 +10067,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23117-2023</t>
+          <t>A 21081-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10081,10 +10081,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45075</v>
+        <v>46146</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10098,11 +10098,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>14.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10145,7 +10145,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 48647-2024</t>
+          <t>A 21137-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45593</v>
+        <v>46146</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10218,7 +10218,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61896-2025</t>
+          <t>A 60043-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10232,10 +10232,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46003</v>
+        <v>44902</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10291,7 +10291,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 35831-2023</t>
+          <t>A 10996-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10305,10 +10305,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45148</v>
+        <v>45723</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10320,13 +10320,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10369,7 +10364,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 35863-2023</t>
+          <t>A 60893-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10383,10 +10378,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45148</v>
+        <v>45999</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10398,13 +10393,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10447,7 +10437,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 10987-2026</t>
+          <t>A 21146-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10461,10 +10451,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46079</v>
+        <v>46146</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10476,13 +10466,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10525,7 +10510,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 12086-2026</t>
+          <t>A 2843-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10535,14 +10520,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46086</v>
+        <v>44581</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10554,13 +10539,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10603,7 +10583,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16885-2025</t>
+          <t>A 22192-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10617,10 +10597,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45755</v>
+        <v>46153</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10633,7 +10613,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10676,7 +10656,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 33218-2023</t>
+          <t>A 59298-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10690,10 +10670,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45127</v>
+        <v>45988</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10705,13 +10685,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10754,7 +10729,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61457-2022</t>
+          <t>A 22222-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10768,10 +10743,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44916</v>
+        <v>46153</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10784,7 +10759,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10827,7 +10802,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16109-2026</t>
+          <t>A 59090-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10841,10 +10816,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46108</v>
+        <v>45988</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10856,13 +10831,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10905,7 +10875,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 34786-2024</t>
+          <t>A 22221-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10919,10 +10889,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45526</v>
+        <v>46153</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10934,13 +10904,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10983,7 +10948,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 29231-2023</t>
+          <t>A 21295-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10997,10 +10962,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45105</v>
+        <v>45062</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11012,8 +10977,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11056,7 +11026,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 17720-2026</t>
+          <t>A 59933-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11070,10 +11040,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46121</v>
+        <v>45993</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11085,8 +11055,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11129,7 +11104,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17897-2026</t>
+          <t>A 59919-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11143,10 +11118,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46122</v>
+        <v>45993</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11160,11 +11135,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11207,7 +11182,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 19323-2023</t>
+          <t>A 63318-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11221,10 +11196,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45049</v>
+        <v>45274</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11237,7 +11212,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11280,7 +11255,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 18285-2026</t>
+          <t>A 32795-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11294,10 +11269,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46126</v>
+        <v>45124</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11309,8 +11284,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11353,7 +11333,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 19079-2026</t>
+          <t>A 35654-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11367,10 +11347,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46132</v>
+        <v>45532</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11383,7 +11363,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>10.1</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11426,7 +11406,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32680-2023</t>
+          <t>A 23117-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11440,10 +11420,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45121</v>
+        <v>45075</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11457,11 +11437,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11504,7 +11484,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 18916-2026</t>
+          <t>A 53585-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11518,10 +11498,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46129</v>
+        <v>45614</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11533,13 +11513,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11582,7 +11557,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 73267-2021</t>
+          <t>A 61896-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11596,10 +11571,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44550</v>
+        <v>46003</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11612,7 +11587,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11655,7 +11630,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 19823-2026</t>
+          <t>A 21836-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11669,10 +11644,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46135</v>
+        <v>45784</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11685,7 +11660,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11728,7 +11703,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 48630-2024</t>
+          <t>A 34861-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11742,10 +11717,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45593</v>
+        <v>44796</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11758,7 +11733,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11801,7 +11776,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53678-2025</t>
+          <t>A 23505-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11815,10 +11790,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45960</v>
+        <v>46163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11830,8 +11805,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11874,7 +11854,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23451-2024</t>
+          <t>A 23516-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11888,10 +11868,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45453</v>
+        <v>46163</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11903,8 +11883,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11947,7 +11932,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 47734-2025</t>
+          <t>A 1338-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11961,10 +11946,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45931</v>
+        <v>44936</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11976,13 +11961,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12025,7 +12005,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 11196-2024</t>
+          <t>A 21745-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12039,10 +12019,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45371</v>
+        <v>45442</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12055,7 +12035,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12098,7 +12078,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28321-2023</t>
+          <t>A 22362-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12112,10 +12092,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45099</v>
+        <v>45446</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12128,7 +12108,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12171,7 +12151,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 25008-2023</t>
+          <t>A 46530-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12185,10 +12165,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45085</v>
+        <v>45197</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12200,8 +12180,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12244,7 +12229,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33219-2023</t>
+          <t>A 61463-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12258,10 +12243,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45127</v>
+        <v>44916</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12273,13 +12258,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12322,7 +12302,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 48590-2024</t>
+          <t>A 33227-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12332,14 +12312,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45593</v>
+        <v>45127</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12353,11 +12333,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12400,7 +12380,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60850-2025</t>
+          <t>A 19323-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12414,10 +12394,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45999</v>
+        <v>45049</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12430,7 +12410,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12473,7 +12453,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 17519-2024</t>
+          <t>A 827-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12487,10 +12467,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45415</v>
+        <v>46030</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12502,13 +12482,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12551,7 +12526,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32796-2023</t>
+          <t>A 73267-2021</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12565,10 +12540,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45124</v>
+        <v>44550</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12580,13 +12555,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12629,7 +12599,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 2818-2022</t>
+          <t>A 26037-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12643,10 +12613,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44581</v>
+        <v>45091</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12659,7 +12629,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>11</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12702,7 +12672,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 7273-2023</t>
+          <t>A 42370-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12712,14 +12682,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44970</v>
+        <v>45905</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12731,8 +12701,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12775,7 +12750,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 20862-2024</t>
+          <t>A 5971-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12789,10 +12764,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45439</v>
+        <v>46052</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12805,7 +12780,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>9.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12848,7 +12823,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 6909-2025</t>
+          <t>A 35335-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12858,14 +12833,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45701</v>
+        <v>45530</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12879,11 +12854,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12926,7 +12901,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 33224-2023</t>
+          <t>A 35336-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12940,10 +12915,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45127</v>
+        <v>45530</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12961,7 +12936,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13004,7 +12979,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 2278-2022</t>
+          <t>A 26104-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13018,10 +12993,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44578</v>
+        <v>46181</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13033,13 +13008,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13082,7 +13052,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 39407-2024</t>
+          <t>A 35863-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13096,10 +13066,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45551</v>
+        <v>45148</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13111,8 +13081,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13155,7 +13130,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 21081-2026</t>
+          <t>A 26129-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13169,10 +13144,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46146</v>
+        <v>46181</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13184,13 +13159,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>14.8</v>
+        <v>2.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13233,7 +13203,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 21137-2026</t>
+          <t>A 22619-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13247,10 +13217,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46146</v>
+        <v>45789</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13262,8 +13232,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13306,7 +13281,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60893-2025</t>
+          <t>A 48647-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13320,10 +13295,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45999</v>
+        <v>45593</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13336,7 +13311,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13379,7 +13354,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 21106-2026</t>
+          <t>A 27075-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13393,10 +13368,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46146</v>
+        <v>46186</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13408,13 +13383,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13457,7 +13427,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 21146-2026</t>
+          <t>A 27080-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13471,10 +13441,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46146</v>
+        <v>46186</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13487,7 +13457,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13530,7 +13500,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 2843-2022</t>
+          <t>A 27076-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13544,10 +13514,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44581</v>
+        <v>46186</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13560,7 +13530,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13603,7 +13573,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 53596-2024</t>
+          <t>A 27252-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13617,10 +13587,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45614</v>
+        <v>46188</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13633,7 +13603,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13676,7 +13646,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 19996-2022</t>
+          <t>A 14382-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13686,14 +13656,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44697</v>
+        <v>45012</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13705,8 +13675,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13749,7 +13724,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22221-2026</t>
+          <t>A 10987-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13763,10 +13738,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46153</v>
+        <v>46079</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13778,8 +13753,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13822,7 +13802,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22192-2026</t>
+          <t>A 23020-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13836,10 +13816,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46153</v>
+        <v>44719</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13852,7 +13832,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>7.5</v>
+        <v>4.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13895,7 +13875,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 22222-2026</t>
+          <t>A 12086-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13905,14 +13885,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46153</v>
+        <v>46086</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13924,8 +13904,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13968,7 +13953,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 19069-2025</t>
+          <t>A 8952-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13982,10 +13967,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45765</v>
+        <v>45355</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13998,7 +13983,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14041,7 +14026,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 63318-2023</t>
+          <t>A 29116-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14055,10 +14040,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45274</v>
+        <v>46201</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14071,7 +14056,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14114,7 +14099,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12484-2022</t>
+          <t>A 29265-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14128,10 +14113,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44638</v>
+        <v>46202</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14144,7 +14129,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14187,7 +14172,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 21836-2025</t>
+          <t>A 70214-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14201,10 +14186,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45784</v>
+        <v>44535</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14217,7 +14202,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14260,7 +14245,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 35850-2023</t>
+          <t>A 16109-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14274,10 +14259,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45148</v>
+        <v>46108</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14291,11 +14276,11 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14338,7 +14323,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 23516-2026</t>
+          <t>A 21634-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14352,10 +14337,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46163</v>
+        <v>46149</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14367,13 +14352,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14416,7 +14396,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 53573-2024</t>
+          <t>A 26325-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14430,10 +14410,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45614</v>
+        <v>46182</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14446,7 +14426,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14489,7 +14469,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 23505-2026</t>
+          <t>A 17897-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14503,10 +14483,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46163</v>
+        <v>46122</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14520,11 +14500,11 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14567,7 +14547,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 8399-2025</t>
+          <t>A 17720-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14577,14 +14557,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45709</v>
+        <v>46121</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14596,13 +14576,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14645,7 +14620,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 55249-2023</t>
+          <t>A 59955-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14659,10 +14634,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45237</v>
+        <v>45993</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14674,8 +14649,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14718,7 +14698,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 18439-2025</t>
+          <t>A 18285-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14732,10 +14712,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45762</v>
+        <v>46126</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14747,13 +14727,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14796,7 +14771,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 40968-2022</t>
+          <t>A 30380-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14810,10 +14785,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44823</v>
+        <v>46209</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14826,7 +14801,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>16.5</v>
+        <v>2.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14869,7 +14844,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 64121-2023</t>
+          <t>A 20862-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14879,14 +14854,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45279</v>
+        <v>45439</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14899,7 +14874,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14942,7 +14917,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 26104-2026</t>
+          <t>A 30374-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14956,10 +14931,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46181</v>
+        <v>46209</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14972,7 +14947,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15015,7 +14990,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 34427-2024</t>
+          <t>A 2812-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15025,14 +15000,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45525</v>
+        <v>44944</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15044,13 +15019,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15093,7 +15063,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 26129-2026</t>
+          <t>A 18916-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15107,10 +15077,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46181</v>
+        <v>46129</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15122,8 +15092,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15166,7 +15141,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 55137-2023</t>
+          <t>A 19079-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15180,10 +15155,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45237</v>
+        <v>46132</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15196,7 +15171,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15239,7 +15214,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 73264-2021</t>
+          <t>A 19823-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15253,10 +15228,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44550</v>
+        <v>46135</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15269,7 +15244,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15312,7 +15287,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 73266-2021</t>
+          <t>A 6909-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15322,14 +15297,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44550</v>
+        <v>45701</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15341,8 +15316,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15385,7 +15365,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 61231-2022</t>
+          <t>A 9693-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15399,10 +15379,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44915</v>
+        <v>45716</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15414,8 +15394,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15458,7 +15443,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 27080-2026</t>
+          <t>A 20933-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15472,10 +15457,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46186</v>
+        <v>45439</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15488,7 +15473,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5.4</v>
+        <v>11.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15531,7 +15516,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 27075-2026</t>
+          <t>A 31480-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15541,14 +15526,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46186</v>
+        <v>46222</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15561,7 +15546,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15604,7 +15589,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 27076-2026</t>
+          <t>A 6118-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15618,10 +15603,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46186</v>
+        <v>45337</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15634,7 +15619,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15677,7 +15662,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 27252-2026</t>
+          <t>A 13198-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15691,10 +15676,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46188</v>
+        <v>45386</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15707,7 +15692,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15750,7 +15735,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 23020-2022</t>
+          <t>A 64121-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15760,14 +15745,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44719</v>
+        <v>45279</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15780,7 +15765,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.3</v>
+        <v>0.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15823,7 +15808,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 1338-2023</t>
+          <t>A 33218-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15837,10 +15822,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44936</v>
+        <v>45127</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15852,8 +15837,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15896,7 +15886,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35654-2024</t>
+          <t>A 33224-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15910,10 +15900,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45532</v>
+        <v>45127</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15925,8 +15915,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15969,7 +15964,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 29116-2026</t>
+          <t>A 16885-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15983,10 +15978,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46201</v>
+        <v>45755</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15999,7 +15994,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16042,7 +16037,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 29265-2026</t>
+          <t>A 27995-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16056,10 +16051,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46202</v>
+        <v>45476</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16072,7 +16067,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16115,7 +16110,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 7297-2023</t>
+          <t>A 9524-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16125,14 +16120,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44970</v>
+        <v>45359</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16144,8 +16139,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16188,7 +16188,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 33227-2023</t>
+          <t>A 65915-2021</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16202,10 +16202,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45127</v>
+        <v>44517</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16217,13 +16217,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>2.9</v>
+        <v>17.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16266,7 +16261,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 38261-2022</t>
+          <t>A 39407-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16280,10 +16275,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44812</v>
+        <v>45551</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16296,7 +16291,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16339,7 +16334,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 54170-2022</t>
+          <t>A 17519-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16353,10 +16348,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44881</v>
+        <v>45415</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16368,8 +16363,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16412,7 +16412,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 24036-2023</t>
+          <t>A 20928-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16426,10 +16426,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45078</v>
+        <v>45439</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16485,7 +16485,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30374-2026</t>
+          <t>A 33085-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16499,10 +16499,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46209</v>
+        <v>46245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16514,8 +16514,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>10.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16558,7 +16563,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 30380-2026</t>
+          <t>A 33136-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16572,10 +16577,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46209</v>
+        <v>46245</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16587,8 +16592,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16631,7 +16641,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 60043-2022</t>
+          <t>A 39507-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16645,10 +16655,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44902</v>
+        <v>46289</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16661,7 +16671,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16704,7 +16714,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 15563-2022</t>
+          <t>A 39366-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16718,10 +16728,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44662</v>
+        <v>46288</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16734,7 +16744,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.7</v>
+        <v>9.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16777,7 +16787,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 20933-2024</t>
+          <t>A 39368-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16791,10 +16801,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45439</v>
+        <v>46288</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16807,7 +16817,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>11.3</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16850,7 +16860,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 31480-2026</t>
+          <t>A 33054-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16860,14 +16870,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46222</v>
+        <v>46245</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16879,8 +16889,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16923,7 +16938,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 56280-2023</t>
+          <t>A 33055-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16937,10 +16952,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45241</v>
+        <v>46245</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16952,8 +16967,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>2.9</v>
+        <v>11.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16996,7 +17016,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 28517-2024</t>
+          <t>A 58688-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17010,10 +17030,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45478</v>
+        <v>45251</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17025,13 +17045,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17074,7 +17089,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 7919-2023</t>
+          <t>A 35855-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17088,10 +17103,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44973</v>
+        <v>45148</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17103,8 +17118,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17147,7 +17167,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 53585-2024</t>
+          <t>A 32796-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17161,10 +17181,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45614</v>
+        <v>45124</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17176,8 +17196,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17220,7 +17245,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 10383-2023</t>
+          <t>A 32822-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17234,10 +17259,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44987</v>
+        <v>45124</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17249,8 +17274,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17293,7 +17323,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 2812-2023</t>
+          <t>A 34849-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17303,14 +17333,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44944</v>
+        <v>45527</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17322,8 +17352,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17366,7 +17401,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 46300-2022</t>
+          <t>A 34886-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17380,10 +17415,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44847</v>
+        <v>45527</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17395,8 +17430,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17439,7 +17479,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 39366-2026</t>
+          <t>A 58121-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17453,10 +17493,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46288</v>
+        <v>45632</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17469,7 +17509,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17512,7 +17552,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 20928-2024</t>
+          <t>A 33741-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17526,10 +17566,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45439</v>
+        <v>46251</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17541,8 +17581,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17585,7 +17630,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 33085-2026</t>
+          <t>A 33887-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17599,10 +17644,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17620,7 +17665,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>10.6</v>
+        <v>4.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17663,7 +17708,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 33136-2026</t>
+          <t>A 18229-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17677,10 +17722,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46245</v>
+        <v>45761</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17692,13 +17737,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17741,7 +17781,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32795-2023</t>
+          <t>A 54170-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17755,10 +17795,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45124</v>
+        <v>44881</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17770,13 +17810,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17819,7 +17854,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 33054-2026</t>
+          <t>A 29427-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17833,10 +17868,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46245</v>
+        <v>45483</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17848,13 +17883,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17897,7 +17927,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 33055-2026</t>
+          <t>A 15563-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17911,10 +17941,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46245</v>
+        <v>44662</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17926,13 +17956,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>11.8</v>
+        <v>3.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17975,7 +18000,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 39368-2026</t>
+          <t>A 40732-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17989,10 +18014,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46288</v>
+        <v>46296</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18005,7 +18030,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18048,7 +18073,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32822-2023</t>
+          <t>A 46300-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18062,10 +18087,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45124</v>
+        <v>44847</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18077,13 +18102,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18126,7 +18146,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 32830-2023</t>
+          <t>A 56280-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18140,10 +18160,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45124</v>
+        <v>45241</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18155,13 +18175,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18204,7 +18219,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 34861-2022</t>
+          <t>A 10989-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18218,10 +18233,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44796</v>
+        <v>45723</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18234,7 +18249,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18277,7 +18292,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 18229-2025</t>
+          <t>A 65062-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18291,10 +18306,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45761</v>
+        <v>45287</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18306,8 +18321,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>0.6</v>
+        <v>11.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18350,7 +18370,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 1409-2025</t>
+          <t>A 67617-2021</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18364,10 +18384,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45667</v>
+        <v>44524</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18380,7 +18400,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18423,7 +18443,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 39507-2026</t>
+          <t>A 55835-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18437,10 +18457,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46289</v>
+        <v>45623</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18453,7 +18473,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18496,7 +18516,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 6118-2024</t>
+          <t>A 30859-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18510,10 +18530,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45337</v>
+        <v>45497</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18526,7 +18546,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18569,7 +18589,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 22582-2024</t>
+          <t>A 35831-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18579,14 +18599,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45447</v>
+        <v>45148</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18600,11 +18620,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18647,7 +18667,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 50635-2023</t>
+          <t>A 22582-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18657,14 +18677,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45217</v>
+        <v>45447</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18676,8 +18696,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18720,7 +18745,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 10989-2025</t>
+          <t>A 7297-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18734,10 +18759,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45723</v>
+        <v>44970</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18750,7 +18775,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18793,7 +18818,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 65062-2023</t>
+          <t>A 41509-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18807,10 +18832,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45287</v>
+        <v>46301</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18822,13 +18847,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>11.3</v>
+        <v>2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18871,7 +18891,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 28327-2022</t>
+          <t>A 15663-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18881,14 +18901,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44747</v>
+        <v>45404</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18901,7 +18921,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18944,7 +18964,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 15663-2024</t>
+          <t>A 41650-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18954,14 +18974,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45404</v>
+        <v>46302</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18974,7 +18994,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19017,7 +19037,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 9693-2025</t>
+          <t>A 34637-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19031,10 +19051,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45716</v>
+        <v>46255</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19046,13 +19066,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19095,7 +19110,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 40732-2026</t>
+          <t>A 1409-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19109,10 +19124,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46296</v>
+        <v>45667</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19125,7 +19140,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19168,7 +19183,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 33887-2026</t>
+          <t>A 19996-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19182,10 +19197,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46251</v>
+        <v>44697</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19197,13 +19212,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19246,7 +19256,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 30859-2024</t>
+          <t>A 60045-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19260,10 +19270,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45497</v>
+        <v>44902</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19276,7 +19286,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19319,7 +19329,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 33741-2026</t>
+          <t>A 10383-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19333,10 +19343,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46251</v>
+        <v>44987</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19348,13 +19358,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I241" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19397,7 +19402,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 58114-2024</t>
+          <t>A 29852-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19411,10 +19416,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45632</v>
+        <v>44756</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19427,7 +19432,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19470,7 +19475,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 6947-2025</t>
+          <t>A 56748-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19480,14 +19485,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45701</v>
+        <v>44894</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19505,7 +19510,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19548,7 +19553,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 35336-2024</t>
+          <t>A 55137-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19562,10 +19567,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45530</v>
+        <v>45237</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19577,13 +19582,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19626,7 +19626,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 41509-2026</t>
+          <t>A 73264-2021</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19640,10 +19640,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46301</v>
+        <v>44550</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2</v>
+        <v>7.9</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19699,7 +19699,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 41650-2026</t>
+          <t>A 73266-2021</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19713,10 +19713,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46302</v>
+        <v>44550</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19772,7 +19772,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 34637-2026</t>
+          <t>A 7299-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19786,10 +19786,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46255</v>
+        <v>44970</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19845,7 +19845,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 70214-2021</t>
+          <t>A 28517-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19859,10 +19859,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44535</v>
+        <v>45478</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19874,8 +19874,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19918,7 +19923,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 59955-2025</t>
+          <t>A 14988-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19932,10 +19937,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45993</v>
+        <v>45399</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19947,13 +19952,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19996,7 +19996,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 26325-2026</t>
+          <t>A 48630-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20010,10 +20010,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46182</v>
+        <v>45593</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20069,7 +20069,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 21634-2026</t>
+          <t>A 62922-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20083,10 +20083,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46149</v>
+        <v>45272</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>S 915-2022</t>
+          <t>S 5497-2022</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20156,10 +20156,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44606</v>
+        <v>44834</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>18.1</v>
+        <v>31.1</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20220,7 +20220,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>S 870-2022</t>
+          <t>S 4414-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20234,10 +20234,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>15.1</v>
+        <v>21</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20298,7 +20298,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>S 933-2022</t>
+          <t>S 4411-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20312,10 +20312,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>40.7</v>
+        <v>7.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20376,7 +20376,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>S 5497-2022</t>
+          <t>S 915-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20390,10 +20390,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44834</v>
+        <v>44606</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>31.1</v>
+        <v>18.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20454,7 +20454,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>S 4414-2023</t>
+          <t>S 6974-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20468,10 +20468,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>21</v>
+        <v>28.8</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20532,7 +20532,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>S 4411-2023</t>
+          <t>S 6964-2022</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20546,10 +20546,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>7.3</v>
+        <v>18.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20610,7 +20610,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>S 6974-2022</t>
+          <t>S 4403-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20624,10 +20624,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>28.8</v>
+        <v>67.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20688,7 +20688,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>S 6964-2022</t>
+          <t>S 4429-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20702,10 +20702,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>18.8</v>
+        <v>80.3</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20766,7 +20766,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>S 4403-2023</t>
+          <t>S 870-2022</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20780,10 +20780,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>67.7</v>
+        <v>15.1</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20844,7 +20844,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>S 4429-2023</t>
+          <t>S 933-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20858,10 +20858,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>80.3</v>
+        <v>40.7</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20939,7 +20939,7 @@
         <v>45834</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>46125</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45526</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44517</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>44651</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>46051</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>46092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46125</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45278</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>45764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>44913</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45583</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>45147</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>44880</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45002</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45378</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44785</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>44606</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44970</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>44812</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>45477</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45197</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>44881</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45477</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45078</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45894</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45891</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45723</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45821</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45831</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45533</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>45905</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>45784</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45091</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>46163</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44662</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>46163</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>45241</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>45929</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44542</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45932</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45932</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>45932</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44876</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>45478</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>44973</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>46181</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45614</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46181</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44987</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44944</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>44847</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>46186</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>46186</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>46186</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>46188</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45124</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45124</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45761</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>45667</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>46201</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45337</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45447</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>46202</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>45971</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>45217</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45723</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45287</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44747</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45404</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45988</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>45716</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>45497</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>46209</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>46209</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>45632</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>45701</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45993</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45439</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>46222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>46003</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45530</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45442</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45789</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>46030</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45355</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>46288</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>45439</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>46245</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>46245</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>46245</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>46245</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>46288</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45905</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>46289</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>46052</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45802</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45530</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45727</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45055</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>45470</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>46296</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>46251</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>46251</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>46079</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45834</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46086</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>45835</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>45476</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45483</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>46301</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>46302</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>46255</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>46108</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45527</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>46121</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>46122</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>44662</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>46126</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45755</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>46132</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>46129</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45148</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45386</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>46135</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44517</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45272</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45527</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45931</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45371</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45127</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45127</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45999</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44535</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45993</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>46182</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>46149</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45399</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>46146</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45012</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>46146</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44916</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45999</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>46146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>46146</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44970</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>44756</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45062</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>46153</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>46153</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>46153</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45274</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45632</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45359</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45623</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44902</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44524</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>45075</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45593</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45148</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45148</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45755</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45127</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>44916</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45526</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45105</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45049</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45121</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44550</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45593</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45453</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45099</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>45127</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45593</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45415</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45124</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>44581</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44970</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45439</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45701</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45127</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44578</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45551</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44581</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45614</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>44697</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45765</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44638</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45148</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45614</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>45709</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45237</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45762</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44823</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45279</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45525</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45237</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44550</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>44550</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44936</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45532</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44606</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44606</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44834</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45266</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>44901</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45266</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45834</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>46125</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>45526</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44517</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>44651</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>46051</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>46092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46125</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45278</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>46174</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>45764</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>44913</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45583</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>45147</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44523</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>44880</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>45530</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45002</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45378</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44549</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>44880</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>44523</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>44771</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44627</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44868</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44735</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44880</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44581</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44785</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44865</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44753</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>44606</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44970</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>44812</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>45477</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45197</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>44881</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45477</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45078</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45894</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>45891</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>45723</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45821</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45831</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45533</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>45905</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>45784</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45091</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>46163</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44662</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>46163</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>45241</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>45929</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44542</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45932</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45932</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>45932</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44876</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>45478</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>44894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>44973</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>46181</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45614</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46181</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44987</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44944</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>44847</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>46186</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>46186</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>46186</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>46188</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45124</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45124</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45761</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>45667</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>46201</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45337</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45447</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>46202</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>45971</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>45217</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45723</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45287</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44747</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45404</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45988</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>45716</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>45497</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>46209</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>46209</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>45632</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>45701</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45988</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45993</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45439</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>46222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>46003</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45530</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45442</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45789</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>46030</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45355</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>46288</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>45439</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>46245</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>46245</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>46245</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>46245</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>46288</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45905</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>46289</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>46052</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45802</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45530</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45727</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45055</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>45470</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>46296</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>46251</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>46251</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>46079</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45834</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46086</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>45835</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>45476</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45483</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>46301</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>46302</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>46255</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>46108</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45527</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>46121</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>46122</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>44662</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>46126</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45755</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>46132</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>46129</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45148</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45386</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>46135</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44517</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45272</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45527</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45931</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45371</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45127</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45127</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45999</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44535</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45993</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>46182</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>46149</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45399</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>46146</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45012</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>46146</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44916</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45999</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>46146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>46146</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44970</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>44756</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45062</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>46153</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>46153</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>46153</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45274</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45632</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45359</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45623</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44902</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44524</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>45075</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45593</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45148</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45148</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45755</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45127</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>44916</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45526</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45105</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45049</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45121</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44550</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45593</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45453</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45099</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>45127</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45593</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45415</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45124</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>44581</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44970</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45439</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45701</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45127</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44578</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45551</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44581</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45614</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>44697</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45765</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44638</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45148</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45614</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>45709</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45237</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45762</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44823</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45279</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45525</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45237</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44550</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>44550</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44936</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45532</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44606</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44606</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44834</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45266</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>44901</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45266</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45266</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45834</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>

--- a/Översikt FORSHAGA.xlsx
+++ b/Översikt FORSHAGA.xlsx
@@ -601,7 +601,7 @@
         <v>45618</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 34758-2024</t>
+          <t>A 66072-2021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,14 +850,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45526</v>
+        <v>44517</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -875,16 +875,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -908,12 +908,125 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Gullklöver
+Skogsklocka
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 66072-2021 artfynd.xlsx", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 66072-2021 karta.png", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 66072-2021 georefererad karta.tif", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 66072-2021 FSC-klagomål.docx", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 66072-2021 FSC-klagomål mail.docx", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 66072-2021 tillsynsbegäran.docx", "A 66072-2021")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 66072-2021 tillsynsbegäran mail.docx", "A 66072-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 34758-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45526</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp
 Fjällig taggsvamp s.str.
@@ -921,148 +1034,35 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 34758-2024 artfynd.xlsx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 34758-2024 karta.png", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 34758-2024 georefererad karta.tif", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 34758-2024 FSC-klagomål.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 34758-2024 FSC-klagomål mail.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 34758-2024 tillsynsbegäran.docx", "A 34758-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 34758-2024 tillsynsbegäran mail.docx", "A 34758-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 66072-2021</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44517</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gullklöver
-Skogsklocka
-Svart trolldruva
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 66072-2021 artfynd.xlsx", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 66072-2021 karta.png", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 66072-2021 georefererad karta.tif", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 66072-2021 FSC-klagomål.docx", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 66072-2021 FSC-klagomål mail.docx", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 66072-2021 tillsynsbegäran.docx", "A 66072-2021")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 66072-2021 tillsynsbegäran mail.docx", "A 66072-2021")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>46125</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>44549</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 5766-2026</t>
+          <t>A 14114-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46051</v>
+        <v>44651</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1319,20 +1319,25 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>25.1</v>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1344,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1356,388 +1361,383 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril
+Göktyta
+Sotnätfjäril</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 14114-2022 artfynd.xlsx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 14114-2022 karta.png", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 14114-2022 georefererad karta.tif", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 14114-2022 FSC-klagomål.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 14114-2022 FSC-klagomål mail.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 14114-2022 tillsynsbegäran.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 14114-2022 tillsynsbegäran mail.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 14114-2022 prioriterade fågelarter.docx", "A 14114-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 63799-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåtryffel
+Svart trolldruva
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 63799-2023 artfynd.xlsx", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 63799-2023 karta.png", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 63799-2023 georefererad karta.tif", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 63799-2023 FSC-klagomål.docx", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 63799-2023 FSC-klagomål mail.docx", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 63799-2023 tillsynsbegäran.docx", "A 63799-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 63799-2023 tillsynsbegäran mail.docx", "A 63799-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 5766-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Nästrot
 Svart trolldruva
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 5766-2026 artfynd.xlsx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 5766-2026 karta.png", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 5766-2026 georefererad karta.tif", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 5766-2026 FSC-klagomål.docx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 5766-2026 FSC-klagomål mail.docx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 5766-2026 tillsynsbegäran.docx", "A 5766-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 5766-2026 tillsynsbegäran mail.docx", "A 5766-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 18103-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46125</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>7.2</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Gransotdyna
 Mörk husmossa
 Blåsippa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18103-2026 artfynd.xlsx", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18103-2026 karta.png", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18103-2026 georefererad karta.tif", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18103-2026 FSC-klagomål.docx", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18103-2026 FSC-klagomål mail.docx", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18103-2026 tillsynsbegäran.docx", "A 18103-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18103-2026 tillsynsbegäran mail.docx", "A 18103-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 14114-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44651</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril
-Göktyta
-Sotnätfjäril</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 14114-2022 artfynd.xlsx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 14114-2022 karta.png", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 14114-2022 georefererad karta.tif", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 14114-2022 FSC-klagomål.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 14114-2022 FSC-klagomål mail.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 14114-2022 tillsynsbegäran.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 14114-2022 tillsynsbegäran mail.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 14114-2022 prioriterade fågelarter.docx", "A 14114-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 63799-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45278</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Blåtryffel
-Svart trolldruva
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 63799-2023 artfynd.xlsx", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 63799-2023 karta.png", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 63799-2023 georefererad karta.tif", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 63799-2023 FSC-klagomål.docx", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 63799-2023 FSC-klagomål mail.docx", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 63799-2023 tillsynsbegäran.docx", "A 63799-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 63799-2023 tillsynsbegäran mail.docx", "A 63799-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18811-2025</t>
+          <t>A 25020-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45764</v>
+        <v>46174</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1803,149 +1803,149 @@
         <v>2</v>
       </c>
       <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 25020-2026 artfynd.xlsx", "A 25020-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 25020-2026 karta.png", "A 25020-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 25020-2026 georefererad karta.tif", "A 25020-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 25020-2026 FSC-klagomål.docx", "A 25020-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 25020-2026 FSC-klagomål mail.docx", "A 25020-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 25020-2026 tillsynsbegäran.docx", "A 25020-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 25020-2026 tillsynsbegäran mail.docx", "A 25020-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 18811-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45764</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Ladusvala
 Bergfink</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 18811-2025 artfynd.xlsx", "A 18811-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 18811-2025 karta.png", "A 18811-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 18811-2025 georefererad karta.tif", "A 18811-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 18811-2025 FSC-klagomål.docx", "A 18811-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 18811-2025 FSC-klagomål mail.docx", "A 18811-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 18811-2025 tillsynsbegäran.docx", "A 18811-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 18811-2025 tillsynsbegäran mail.docx", "A 18811-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25020-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 25020-2026 artfynd.xlsx", "A 25020-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 25020-2026 karta.png", "A 25020-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 25020-2026 georefererad karta.tif", "A 25020-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 25020-2026 FSC-klagomål.docx", "A 25020-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 25020-2026 FSC-klagomål mail.docx", "A 25020-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 25020-2026 tillsynsbegäran.docx", "A 25020-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 25020-2026 tillsynsbegäran mail.docx", "A 25020-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60736-2022</t>
+          <t>A 53706-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44913</v>
+        <v>44880</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2087,11 +2087,16 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>17.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2124,50 +2129,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 53706-2022 artfynd.xlsx", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 53706-2022 karta.png", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 53706-2022 georefererad karta.tif", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 53706-2022 FSC-klagomål.docx", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 53706-2022 FSC-klagomål mail.docx", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 53706-2022 tillsynsbegäran.docx", "A 53706-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 53706-2022 tillsynsbegäran mail.docx", "A 53706-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35334-2024</t>
+          <t>A 12320-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2177,14 +2178,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45530</v>
+        <v>45378</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2198,11 +2199,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2238,39 +2239,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12320-2024 artfynd.xlsx", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12320-2024 karta.png", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12320-2024 georefererad karta.tif", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12320-2024 FSC-klagomål.docx", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12320-2024 FSC-klagomål mail.docx", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12320-2024 tillsynsbegäran.docx", "A 12320-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12320-2024 tillsynsbegäran mail.docx", "A 12320-2024")</f>
         <v/>
       </c>
     </row>
@@ -2294,7 +2295,7 @@
         <v>45002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2386,7 +2387,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 35573-2023</t>
+          <t>A 35334-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2400,10 +2401,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45147</v>
+        <v>45530</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2421,7 +2422,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2457,256 +2458,261 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35334-2024 artfynd.xlsx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35334-2024 karta.png", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35334-2024 georefererad karta.tif", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35334-2024 FSC-klagomål.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35334-2024 FSC-klagomål mail.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35334-2024 tillsynsbegäran.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35334-2024 tillsynsbegäran mail.docx", "A 35334-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 46620-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45583</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 35573-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45147</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>FORSHAGA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 35573-2023 artfynd.xlsx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 35573-2023 karta.png", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 35573-2023 georefererad karta.tif", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 35573-2023 FSC-klagomål.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 35573-2023 FSC-klagomål mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 35573-2023 tillsynsbegäran.docx", "A 35573-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 35573-2023 tillsynsbegäran mail.docx", "A 35573-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 67321-2021</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44523</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 67321-2021 artfynd.xlsx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 67321-2021 karta.png", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 67321-2021 georefererad karta.tif", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 67321-2021 FSC-klagomål.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 67321-2021 FSC-klagomål mail.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 67321-2021 tillsynsbegäran.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 67321-2021 tillsynsbegäran mail.docx", "A 67321-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 46620-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45583</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 46620-2024 artfynd.xlsx", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 46620-2024 karta.png", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 46620-2024 georefererad karta.tif", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 46620-2024 FSC-klagomål.docx", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 46620-2024 FSC-klagomål mail.docx", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 46620-2024 tillsynsbegäran.docx", "A 46620-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 46620-2024 tillsynsbegäran mail.docx", "A 46620-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53706-2022</t>
+          <t>A 60736-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2726,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44880</v>
+        <v>44913</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2735,16 +2741,11 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>17.7</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2777,39 +2778,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 53706-2022 artfynd.xlsx", "A 53706-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 60736-2022 artfynd.xlsx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 53706-2022 karta.png", "A 53706-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 60736-2022 karta.png", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 53706-2022 georefererad karta.tif", "A 53706-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 60736-2022 georefererad karta.tif", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 53706-2022 FSC-klagomål.docx", "A 53706-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 60736-2022 FSC-klagomål.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 53706-2022 FSC-klagomål mail.docx", "A 53706-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 60736-2022 FSC-klagomål mail.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 53706-2022 tillsynsbegäran.docx", "A 53706-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 60736-2022 tillsynsbegäran.docx", "A 60736-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 53706-2022 tillsynsbegäran mail.docx", "A 53706-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 60736-2022 tillsynsbegäran mail.docx", "A 60736-2022")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/fåglar/A 60736-2022 prioriterade fågelarter.docx", "A 60736-2022")</f>
         <v/>
       </c>
     </row>
@@ -2833,7 +2838,7 @@
         <v>45188</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2921,7 +2926,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12320-2024</t>
+          <t>A 67321-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2931,14 +2936,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45378</v>
+        <v>44523</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,13 +2955,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2992,39 +2992,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 12320-2024 artfynd.xlsx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/artfynd/A 67321-2021 artfynd.xlsx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 12320-2024 karta.png", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor/A 67321-2021 karta.png", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 12320-2024 georefererad karta.tif", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/kartor_geotiff/A 67321-2021 georefererad karta.tif", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 12320-2024 FSC-klagomål.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomål/A 67321-2021 FSC-klagomål.docx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 12320-2024 FSC-klagomål mail.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/klagomålsmail/A 67321-2021 FSC-klagomål mail.docx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 12320-2024 tillsynsbegäran.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsyn/A 67321-2021 tillsynsbegäran.docx", "A 67321-2021")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 12320-2024 tillsynsbegäran mail.docx", "A 12320-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1763/tillsynsmail/A 67321-2021 tillsynsbegäran mail.docx", "A 67321-2021")</f>
         <v/>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
         <v>45119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>44546</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>44549</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44616</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>44726</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44880</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>44509</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44523</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44596</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>44771</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44868</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44753</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44735</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44880</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2834-2022</t>
+          <t>A 7289-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44581</v>
+        <v>44606</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4584,7 +4584,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 66111-2021</t>
+          <t>A 19996-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44517</v>
+        <v>44697</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4657,7 +4657,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18229-2025</t>
+          <t>A 2834-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45761</v>
+        <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 67198-2021</t>
+          <t>A 72240-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44523</v>
+        <v>44544</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21295-2023</t>
+          <t>A 67198-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45062</v>
+        <v>44523</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4832,13 +4832,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4881,7 +4876,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33033-2022</t>
+          <t>A 66111-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4895,10 +4890,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44785</v>
+        <v>44517</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4910,13 +4905,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4959,7 +4949,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1409-2025</t>
+          <t>A 60045-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4973,10 +4963,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45667</v>
+        <v>44902</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4989,7 +4979,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5032,7 +5022,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50060-2022</t>
+          <t>A 10383-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5046,10 +5036,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44865</v>
+        <v>44987</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5062,7 +5052,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5105,7 +5095,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29520-2022</t>
+          <t>A 33033-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5119,10 +5109,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44753</v>
+        <v>44785</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5136,11 +5126,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5183,7 +5173,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 72240-2021</t>
+          <t>A 50060-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5197,10 +5187,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44544</v>
+        <v>44865</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5213,7 +5203,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5256,7 +5246,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 58121-2024</t>
+          <t>A 29520-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5270,10 +5260,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45632</v>
+        <v>44753</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5285,8 +5275,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5329,7 +5324,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7289-2022</t>
+          <t>A 8952-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5343,10 +5338,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44606</v>
+        <v>45355</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5402,7 +5397,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9524-2024</t>
+          <t>A 29852-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5412,14 +5407,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45359</v>
+        <v>44756</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5431,13 +5426,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5480,7 +5470,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55835-2024</t>
+          <t>A 23451-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5494,10 +5484,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45623</v>
+        <v>45453</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5510,7 +5500,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5553,7 +5543,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60045-2022</t>
+          <t>A 28242-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5567,10 +5557,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44902</v>
+        <v>45477</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5583,7 +5573,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5626,7 +5616,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6118-2024</t>
+          <t>A 25462-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5640,10 +5630,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45337</v>
+        <v>45802</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5655,8 +5645,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5699,7 +5694,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46530-2023</t>
+          <t>A 56748-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5713,10 +5708,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45197</v>
+        <v>44894</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5734,7 +5729,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5777,7 +5772,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22582-2024</t>
+          <t>A 6947-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5787,14 +5782,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45447</v>
+        <v>45701</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5812,7 +5807,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5855,7 +5850,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10996-2025</t>
+          <t>A 55137-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5869,10 +5864,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45723</v>
+        <v>45237</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5885,7 +5880,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5928,7 +5923,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 67617-2021</t>
+          <t>A 28271-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5942,10 +5937,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44524</v>
+        <v>45477</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5958,7 +5953,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6001,7 +5996,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 39213-2023</t>
+          <t>A 73264-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45166</v>
+        <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6030,13 +6025,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>7.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6079,7 +6069,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 23117-2023</t>
+          <t>A 73266-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6093,10 +6083,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45075</v>
+        <v>44550</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6108,13 +6098,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6157,7 +6142,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 50635-2023</t>
+          <t>A 20244-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6171,10 +6156,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45217</v>
+        <v>45055</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6187,7 +6172,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6230,7 +6215,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10989-2025</t>
+          <t>A 11765-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6244,10 +6229,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6259,8 +6244,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6303,7 +6293,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35940-2024</t>
+          <t>A 7299-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6317,10 +6307,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45533</v>
+        <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6333,7 +6323,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.7</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6376,7 +6366,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 65062-2023</t>
+          <t>A 34427-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6386,14 +6376,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45287</v>
+        <v>45525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6411,7 +6401,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>11.3</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6454,7 +6444,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48647-2024</t>
+          <t>A 39213-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6468,10 +6458,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45593</v>
+        <v>45166</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6483,8 +6473,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6527,7 +6522,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26037-2023</t>
+          <t>A 26869-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6537,14 +6532,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45091</v>
+        <v>45470</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6556,8 +6551,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 71625-2021</t>
+          <t>A 28517-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44542</v>
+        <v>45478</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6629,8 +6629,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6673,7 +6678,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28327-2022</t>
+          <t>A 14988-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6687,10 +6692,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44747</v>
+        <v>45399</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6703,7 +6708,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6746,7 +6751,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15663-2024</t>
+          <t>A 39748-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6756,14 +6761,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45404</v>
+        <v>45891</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6775,8 +6780,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6819,7 +6829,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9693-2025</t>
+          <t>A 48630-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6833,10 +6843,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45716</v>
+        <v>45593</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6848,13 +6858,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6897,7 +6902,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30859-2024</t>
+          <t>A 50635-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6911,10 +6916,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45497</v>
+        <v>45217</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6927,7 +6932,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6970,7 +6975,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35831-2023</t>
+          <t>A 62922-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6984,10 +6989,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45148</v>
+        <v>45272</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6999,13 +7004,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7048,7 +7048,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35863-2023</t>
+          <t>A 30853-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45148</v>
+        <v>45831</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7077,13 +7077,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7126,7 +7121,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 53074-2022</t>
+          <t>A 29188-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7140,10 +7135,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44876</v>
+        <v>45821</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7156,7 +7151,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7199,7 +7194,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58114-2024</t>
+          <t>A 40080-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7213,10 +7208,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45632</v>
+        <v>45894</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7229,7 +7224,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7272,7 +7267,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28242-2024</t>
+          <t>A 40744-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7286,10 +7281,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45477</v>
+        <v>45897</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7301,8 +7296,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6947-2025</t>
+          <t>A 53074-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45701</v>
+        <v>44876</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7374,13 +7374,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7423,7 +7418,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28271-2024</t>
+          <t>A 35850-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7437,10 +7432,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45477</v>
+        <v>45148</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7452,8 +7447,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7496,7 +7496,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56748-2022</t>
+          <t>A 2278-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44894</v>
+        <v>44578</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7574,7 +7574,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40080-2025</t>
+          <t>A 32680-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45894</v>
+        <v>45121</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7603,8 +7603,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7647,7 +7652,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39748-2025</t>
+          <t>A 7273-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7661,10 +7666,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45891</v>
+        <v>44970</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7674,11 +7679,6 @@
       <c r="G85" t="inlineStr">
         <is>
           <t>FORSHAGA</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -7725,7 +7725,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 29188-2025</t>
+          <t>A 42441-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45821</v>
+        <v>45905</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>4.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7798,7 +7798,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30853-2025</t>
+          <t>A 31831-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45831</v>
+        <v>45834</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7871,7 +7871,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40744-2025</t>
+          <t>A 61457-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7885,10 +7885,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45897</v>
+        <v>44916</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7900,13 +7900,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7949,7 +7944,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 16885-2025</t>
+          <t>A 42572-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7963,10 +7958,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45755</v>
+        <v>45905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7979,7 +7974,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7.1</v>
+        <v>12.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8022,7 +8017,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42441-2025</t>
+          <t>A 31968-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8036,10 +8031,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45905</v>
+        <v>45835</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8052,7 +8047,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8095,7 +8090,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42572-2025</t>
+          <t>A 40968-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8109,10 +8104,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45905</v>
+        <v>44823</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8125,7 +8120,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8168,7 +8163,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35335-2024</t>
+          <t>A 12484-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8182,10 +8177,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45530</v>
+        <v>44638</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8197,13 +8192,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8246,7 +8236,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33218-2023</t>
+          <t>A 19069-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8260,10 +8250,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45127</v>
+        <v>45765</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8275,13 +8265,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8324,7 +8309,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61457-2022</t>
+          <t>A 46868-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8338,10 +8323,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44916</v>
+        <v>45929</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8354,7 +8339,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8397,7 +8382,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 27995-2024</t>
+          <t>A 61231-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8411,10 +8396,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45476</v>
+        <v>44915</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8427,7 +8412,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8470,7 +8455,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29427-2024</t>
+          <t>A 2818-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8484,10 +8469,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45483</v>
+        <v>44581</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8500,7 +8485,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.7</v>
+        <v>11</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8543,7 +8528,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 46868-2025</t>
+          <t>A 7919-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8557,10 +8542,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45929</v>
+        <v>44973</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8573,7 +8558,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8616,7 +8601,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34849-2024</t>
+          <t>A 28327-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8626,14 +8611,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45527</v>
+        <v>44747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8645,13 +8630,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8694,7 +8674,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34786-2024</t>
+          <t>A 33222-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8708,10 +8688,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45526</v>
+        <v>45127</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8725,11 +8705,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8772,7 +8752,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 29231-2023</t>
+          <t>A 33229-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8786,10 +8766,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45105</v>
+        <v>45127</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8801,8 +8781,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8862,7 +8847,7 @@
         <v>45932</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8935,7 +8920,7 @@
         <v>44662</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9008,7 +8993,7 @@
         <v>45932</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9081,7 +9066,7 @@
         <v>45932</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9137,7 +9122,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35855-2023</t>
+          <t>A 35940-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9151,10 +9136,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45148</v>
+        <v>45533</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9166,13 +9151,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.2</v>
+        <v>6.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9215,7 +9195,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19323-2023</t>
+          <t>A 48590-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9225,14 +9205,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45049</v>
+        <v>45593</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9244,8 +9224,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9288,7 +9273,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13198-2024</t>
+          <t>A 53596-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9302,10 +9287,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45386</v>
+        <v>45614</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9318,7 +9303,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9361,7 +9346,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 32680-2023</t>
+          <t>A 51123-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9375,10 +9360,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45121</v>
+        <v>45947</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9390,13 +9375,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9439,7 +9419,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 65915-2021</t>
+          <t>A 71625-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9453,10 +9433,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44517</v>
+        <v>44542</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9469,7 +9449,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>17.2</v>
+        <v>4.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9512,7 +9492,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62922-2023</t>
+          <t>A 24036-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9526,10 +9506,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45272</v>
+        <v>45078</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9542,7 +9522,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9585,7 +9565,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 34886-2024</t>
+          <t>A 53573-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9599,10 +9579,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45527</v>
+        <v>45614</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9614,13 +9594,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9663,7 +9638,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 73267-2021</t>
+          <t>A 32830-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9677,10 +9652,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44550</v>
+        <v>45124</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9692,8 +9667,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9736,7 +9716,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 51123-2025</t>
+          <t>A 21106-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9750,10 +9730,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45947</v>
+        <v>46146</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9765,8 +9745,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>3.1</v>
+        <v>8.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9809,7 +9794,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 48630-2024</t>
+          <t>A 21081-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9823,10 +9808,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45593</v>
+        <v>46146</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9838,8 +9823,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>7.5</v>
+        <v>14.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9882,7 +9872,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 33222-2023</t>
+          <t>A 21137-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9896,10 +9886,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45127</v>
+        <v>46146</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9911,13 +9901,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9960,7 +9945,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33229-2023</t>
+          <t>A 29231-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9974,10 +9959,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45127</v>
+        <v>45105</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9989,13 +9974,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10038,7 +10018,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 35336-2024</t>
+          <t>A 60893-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10052,10 +10032,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45530</v>
+        <v>45999</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10067,13 +10047,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10116,7 +10091,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23451-2024</t>
+          <t>A 21146-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10130,10 +10105,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45453</v>
+        <v>46146</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10146,7 +10121,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10189,7 +10164,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28321-2023</t>
+          <t>A 22192-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10203,10 +10178,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45099</v>
+        <v>46153</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10219,7 +10194,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10262,7 +10237,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 25008-2023</t>
+          <t>A 22222-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10276,10 +10251,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45085</v>
+        <v>46153</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10292,7 +10267,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10335,7 +10310,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33219-2023</t>
+          <t>A 25008-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10349,10 +10324,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45127</v>
+        <v>45085</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10364,13 +10339,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10413,7 +10383,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 14988-2024</t>
+          <t>A 22221-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10427,10 +10397,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45399</v>
+        <v>46153</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10443,7 +10413,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10486,7 +10456,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 48590-2024</t>
+          <t>A 38261-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10496,14 +10466,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45593</v>
+        <v>44812</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10515,13 +10485,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10564,7 +10529,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58688-2023</t>
+          <t>A 34786-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10578,10 +10543,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45251</v>
+        <v>45526</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10593,8 +10558,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10637,7 +10607,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 17519-2024</t>
+          <t>A 55433-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10651,10 +10621,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45415</v>
+        <v>45971</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10666,13 +10636,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>14.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10715,7 +10680,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14382-2023</t>
+          <t>A 63318-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10725,14 +10690,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45012</v>
+        <v>45274</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10744,13 +10709,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10793,7 +10753,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61463-2022</t>
+          <t>A 33219-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10807,10 +10767,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44916</v>
+        <v>45127</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10822,8 +10782,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10866,7 +10831,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7299-2023</t>
+          <t>A 21836-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10880,10 +10845,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44970</v>
+        <v>45784</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10896,7 +10861,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>4.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10939,7 +10904,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 32796-2023</t>
+          <t>A 59298-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10953,10 +10918,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45124</v>
+        <v>45988</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10968,13 +10933,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11017,7 +10977,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 29852-2022</t>
+          <t>A 59090-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11031,10 +10991,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44756</v>
+        <v>45988</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11047,7 +11007,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11090,7 +11050,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 55433-2025</t>
+          <t>A 59933-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11104,10 +11064,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45971</v>
+        <v>45993</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11119,8 +11079,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>14.2</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11163,7 +11128,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 2818-2022</t>
+          <t>A 59919-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11177,10 +11142,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44581</v>
+        <v>45993</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11192,8 +11157,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>11</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11236,7 +11206,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61896-2025</t>
+          <t>A 23505-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11250,10 +11220,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46003</v>
+        <v>46163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11265,8 +11235,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11309,7 +11284,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 59090-2025</t>
+          <t>A 23516-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11323,10 +11298,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45988</v>
+        <v>46163</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11338,8 +11313,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11382,7 +11362,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 7273-2023</t>
+          <t>A 8399-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11392,14 +11372,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44970</v>
+        <v>45709</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11411,8 +11391,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11455,7 +11440,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20862-2024</t>
+          <t>A 61896-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11469,10 +11454,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45439</v>
+        <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11485,7 +11470,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>9.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11528,7 +11513,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 59298-2025</t>
+          <t>A 55249-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11542,10 +11527,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45988</v>
+        <v>45237</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11558,7 +11543,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11601,7 +11586,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 59933-2025</t>
+          <t>A 28321-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11615,10 +11600,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45993</v>
+        <v>45099</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11630,13 +11615,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11679,7 +11659,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 6909-2025</t>
+          <t>A 21745-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11689,14 +11669,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45701</v>
+        <v>45442</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11708,13 +11688,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11757,7 +11732,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 21745-2024</t>
+          <t>A 22362-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11771,10 +11746,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45442</v>
+        <v>45446</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11787,7 +11762,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11830,7 +11805,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33224-2023</t>
+          <t>A 58114-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11844,10 +11819,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45127</v>
+        <v>45632</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11859,13 +11834,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11908,7 +11878,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 59919-2025</t>
+          <t>A 827-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11922,10 +11892,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45993</v>
+        <v>46030</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11937,13 +11907,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11986,7 +11951,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 2278-2022</t>
+          <t>A 60043-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12000,10 +11965,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44578</v>
+        <v>44902</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12015,13 +11980,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12064,7 +12024,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 22362-2024</t>
+          <t>A 10996-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12078,10 +12038,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45446</v>
+        <v>45723</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12094,7 +12054,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12137,7 +12097,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 39407-2024</t>
+          <t>A 26104-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12151,10 +12111,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45551</v>
+        <v>46181</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12167,7 +12127,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12210,7 +12170,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29116-2026</t>
+          <t>A 2843-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12224,10 +12184,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46201</v>
+        <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12240,7 +12200,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12283,7 +12243,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 2843-2022</t>
+          <t>A 26129-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12297,10 +12257,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44581</v>
+        <v>46181</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12313,7 +12273,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12356,7 +12316,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 29265-2026</t>
+          <t>A 18439-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12370,10 +12330,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46202</v>
+        <v>45762</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12385,8 +12345,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12429,7 +12394,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 22619-2025</t>
+          <t>A 21295-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12443,10 +12408,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45789</v>
+        <v>45062</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12464,7 +12429,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12507,7 +12472,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 827-2026</t>
+          <t>A 27075-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12521,10 +12486,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46030</v>
+        <v>46186</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12537,7 +12502,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12580,7 +12545,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 53596-2024</t>
+          <t>A 27080-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12594,10 +12559,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45614</v>
+        <v>46186</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12610,7 +12575,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12653,7 +12618,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 19996-2022</t>
+          <t>A 42370-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12663,14 +12628,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44697</v>
+        <v>45905</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12682,8 +12647,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12726,7 +12696,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 19069-2025</t>
+          <t>A 27076-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12740,10 +12710,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45765</v>
+        <v>46186</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12756,7 +12726,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12799,7 +12769,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8952-2024</t>
+          <t>A 5971-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12813,10 +12783,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45355</v>
+        <v>46052</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12829,7 +12799,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12872,7 +12842,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 30374-2026</t>
+          <t>A 27252-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12886,10 +12856,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46209</v>
+        <v>46188</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12902,7 +12872,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12945,7 +12915,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 30380-2026</t>
+          <t>A 32795-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12959,10 +12929,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46209</v>
+        <v>45124</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12974,8 +12944,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13018,7 +12993,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 12484-2022</t>
+          <t>A 35654-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13032,10 +13007,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44638</v>
+        <v>45532</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13048,7 +13023,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13091,7 +13066,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35850-2023</t>
+          <t>A 23117-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13105,10 +13080,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45148</v>
+        <v>45075</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13122,11 +13097,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13169,7 +13144,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 42370-2025</t>
+          <t>A 53585-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13179,14 +13154,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45905</v>
+        <v>45614</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13198,13 +13173,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13247,7 +13217,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 53573-2024</t>
+          <t>A 34861-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13261,10 +13231,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45614</v>
+        <v>44796</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13277,7 +13247,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13320,7 +13290,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 5971-2026</t>
+          <t>A 23020-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13334,10 +13304,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46052</v>
+        <v>44719</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13350,7 +13320,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13393,7 +13363,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 20933-2024</t>
+          <t>A 1338-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13407,10 +13377,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45439</v>
+        <v>44936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13423,7 +13393,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>11.3</v>
+        <v>6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13466,7 +13436,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 31480-2026</t>
+          <t>A 10987-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13476,14 +13446,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46222</v>
+        <v>46079</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13495,8 +13465,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13539,7 +13514,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 8399-2025</t>
+          <t>A 61463-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13549,14 +13524,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45709</v>
+        <v>44916</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13568,13 +13543,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13617,7 +13587,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 55249-2023</t>
+          <t>A 29116-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13631,10 +13601,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45237</v>
+        <v>46201</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13647,7 +13617,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13690,7 +13660,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 18439-2025</t>
+          <t>A 12086-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13700,14 +13670,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45762</v>
+        <v>46086</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13725,7 +13695,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13768,7 +13738,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 40968-2022</t>
+          <t>A 29265-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13782,10 +13752,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44823</v>
+        <v>46202</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13798,7 +13768,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>16.5</v>
+        <v>2.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13841,7 +13811,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 64121-2023</t>
+          <t>A 33227-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13851,14 +13821,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45279</v>
+        <v>45127</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13870,8 +13840,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.1</v>
+        <v>2.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13914,7 +13889,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 34427-2024</t>
+          <t>A 46530-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13924,14 +13899,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45525</v>
+        <v>45197</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13949,7 +13924,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13992,7 +13967,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 10987-2026</t>
+          <t>A 19323-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14006,10 +13981,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46079</v>
+        <v>45049</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14021,13 +13996,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14070,7 +14040,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 55137-2023</t>
+          <t>A 73267-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14084,10 +14054,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45237</v>
+        <v>44550</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14100,7 +14070,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14143,7 +14113,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 39366-2026</t>
+          <t>A 26037-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14157,10 +14127,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46288</v>
+        <v>45091</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14173,7 +14143,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>9.5</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14216,7 +14186,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 20928-2024</t>
+          <t>A 30380-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14230,10 +14200,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45439</v>
+        <v>46209</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14246,7 +14216,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14289,7 +14259,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 33085-2026</t>
+          <t>A 30374-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14303,10 +14273,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46245</v>
+        <v>46209</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14318,13 +14288,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>10.6</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14367,7 +14332,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 33136-2026</t>
+          <t>A 35335-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14381,10 +14346,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46245</v>
+        <v>45530</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14398,11 +14363,11 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14445,7 +14410,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33054-2026</t>
+          <t>A 16109-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14459,10 +14424,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46245</v>
+        <v>46108</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14480,7 +14445,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14523,7 +14488,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 33055-2026</t>
+          <t>A 35863-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14537,10 +14502,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46245</v>
+        <v>45148</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14554,11 +14519,11 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>11.8</v>
+        <v>1.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14601,7 +14566,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 39368-2026</t>
+          <t>A 35336-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14615,10 +14580,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46288</v>
+        <v>45530</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14630,8 +14595,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14674,7 +14644,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 73264-2021</t>
+          <t>A 17897-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14688,10 +14658,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44550</v>
+        <v>46122</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14703,8 +14673,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14747,7 +14722,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 73266-2021</t>
+          <t>A 17720-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14761,10 +14736,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44550</v>
+        <v>46121</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14777,7 +14752,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14820,7 +14795,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 25462-2025</t>
+          <t>A 20933-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14834,10 +14809,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45802</v>
+        <v>45439</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14849,13 +14824,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>0.8</v>
+        <v>11.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14898,7 +14868,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 61231-2022</t>
+          <t>A 18285-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14912,10 +14882,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44915</v>
+        <v>46126</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14928,7 +14898,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14971,7 +14941,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 12086-2026</t>
+          <t>A 31480-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14981,14 +14951,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46086</v>
+        <v>46222</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15000,13 +14970,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15049,7 +15014,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 39507-2026</t>
+          <t>A 22619-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15063,10 +15028,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46289</v>
+        <v>45789</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15078,8 +15043,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15122,7 +15092,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 1338-2023</t>
+          <t>A 18916-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15136,10 +15106,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44936</v>
+        <v>46129</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15151,8 +15121,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15195,7 +15170,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 35654-2024</t>
+          <t>A 19079-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15209,10 +15184,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45532</v>
+        <v>46132</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15225,7 +15200,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15268,7 +15243,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 16109-2026</t>
+          <t>A 19823-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15282,10 +15257,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46108</v>
+        <v>46135</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15297,13 +15272,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15346,7 +15316,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 40732-2026</t>
+          <t>A 48647-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15360,10 +15330,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46296</v>
+        <v>45593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15376,7 +15346,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15419,7 +15389,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 33887-2026</t>
+          <t>A 53678-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15433,10 +15403,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46251</v>
+        <v>45960</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15448,13 +15418,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15497,7 +15462,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 33741-2026</t>
+          <t>A 14382-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15507,14 +15472,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46251</v>
+        <v>45012</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15532,7 +15497,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15575,7 +15540,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 17720-2026</t>
+          <t>A 11196-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15589,10 +15554,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46121</v>
+        <v>45371</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15605,7 +15570,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15648,7 +15613,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 17897-2026</t>
+          <t>A 20928-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15662,10 +15627,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46122</v>
+        <v>45439</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15677,13 +15642,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>8.4</v>
+        <v>2.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15726,7 +15686,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 11765-2025</t>
+          <t>A 33085-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15740,10 +15700,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45727</v>
+        <v>46245</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15761,7 +15721,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>10.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15804,7 +15764,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 20244-2023</t>
+          <t>A 33136-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15818,10 +15778,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45055</v>
+        <v>46245</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15833,8 +15793,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15877,7 +15842,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 7297-2023</t>
+          <t>A 60850-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15891,10 +15856,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44970</v>
+        <v>45999</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15907,7 +15872,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15950,7 +15915,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 33227-2023</t>
+          <t>A 39507-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15964,10 +15929,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45127</v>
+        <v>46289</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15979,13 +15944,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16028,7 +15988,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 38261-2022</t>
+          <t>A 47734-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16042,10 +16002,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44812</v>
+        <v>45931</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16057,8 +16017,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16101,7 +16066,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 54170-2022</t>
+          <t>A 39366-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16115,10 +16080,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44881</v>
+        <v>46288</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16131,7 +16096,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.2</v>
+        <v>9.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16174,7 +16139,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 24036-2023</t>
+          <t>A 39368-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16188,10 +16153,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45078</v>
+        <v>46288</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16204,7 +16169,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16247,7 +16212,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 18285-2026</t>
+          <t>A 33054-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16261,10 +16226,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46126</v>
+        <v>46245</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16276,8 +16241,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16320,7 +16290,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 19079-2026</t>
+          <t>A 33055-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16334,10 +16304,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46132</v>
+        <v>46245</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16349,8 +16319,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>10.1</v>
+        <v>11.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16393,7 +16368,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 41509-2026</t>
+          <t>A 20862-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16407,10 +16382,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46301</v>
+        <v>45439</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16423,7 +16398,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16466,7 +16441,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 41650-2026</t>
+          <t>A 2812-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16480,10 +16455,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46302</v>
+        <v>44944</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16496,7 +16471,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16539,7 +16514,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34637-2026</t>
+          <t>A 6909-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16549,14 +16524,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46255</v>
+        <v>45701</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16568,8 +16543,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16612,7 +16592,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 18916-2026</t>
+          <t>A 9693-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16626,10 +16606,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46129</v>
+        <v>45716</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16647,7 +16627,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16690,7 +16670,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 19823-2026</t>
+          <t>A 33741-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16704,10 +16684,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46135</v>
+        <v>46251</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16719,8 +16699,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16763,7 +16748,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 26869-2024</t>
+          <t>A 33887-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16773,14 +16758,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45470</v>
+        <v>46251</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16798,7 +16783,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16841,7 +16826,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 60043-2022</t>
+          <t>A 6118-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16855,10 +16840,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44902</v>
+        <v>45337</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16871,7 +16856,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16914,7 +16899,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 15563-2022</t>
+          <t>A 13198-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16928,10 +16913,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44662</v>
+        <v>45386</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16944,7 +16929,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16987,7 +16972,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 53678-2025</t>
+          <t>A 64121-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16997,14 +16982,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45960</v>
+        <v>45279</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17017,7 +17002,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17060,7 +17045,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 56280-2023</t>
+          <t>A 33218-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17074,10 +17059,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45241</v>
+        <v>45127</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17089,8 +17074,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17133,7 +17123,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 47734-2025</t>
+          <t>A 33224-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17147,10 +17137,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45931</v>
+        <v>45127</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17168,7 +17158,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17211,7 +17201,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 11196-2024</t>
+          <t>A 16885-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17225,10 +17215,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45371</v>
+        <v>45755</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17241,7 +17231,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17284,7 +17274,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 60850-2025</t>
+          <t>A 27995-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17298,10 +17288,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45999</v>
+        <v>45476</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17314,7 +17304,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17357,7 +17347,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 28517-2024</t>
+          <t>A 40732-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17371,10 +17361,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45478</v>
+        <v>46296</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17386,13 +17376,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17435,7 +17420,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 7919-2023</t>
+          <t>A 9524-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17445,14 +17430,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44973</v>
+        <v>45359</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17464,8 +17449,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17508,7 +17498,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 53585-2024</t>
+          <t>A 65915-2021</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17522,10 +17512,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45614</v>
+        <v>44517</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17538,7 +17528,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.3</v>
+        <v>17.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17581,7 +17571,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 10383-2023</t>
+          <t>A 39407-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17595,10 +17585,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44987</v>
+        <v>45551</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17611,7 +17601,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17654,7 +17644,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 2812-2023</t>
+          <t>A 17519-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17668,10 +17658,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44944</v>
+        <v>45415</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17683,8 +17673,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17727,7 +17722,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 46300-2022</t>
+          <t>A 41509-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17741,10 +17736,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44847</v>
+        <v>46301</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17757,7 +17752,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17800,7 +17795,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 70214-2021</t>
+          <t>A 41650-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17814,10 +17809,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44535</v>
+        <v>46302</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17830,7 +17825,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17873,7 +17868,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 59955-2025</t>
+          <t>A 34637-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17887,10 +17882,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45993</v>
+        <v>46255</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17902,13 +17897,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17951,7 +17941,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 26325-2026</t>
+          <t>A 58688-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17965,10 +17955,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46182</v>
+        <v>45251</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17981,7 +17971,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18024,7 +18014,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32795-2023</t>
+          <t>A 35855-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18038,10 +18028,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45124</v>
+        <v>45148</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18059,7 +18049,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18102,7 +18092,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 21634-2026</t>
+          <t>A 32796-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18116,10 +18106,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46149</v>
+        <v>45124</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18131,8 +18121,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18192,7 +18187,7 @@
         <v>45124</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18253,7 +18248,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 32830-2023</t>
+          <t>A 34849-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18263,14 +18258,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45124</v>
+        <v>45527</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18284,11 +18279,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18331,7 +18326,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 21081-2026</t>
+          <t>A 34886-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18345,10 +18340,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46146</v>
+        <v>45527</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18366,7 +18361,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>14.8</v>
+        <v>6.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18409,7 +18404,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 21137-2026</t>
+          <t>A 58121-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18423,10 +18418,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46146</v>
+        <v>45632</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18439,7 +18434,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18482,7 +18477,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 34861-2022</t>
+          <t>A 18229-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18496,10 +18491,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44796</v>
+        <v>45761</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18512,7 +18507,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18555,7 +18550,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 60893-2025</t>
+          <t>A 54170-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18569,10 +18564,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45999</v>
+        <v>44881</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18585,7 +18580,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18628,7 +18623,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 31831-2025</t>
+          <t>A 29427-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18642,10 +18637,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45834</v>
+        <v>45483</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18658,7 +18653,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18701,7 +18696,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 21106-2026</t>
+          <t>A 15563-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18715,10 +18710,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46146</v>
+        <v>44662</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18730,13 +18725,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>8.1</v>
+        <v>3.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18779,7 +18769,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 21146-2026</t>
+          <t>A 46300-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18793,10 +18783,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46146</v>
+        <v>44847</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18809,7 +18799,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18852,7 +18842,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 31968-2025</t>
+          <t>A 56280-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18866,10 +18856,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45835</v>
+        <v>45241</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18882,7 +18872,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18925,7 +18915,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 22221-2026</t>
+          <t>A 70214-2021</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18939,10 +18929,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46153</v>
+        <v>44535</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18955,7 +18945,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18998,7 +18988,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 22192-2026</t>
+          <t>A 21634-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19012,10 +19002,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19028,7 +19018,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19071,7 +19061,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 22222-2026</t>
+          <t>A 26325-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19085,10 +19075,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19101,7 +19091,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19144,7 +19134,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 63318-2023</t>
+          <t>A 10989-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19158,10 +19148,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45274</v>
+        <v>45723</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19174,7 +19164,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19217,7 +19207,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 44305-2026</t>
+          <t>A 59955-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19231,10 +19221,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46319</v>
+        <v>45993</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19246,8 +19236,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>7.9</v>
+        <v>4.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19290,7 +19285,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 21836-2025</t>
+          <t>A 65062-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19304,10 +19299,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45784</v>
+        <v>45287</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19319,8 +19314,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>4.2</v>
+        <v>11.3</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19363,7 +19363,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 23516-2026</t>
+          <t>A 67617-2021</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19377,10 +19377,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46163</v>
+        <v>44524</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19392,13 +19392,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19441,7 +19436,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 23505-2026</t>
+          <t>A 55835-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19455,10 +19450,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46163</v>
+        <v>45623</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19470,13 +19465,8 @@
           <t>FORSHAGA</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19519,7 +19509,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 26104-2026</t>
+          <t>A 30859-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19533,10 +19523,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46181</v>
+        <v>45497</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19549,7 +19539,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19592,7 +19582,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 26129-2026</t>
+          <t>A 35831-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19606,10 +19596,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46181</v>
+        <v>45148</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19621,8 +19611,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19665,7 +19660,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 27080-2026</t>
+          <t>A 44305-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19679,10 +19674,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46186</v>
+        <v>46319</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19695,7 +19690,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>5.4</v>
+        <v>7.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19738,7 +19733,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 27075-2026</t>
+          <t>A 22582-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19748,14 +19743,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46186</v>
+        <v>45447</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19767,8 +19762,13 @@
           <t>FORSHAGA</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I247" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19811,7 +19811,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 27076-2026</t>
+          <t>A 7297-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19825,10 +19825,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46186</v>
+        <v>44970</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19884,7 +19884,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 27252-2026</t>
+          <t>A 15663-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19894,14 +19894,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46188</v>
+        <v>45404</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19957,7 +19957,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 23020-2022</t>
+          <t>A 1409-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19971,10 +19971,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44719</v>
+        <v>45667</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20030,7 +20030,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>S 915-2022</t>
+          <t>S 5497-2022</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20044,10 +20044,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44606</v>
+        <v>44834</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>18.1</v>
+        <v>31.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20108,7 +20108,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>S 870-2022</t>
+          <t>S 4414-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20122,10 +20122,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>15.1</v>
+        <v>21</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20186,7 +20186,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>S 933-2022</t>
+          <t>S 4411-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20200,10 +20200,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>40.7</v>
+        <v>7.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20264,7 +20264,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>S 5497-2022</t>
+          <t>S 915-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20278,10 +20278,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44834</v>
+        <v>44606</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>31.1</v>
+        <v>18.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20342,7 +20342,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>S 4414-2023</t>
+          <t>S 6974-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20356,10 +20356,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>21</v>
+        <v>28.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20420,7 +20420,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>S 4411-2023</t>
+          <t>S 6964-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20434,10 +20434,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>7.3</v>
+        <v>18.8</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20498,7 +20498,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>S 6974-2022</t>
+          <t>S 4403-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20512,10 +20512,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>28.8</v>
+        <v>67.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20576,7 +20576,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>S 6964-2022</t>
+          <t>S 4429-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20590,10 +20590,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>18.8</v>
+        <v>80.3</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20654,7 +20654,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>S 4403-2023</t>
+          <t>S 870-2022</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>67.7</v>
+        <v>15.1</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20732,7 +20732,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>S 4429-2023</t>
+          <t>S 933-2022</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20746,10 +20746,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>80.3</v>
+        <v>40.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20827,7 +20827,7 @@
         <v>45834</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
